--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -32,7 +32,7 @@
     <t xml:space="preserve">Грошовий потік — звіт Pillar</t>
   </si>
   <si>
-    <t xml:space="preserve">Дані: 22.06.2026 · без проєктів на паузі/втрачених</t>
+    <t xml:space="preserve">Дані: 23.06.2026 · без проєктів на паузі/втрачених</t>
   </si>
   <si>
     <t xml:space="preserve">План усього, ₴</t>
@@ -786,7 +786,7 @@
       </c>
       <c r="B5" s="4" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"&lt;&gt;",'Графік надходжень'!G:G)</f>
-        <v>23879731.29</v>
+        <v>23975699.59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -795,7 +795,7 @@
       </c>
       <c r="B6" s="4" t="n">
         <f aca="false">B4-B5</f>
-        <v>58682759.85</v>
+        <v>58586791.55</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -804,7 +804,7 @@
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">IF(B4=0,0,B5/B4)</f>
-        <v>0.289232204119271</v>
+        <v>0.290394575780723</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1830,11 +1830,11 @@
         <v>95968.3</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>95968.3</v>
+        <v>96000</v>
       </c>
       <c r="H30" s="11" t="n">
         <f aca="false">F30-G30</f>
-        <v>0</v>
+        <v>-31.6999999999971</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>25</v>
@@ -2127,11 +2127,11 @@
         <v>95968.3</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0</v>
+        <v>95936.6</v>
       </c>
       <c r="H39" s="11" t="n">
         <f aca="false">F39-G39</f>
-        <v>95968.3</v>
+        <v>31.6999999999971</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>58</v>
@@ -2711,11 +2711,11 @@
       </c>
       <c r="G57" s="12" t="n">
         <f aca="false">SUM(G2:G56)</f>
-        <v>23879731.29</v>
+        <v>23975699.59</v>
       </c>
       <c r="H57" s="12" t="n">
         <f aca="false">SUM(H2:H56)</f>
-        <v>58682759.85</v>
+        <v>58586791.55</v>
       </c>
     </row>
   </sheetData>
@@ -2813,15 +2813,15 @@
       </c>
       <c r="C4" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-06",'Графік надходжень'!G:G)</f>
-        <v>4023024.33</v>
+        <v>4118992.63</v>
       </c>
       <c r="D4" s="11" t="n">
         <f aca="false">B4-C4</f>
-        <v>27702946.1</v>
+        <v>27606977.8</v>
       </c>
       <c r="E4" s="13" t="n">
         <f aca="false">IF(B4=0,0,C4/B4)</f>
-        <v>0.126805398715112</v>
+        <v>0.129830311702777</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2897,15 +2897,15 @@
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">SUM(C2:C7)</f>
-        <v>23879731.29</v>
+        <v>23975699.59</v>
       </c>
       <c r="D8" s="12" t="n">
         <f aca="false">SUM(D2:D7)</f>
-        <v>58682759.85</v>
+        <v>58586791.55</v>
       </c>
       <c r="E8" s="14" t="n">
         <f aca="false">IF(B8=0,0,C8/B8)</f>
-        <v>0.289232204119271</v>
+        <v>0.290394575780723</v>
       </c>
     </row>
   </sheetData>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Прострочені" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Графік надходжень'!$A$1:$I$56</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Прострочені!$A$1:$G$9</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Графік надходжень'!$A$1:$I$58</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Прострочені!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="72">
   <si>
     <t xml:space="preserve">Грошовий потік — звіт Pillar</t>
   </si>
   <si>
-    <t xml:space="preserve">Дані: 23.06.2026 · без проєктів на паузі/втрачених</t>
+    <t xml:space="preserve">Дані: 24.06.2026 · без проєктів на паузі/втрачених</t>
   </si>
   <si>
     <t xml:space="preserve">План усього, ₴</t>
@@ -161,6 +161,9 @@
     <t xml:space="preserve">П'ятий платіж</t>
   </si>
   <si>
+    <t xml:space="preserve">8602 Євген Весільна тераса Подорожнє</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
@@ -183,9 +186,6 @@
   </si>
   <si>
     <t xml:space="preserve">А Фора  SCP  32PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8602 Євген Весільна тераса Подорожнє</t>
   </si>
   <si>
     <t xml:space="preserve">А Головне управління Національної поліції в Одеській області  SCP  15PS</t>
@@ -777,7 +777,7 @@
       </c>
       <c r="B4" s="4" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"&lt;&gt;",'Графік надходжень'!F:F)</f>
-        <v>82562491.14</v>
+        <v>84072481.94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -786,7 +786,7 @@
       </c>
       <c r="B5" s="4" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"&lt;&gt;",'Графік надходжень'!G:G)</f>
-        <v>23975699.59</v>
+        <v>25485690.39</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -804,7 +804,7 @@
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">IF(B4=0,0,B5/B4)</f>
-        <v>0.290394575780723</v>
+        <v>0.303139502984917</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -813,7 +813,7 @@
       </c>
       <c r="B8" s="4" t="n">
         <f aca="false">SUMIF(Прострочені!A:A,"&lt;&gt;",Прострочені!G:G)</f>
-        <v>14958918.6</v>
+        <v>25095786.1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -822,7 +822,7 @@
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">COUNTIF('Графік надходжень'!J2:J100000,"&lt;&gt;")</f>
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -841,7 +841,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -1449,25 +1449,25 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>6842</v>
+        <v>7508</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>3308968</v>
+        <v>1245999.94</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>3308968</v>
+        <v>1245999.94</v>
       </c>
       <c r="H19" s="11" t="n">
         <f aca="false">F19-G19</f>
@@ -1482,25 +1482,25 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>7960</v>
+        <v>7508</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>99610.8</v>
+        <v>1502000</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>99610.8</v>
+        <v>1502000</v>
       </c>
       <c r="H20" s="11" t="n">
         <f aca="false">F20-G20</f>
@@ -1518,22 +1518,22 @@
         <v>46169</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>8454</v>
+        <v>6842</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>103606.2</v>
+        <v>3308968</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>103606.2</v>
+        <v>3308968</v>
       </c>
       <c r="H21" s="11" t="n">
         <f aca="false">F21-G21</f>
@@ -1548,25 +1548,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>8188</v>
+        <v>7960</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>208000</v>
+        <v>99610.8</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>208000</v>
+        <v>99610.8</v>
       </c>
       <c r="H22" s="11" t="n">
         <f aca="false">F22-G22</f>
@@ -1581,25 +1581,25 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>8454</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>69666</v>
+        <v>103606.2</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>69666</v>
+        <v>103606.2</v>
       </c>
       <c r="H23" s="11" t="n">
         <f aca="false">F23-G23</f>
@@ -1617,22 +1617,22 @@
         <v>46170</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>8544</v>
+        <v>8188</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>48</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>261990</v>
+        <v>208000</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>261990</v>
+        <v>208000</v>
       </c>
       <c r="H24" s="11" t="n">
         <f aca="false">F24-G24</f>
@@ -1647,25 +1647,25 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>8185</v>
+        <v>8454</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>168024</v>
+        <v>69666</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>168024</v>
+        <v>69666</v>
       </c>
       <c r="H25" s="11" t="n">
         <f aca="false">F25-G25</f>
@@ -1675,18 +1675,18 @@
         <v>25</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>46177</v>
+        <v>46170</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>7894</v>
+        <v>8544</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>32</v>
@@ -1695,10 +1695,10 @@
         <v>20</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>1487743.97</v>
+        <v>261990</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>1487743.97</v>
+        <v>261990</v>
       </c>
       <c r="H26" s="11" t="n">
         <f aca="false">F26-G26</f>
@@ -1708,30 +1708,30 @@
         <v>25</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>46178</v>
+        <v>46175</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>7508</v>
+        <v>8185</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>1245999.94</v>
+        <v>168024</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>1245999.94</v>
+        <v>168024</v>
       </c>
       <c r="H27" s="11" t="n">
         <f aca="false">F27-G27</f>
@@ -1741,30 +1741,30 @@
         <v>25</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>8140</v>
+        <v>7894</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>86041.2</v>
+        <v>1487743.97</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>86041.2</v>
+        <v>1487743.97</v>
       </c>
       <c r="H28" s="11" t="n">
         <f aca="false">F28-G28</f>
@@ -1774,18 +1774,18 @@
         <v>25</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>3456</v>
+        <v>8544</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>32</v>
@@ -1794,10 +1794,10 @@
         <v>30</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>783940.92</v>
+        <v>7990.8</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>783940.92</v>
+        <v>7990.8</v>
       </c>
       <c r="H29" s="11" t="n">
         <f aca="false">F29-G29</f>
@@ -1807,453 +1807,453 @@
         <v>25</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>8360</v>
+        <v>8140</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>95968.3</v>
+        <v>86041.2</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>96000</v>
+        <v>86041.2</v>
       </c>
       <c r="H30" s="11" t="n">
         <f aca="false">F30-G30</f>
-        <v>-31.6999999999971</v>
+        <v>0</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>25</v>
       </c>
       <c r="J30" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>7244</v>
+        <v>3456</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>132708.6</v>
+        <v>783940.92</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0</v>
+        <v>783940.92</v>
       </c>
       <c r="H31" s="11" t="n">
         <f aca="false">F31-G31</f>
-        <v>132708.6</v>
+        <v>0</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>7474</v>
+        <v>8360</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>1749999</v>
+        <v>95968.3</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="H32" s="11" t="n">
         <f aca="false">F32-G32</f>
-        <v>1749999</v>
+        <v>-31.6999999999971</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J32" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>6406</v>
+        <v>7244</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>373582</v>
+        <v>132708.6</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>155306</v>
+        <v>0</v>
       </c>
       <c r="H33" s="11" t="n">
         <f aca="false">F33-G33</f>
-        <v>218276</v>
+        <v>132708.6</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>21</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>7002</v>
+        <v>7474</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>573945</v>
+        <v>1749999</v>
       </c>
       <c r="G34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="11" t="n">
         <f aca="false">F34-G34</f>
-        <v>573945</v>
+        <v>1749999</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>21</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>5870</v>
+        <v>6406</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>7800000</v>
+        <v>373582</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0</v>
+        <v>155306</v>
       </c>
       <c r="H35" s="11" t="n">
         <f aca="false">F35-G35</f>
-        <v>7800000</v>
+        <v>218276</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>21</v>
       </c>
       <c r="J35" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>120000</v>
+        <v>573945</v>
       </c>
       <c r="G36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="11" t="n">
         <f aca="false">F36-G36</f>
-        <v>120000</v>
+        <v>573945</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>21</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>46195</v>
+        <v>46189</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>8644</v>
+        <v>5870</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>415900</v>
+        <v>7800000</v>
       </c>
       <c r="G37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="11" t="n">
         <f aca="false">F37-G37</f>
-        <v>415900</v>
+        <v>7800000</v>
       </c>
       <c r="I37" s="9" t="s">
         <v>21</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>46197</v>
+        <v>46195</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>10136835.8</v>
+        <v>120000</v>
       </c>
       <c r="G38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="11" t="n">
         <f aca="false">F38-G38</f>
-        <v>10136835.8</v>
+        <v>120000</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="J38" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>46197</v>
+        <v>46195</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>8360</v>
+        <v>8644</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>95968.3</v>
+        <v>415900</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>95936.6</v>
+        <v>0</v>
       </c>
       <c r="H39" s="11" t="n">
         <f aca="false">F39-G39</f>
-        <v>31.6999999999971</v>
+        <v>415900</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>46202</v>
+        <v>46197</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>6704</v>
+        <v>5910</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>6396000</v>
+        <v>10136835.8</v>
       </c>
       <c r="G40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="11" t="n">
         <f aca="false">F40-G40</f>
-        <v>6396000</v>
+        <v>10136835.8</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>46203</v>
+        <v>46197</v>
       </c>
       <c r="B41" s="9" t="n">
-        <v>8185</v>
+        <v>8360</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>63313.4</v>
+        <v>95968.3</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>0</v>
+        <v>95936.6</v>
       </c>
       <c r="H41" s="11" t="n">
         <f aca="false">F41-G41</f>
-        <v>63313.4</v>
+        <v>31.6999999999971</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>7002</v>
+        <v>6704</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>126896.64</v>
+        <v>6396000</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="11" t="n">
         <f aca="false">F42-G42</f>
-        <v>126896.64</v>
+        <v>6396000</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>58</v>
       </c>
       <c r="J42" s="0" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>46211</v>
+        <v>46203</v>
       </c>
       <c r="B43" s="9" t="n">
         <v>8185</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>63313.4</v>
@@ -2269,18 +2269,18 @@
         <v>58</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>46214</v>
+        <v>46210</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>32</v>
@@ -2289,14 +2289,14 @@
         <v>30</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>15929313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="11" t="n">
         <f aca="false">F44-G44</f>
-        <v>15929313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="I44" s="9" t="s">
         <v>58</v>
@@ -2307,13 +2307,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>46215</v>
+        <v>46211</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>7002</v>
+        <v>8185</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>32</v>
@@ -2322,14 +2322,14 @@
         <v>34</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="11" t="n">
         <f aca="false">F45-G45</f>
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="I45" s="9" t="s">
         <v>58</v>
@@ -2340,29 +2340,29 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>46220</v>
+        <v>46214</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>8188</v>
+        <v>5910</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>73926</v>
+        <v>15929313.4</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="11" t="n">
         <f aca="false">F46-G46</f>
-        <v>73926</v>
+        <v>15929313.4</v>
       </c>
       <c r="I46" s="9" t="s">
         <v>58</v>
@@ -2373,13 +2373,13 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>46225</v>
+        <v>46215</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>3456</v>
+        <v>7002</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>32</v>
@@ -2388,14 +2388,14 @@
         <v>34</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>335974.68</v>
+        <v>126896.64</v>
       </c>
       <c r="G47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="11" t="n">
         <f aca="false">F47-G47</f>
-        <v>335974.68</v>
+        <v>126896.64</v>
       </c>
       <c r="I47" s="9" t="s">
         <v>58</v>
@@ -2406,32 +2406,32 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>46225</v>
+        <v>46220</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>8008</v>
+        <v>8188</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>178088.4</v>
+        <v>73926</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>178088.4</v>
+        <v>0</v>
       </c>
       <c r="H48" s="11" t="n">
         <f aca="false">F48-G48</f>
-        <v>0</v>
+        <v>73926</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="J48" s="0" t="s">
         <v>59</v>
@@ -2439,29 +2439,29 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>7894</v>
+        <v>3456</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>737597.4</v>
+        <v>335974.68</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="11" t="n">
         <f aca="false">F49-G49</f>
-        <v>737597.4</v>
+        <v>335974.68</v>
       </c>
       <c r="I49" s="9" t="s">
         <v>58</v>
@@ -2472,7 +2472,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>46233</v>
+        <v>46225</v>
       </c>
       <c r="B50" s="9" t="n">
         <v>8008</v>
@@ -2484,20 +2484,20 @@
         <v>32</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F50" s="10" t="n">
         <v>178088.4</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>0</v>
+        <v>178088.4</v>
       </c>
       <c r="H50" s="11" t="n">
         <f aca="false">F50-G50</f>
-        <v>178088.4</v>
+        <v>0</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="J50" s="0" t="s">
         <v>59</v>
@@ -2505,29 +2505,29 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="B51" s="9" t="n">
         <v>7894</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>185968</v>
+        <v>737597.4</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="11" t="n">
         <f aca="false">F51-G51</f>
-        <v>185968</v>
+        <v>737597.4</v>
       </c>
       <c r="I51" s="9" t="s">
         <v>58</v>
@@ -2538,13 +2538,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>46245</v>
+        <v>46233</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>7894</v>
+        <v>8008</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>32</v>
@@ -2553,80 +2553,80 @@
         <v>34</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>185967.99</v>
+        <v>178088.4</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="11" t="n">
         <f aca="false">F52-G52</f>
-        <v>185967.99</v>
+        <v>178088.4</v>
       </c>
       <c r="I52" s="9" t="s">
         <v>58</v>
       </c>
       <c r="J52" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>46246</v>
+        <v>46234</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>2896238.8</v>
+        <v>185968</v>
       </c>
       <c r="G53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="11" t="n">
         <f aca="false">F53-G53</f>
-        <v>2896238.8</v>
+        <v>185968</v>
       </c>
       <c r="I53" s="9" t="s">
         <v>58</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>46260</v>
+        <v>46245</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>7002</v>
+        <v>7894</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>573945</v>
+        <v>185967.99</v>
       </c>
       <c r="G54" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="11" t="n">
         <f aca="false">F54-G54</f>
-        <v>573945</v>
+        <v>185967.99</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>58</v>
@@ -2637,46 +2637,46 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>46277</v>
+        <v>46246</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>4880000</v>
+        <v>2896238.8</v>
       </c>
       <c r="G55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="11" t="n">
         <f aca="false">F55-G55</f>
-        <v>4880000</v>
+        <v>2896238.8</v>
       </c>
       <c r="I55" s="9" t="s">
         <v>58</v>
       </c>
       <c r="J55" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>7894</v>
+        <v>7002</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>32</v>
@@ -2685,41 +2685,107 @@
         <v>43</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>737597.4</v>
+        <v>573945</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="11" t="n">
         <f aca="false">F56-G56</f>
-        <v>737597.4</v>
+        <v>573945</v>
       </c>
       <c r="I56" s="9" t="s">
         <v>58</v>
       </c>
       <c r="J56" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F57" s="10" t="n">
+        <v>4880000</v>
+      </c>
+      <c r="G57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="11" t="n">
+        <f aca="false">F57-G57</f>
+        <v>4880000</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J57" s="0" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E57" s="3" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>7894</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>737597.4</v>
+      </c>
+      <c r="G58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="11" t="n">
+        <f aca="false">F58-G58</f>
+        <v>737597.4</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J58" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E59" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F57" s="12" t="n">
-        <f aca="false">SUM(F2:F56)</f>
-        <v>82562491.14</v>
-      </c>
-      <c r="G57" s="12" t="n">
-        <f aca="false">SUM(G2:G56)</f>
-        <v>23975699.59</v>
-      </c>
-      <c r="H57" s="12" t="n">
-        <f aca="false">SUM(H2:H56)</f>
+      <c r="F59" s="12" t="n">
+        <f aca="false">SUM(F2:F58)</f>
+        <v>84072481.94</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <f aca="false">SUM(G2:G58)</f>
+        <v>25485690.39</v>
+      </c>
+      <c r="H59" s="12" t="n">
+        <f aca="false">SUM(H2:H58)</f>
         <v>58586791.55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I56"/>
+  <autoFilter ref="A1:I58"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2788,11 +2854,11 @@
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-05",'Графік надходжень'!F:F)</f>
-        <v>17187965.56</v>
+        <v>19935965.5</v>
       </c>
       <c r="C3" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-05",'Графік надходжень'!G:G)</f>
-        <v>17187965.56</v>
+        <v>19935965.5</v>
       </c>
       <c r="D3" s="11" t="n">
         <f aca="false">B3-C3</f>
@@ -2809,11 +2875,11 @@
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-06",'Графік надходжень'!F:F)</f>
-        <v>31725970.43</v>
+        <v>30487961.29</v>
       </c>
       <c r="C4" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-06",'Графік надходжень'!G:G)</f>
-        <v>4118992.63</v>
+        <v>2880983.49</v>
       </c>
       <c r="D4" s="11" t="n">
         <f aca="false">B4-C4</f>
@@ -2821,7 +2887,7 @@
       </c>
       <c r="E4" s="13" t="n">
         <f aca="false">IF(B4=0,0,C4/B4)</f>
-        <v>0.129830311702777</v>
+        <v>0.0944957736791984</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2893,11 +2959,11 @@
       </c>
       <c r="B8" s="12" t="n">
         <f aca="false">SUM(B2:B7)</f>
-        <v>82562491.14</v>
+        <v>84072481.94</v>
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">SUM(C2:C7)</f>
-        <v>23975699.59</v>
+        <v>25485690.39</v>
       </c>
       <c r="D8" s="12" t="n">
         <f aca="false">SUM(D2:D7)</f>
@@ -2905,7 +2971,7 @@
       </c>
       <c r="E8" s="14" t="n">
         <f aca="false">IF(B8=0,0,C8/B8)</f>
-        <v>0.290394575780723</v>
+        <v>0.303139502984917</v>
       </c>
     </row>
   </sheetData>
@@ -2924,7 +2990,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -2959,215 +3025,263 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="n">
-        <v>46189</v>
+        <v>46197</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5870</v>
+        <v>5910</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>7800000</v>
+        <v>10136835.8</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="11" t="n">
         <f aca="false">E2-F2</f>
-        <v>7800000</v>
+        <v>10136835.8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
-        <v>46113</v>
+        <v>46189</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>7068</v>
+        <v>5870</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>5640128</v>
+        <v>7800000</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G3" s="11" t="n">
         <f aca="false">E3-F3</f>
-        <v>3948090</v>
+        <v>7800000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
-        <v>46185</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7474</v>
+        <v>7068</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1749999</v>
+        <v>5640128</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G4" s="11" t="n">
         <f aca="false">E4-F4</f>
-        <v>1749999</v>
+        <v>3948090</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>7002</v>
+        <v>7474</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>573945</v>
+        <v>1749999</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="11" t="n">
         <f aca="false">E5-F5</f>
-        <v>573945</v>
+        <v>1749999</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>8644</v>
+        <v>7002</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>415900</v>
+        <v>573945</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="11" t="n">
         <f aca="false">E6-F6</f>
-        <v>415900</v>
+        <v>573945</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>6406</v>
+        <v>8644</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>373582</v>
+        <v>415900</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>155306</v>
+        <v>0</v>
       </c>
       <c r="G7" s="11" t="n">
         <f aca="false">E7-F7</f>
-        <v>218276</v>
+        <v>415900</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>7244</v>
+        <v>6406</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>132708.6</v>
+        <v>373582</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0</v>
+        <v>155306</v>
       </c>
       <c r="G8" s="11" t="n">
         <f aca="false">E8-F8</f>
-        <v>132708.6</v>
+        <v>218276</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>46195</v>
+        <v>46185</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>4766</v>
+        <v>7244</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>120000</v>
+        <v>132708.6</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">E9-F9</f>
+        <v>132708.6</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="11" t="n">
         <v>120000</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="3" t="s">
+      <c r="F10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <f aca="false">E10-F10</f>
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>8360</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>95968.3</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>95936.6</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <f aca="false">E11-F11</f>
+        <v>31.6999999999971</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="12" t="n">
-        <f aca="false">SUM(E2:E9)</f>
-        <v>16806262.6</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <f aca="false">SUM(F2:F9)</f>
-        <v>1847344</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <f aca="false">SUM(G2:G9)</f>
-        <v>14958918.6</v>
+      <c r="E12" s="12" t="n">
+        <f aca="false">SUM(E2:E11)</f>
+        <v>27039066.7</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <f aca="false">SUM(F2:F11)</f>
+        <v>1943280.6</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <f aca="false">SUM(G2:G11)</f>
+        <v>25095786.1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G11"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Прострочені" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Графік надходжень'!$A$1:$I$58</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Прострочені!$A$1:$G$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Графік надходжень'!$A$1:$I$62</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Прострочені!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="73">
   <si>
     <t xml:space="preserve">Грошовий потік — звіт Pillar</t>
   </si>
   <si>
-    <t xml:space="preserve">Дані: 24.06.2026 · без проєктів на паузі/втрачених</t>
+    <t xml:space="preserve">Дані: 25.06.2026 · без проєктів на паузі/втрачених</t>
   </si>
   <si>
     <t xml:space="preserve">План усього, ₴</t>
@@ -179,12 +179,15 @@
     <t xml:space="preserve">Isolar фланець Хмельницький</t>
   </si>
   <si>
+    <t xml:space="preserve">А Сцена Корчин</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06</t>
+  </si>
+  <si>
     <t xml:space="preserve">Фундамент Hytte House Development Славське</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06</t>
-  </si>
-  <si>
     <t xml:space="preserve">А Фора  SCP  32PS</t>
   </si>
   <si>
@@ -194,16 +197,16 @@
     <t xml:space="preserve">Максим Яловий Чинадієво</t>
   </si>
   <si>
+    <t xml:space="preserve">Solars ГШ 1,7+надставки 3,5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">очікується</t>
+  </si>
+  <si>
+    <t xml:space="preserve">А   AGM 2V</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALTECO Carport Model Taurus 280кВт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solars ГШ 1,7+надставки 3,5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">А   AGM 2V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">очікується</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07</t>
@@ -777,7 +780,7 @@
       </c>
       <c r="B4" s="4" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"&lt;&gt;",'Графік надходжень'!F:F)</f>
-        <v>84072481.94</v>
+        <v>83776816.96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -786,7 +789,7 @@
       </c>
       <c r="B5" s="4" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"&lt;&gt;",'Графік надходжень'!G:G)</f>
-        <v>25485690.39</v>
+        <v>28509018.41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -795,7 +798,7 @@
       </c>
       <c r="B6" s="4" t="n">
         <f aca="false">B4-B5</f>
-        <v>58586791.55</v>
+        <v>55267798.55</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -804,7 +807,7 @@
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">IF(B4=0,0,B5/B4)</f>
-        <v>0.303139502984917</v>
+        <v>0.340297225945119</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -813,7 +816,7 @@
       </c>
       <c r="B8" s="4" t="n">
         <f aca="false">SUMIF(Прострочені!A:A,"&lt;&gt;",Прострочені!G:G)</f>
-        <v>25095786.1</v>
+        <v>12322066.7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -822,7 +825,7 @@
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">COUNTIF('Графік надходжень'!J2:J100000,"&lt;&gt;")</f>
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -841,7 +844,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -1497,10 +1500,10 @@
         <v>30</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1502000</v>
+        <v>751000.06</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>1502000</v>
+        <v>751000.06</v>
       </c>
       <c r="H20" s="11" t="n">
         <f aca="false">F20-G20</f>
@@ -1629,10 +1632,10 @@
         <v>20</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>208000</v>
+        <v>206200</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>208000</v>
+        <v>206200</v>
       </c>
       <c r="H24" s="11" t="n">
         <f aca="false">F24-G24</f>
@@ -1716,22 +1719,22 @@
         <v>46175</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>8185</v>
+        <v>5682</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>168024</v>
+        <v>87150</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>168024</v>
+        <v>87150</v>
       </c>
       <c r="H27" s="11" t="n">
         <f aca="false">F27-G27</f>
@@ -1746,10 +1749,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>7894</v>
+        <v>8185</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>52</v>
@@ -1761,10 +1764,10 @@
         <v>20</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>1487743.97</v>
+        <v>168024</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>1487743.97</v>
+        <v>168024</v>
       </c>
       <c r="H28" s="11" t="n">
         <f aca="false">F28-G28</f>
@@ -1779,25 +1782,25 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>8544</v>
+        <v>7894</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>7990.8</v>
+        <v>1487743.97</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>7990.8</v>
+        <v>1487743.97</v>
       </c>
       <c r="H29" s="11" t="n">
         <f aca="false">F29-G29</f>
@@ -1812,25 +1815,25 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>8140</v>
+        <v>8544</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>86041.2</v>
+        <v>7990.8</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>86041.2</v>
+        <v>7990.8</v>
       </c>
       <c r="H30" s="11" t="n">
         <f aca="false">F30-G30</f>
@@ -1845,25 +1848,25 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>3456</v>
+        <v>8140</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>783940.92</v>
+        <v>86041.2</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>783940.92</v>
+        <v>86041.2</v>
       </c>
       <c r="H31" s="11" t="n">
         <f aca="false">F31-G31</f>
@@ -1881,10 +1884,10 @@
         <v>46184</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>8360</v>
+        <v>3456</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>32</v>
@@ -1893,14 +1896,14 @@
         <v>30</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>95968.3</v>
+        <v>783940.92</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>96000</v>
+        <v>783940.92</v>
       </c>
       <c r="H32" s="11" t="n">
         <f aca="false">F32-G32</f>
-        <v>-31.6999999999971</v>
+        <v>0</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>25</v>
@@ -1911,32 +1914,32 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>7244</v>
+        <v>8360</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>132708.6</v>
+        <v>95968.3</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="H33" s="11" t="n">
         <f aca="false">F33-G33</f>
-        <v>132708.6</v>
+        <v>-31.6999999999971</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>51</v>
@@ -1950,7 +1953,7 @@
         <v>7474</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>24</v>
@@ -1962,14 +1965,14 @@
         <v>1749999</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0</v>
+        <v>1749999</v>
       </c>
       <c r="H34" s="11" t="n">
         <f aca="false">F34-G34</f>
-        <v>1749999</v>
+        <v>0</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>51</v>
@@ -1983,7 +1986,7 @@
         <v>6406</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>19</v>
@@ -1992,17 +1995,17 @@
         <v>20</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>373582</v>
+        <v>154980</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>155306</v>
+        <v>154980</v>
       </c>
       <c r="H35" s="11" t="n">
         <f aca="false">F35-G35</f>
-        <v>218276</v>
+        <v>0</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>51</v>
@@ -2010,29 +2013,29 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>7002</v>
+        <v>5870</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>573945</v>
+        <v>7800000</v>
       </c>
       <c r="G36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="11" t="n">
         <f aca="false">F36-G36</f>
-        <v>573945</v>
+        <v>7800000</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>21</v>
@@ -2046,26 +2049,26 @@
         <v>46189</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>5870</v>
+        <v>7002</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>7800000</v>
+        <v>573945</v>
       </c>
       <c r="G37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="11" t="n">
         <f aca="false">F37-G37</f>
-        <v>7800000</v>
+        <v>573945</v>
       </c>
       <c r="I37" s="9" t="s">
         <v>21</v>
@@ -2079,29 +2082,29 @@
         <v>46195</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>4766</v>
+        <v>8644</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>120000</v>
+        <v>415900</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>0</v>
+        <v>415900</v>
       </c>
       <c r="H38" s="11" t="n">
         <f aca="false">F38-G38</f>
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J38" s="0" t="s">
         <v>51</v>
@@ -2109,32 +2112,32 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>8644</v>
+        <v>5682</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>415900</v>
+        <v>369984.96</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0</v>
+        <v>369984.96</v>
       </c>
       <c r="H39" s="11" t="n">
         <f aca="false">F39-G39</f>
-        <v>415900</v>
+        <v>0</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J39" s="0" t="s">
         <v>51</v>
@@ -2145,29 +2148,29 @@
         <v>46197</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>5910</v>
+        <v>7068</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>10136835.8</v>
+        <v>0</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>0</v>
+        <v>1153420</v>
       </c>
       <c r="H40" s="11" t="n">
         <f aca="false">F40-G40</f>
-        <v>10136835.8</v>
+        <v>-1153420</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="J40" s="0" t="s">
         <v>51</v>
@@ -2233,7 +2236,7 @@
         <v>6396000</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J42" s="0" t="s">
         <v>51</v>
@@ -2244,29 +2247,29 @@
         <v>46203</v>
       </c>
       <c r="B43" s="9" t="n">
-        <v>8185</v>
+        <v>5910</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>63313.4</v>
+        <v>10136835.8</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="11" t="n">
         <f aca="false">F43-G43</f>
-        <v>63313.4</v>
+        <v>10136835.8</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J43" s="0" t="s">
         <v>51</v>
@@ -2274,13 +2277,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>46210</v>
+        <v>46203</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>7002</v>
+        <v>8185</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>32</v>
@@ -2289,163 +2292,163 @@
         <v>30</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="11" t="n">
         <f aca="false">F44-G44</f>
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>46211</v>
+        <v>46204</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>8185</v>
+        <v>4766</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>63313.4</v>
+        <v>120000</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="11" t="n">
         <f aca="false">F45-G45</f>
-        <v>63313.4</v>
+        <v>120000</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>46214</v>
+        <v>46206</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>5910</v>
+        <v>7244</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>15929313.4</v>
+        <v>132708.6</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="11" t="n">
         <f aca="false">F46-G46</f>
-        <v>15929313.4</v>
+        <v>132708.6</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J46" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>46215</v>
+        <v>46209</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>7002</v>
+        <v>8188</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>126896.64</v>
+        <v>73926</v>
       </c>
       <c r="G47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="11" t="n">
         <f aca="false">F47-G47</f>
-        <v>126896.64</v>
+        <v>73926</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J47" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>46220</v>
+        <v>46210</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>8188</v>
+        <v>7002</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>73926</v>
+        <v>126896.64</v>
       </c>
       <c r="G48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="11" t="n">
         <f aca="false">F48-G48</f>
-        <v>73926</v>
+        <v>126896.64</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J48" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>46225</v>
+        <v>46211</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>3456</v>
+        <v>8185</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>32</v>
@@ -2454,97 +2457,97 @@
         <v>34</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>335974.68</v>
+        <v>63313.4</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="11" t="n">
         <f aca="false">F49-G49</f>
-        <v>335974.68</v>
+        <v>63313.4</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J49" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>8008</v>
+        <v>6406</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>178088.4</v>
+        <v>218602</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>178088.4</v>
+        <v>0</v>
       </c>
       <c r="H50" s="11" t="n">
         <f aca="false">F50-G50</f>
-        <v>0</v>
+        <v>218602</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="J50" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>46231</v>
+        <v>46214</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>737597.4</v>
+        <v>15929313.4</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="11" t="n">
         <f aca="false">F51-G51</f>
-        <v>737597.4</v>
+        <v>15929313.4</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J51" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>46233</v>
+        <v>46215</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>8008</v>
+        <v>7002</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>32</v>
@@ -2553,83 +2556,83 @@
         <v>34</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>178088.4</v>
+        <v>126896.64</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="11" t="n">
         <f aca="false">F52-G52</f>
-        <v>178088.4</v>
+        <v>126896.64</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J52" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>46234</v>
+        <v>46225</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>7894</v>
+        <v>3456</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>185968</v>
+        <v>335974.68</v>
       </c>
       <c r="G53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="11" t="n">
         <f aca="false">F53-G53</f>
-        <v>185968</v>
+        <v>335974.68</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>46245</v>
+        <v>46225</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>7894</v>
+        <v>8008</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>185967.99</v>
+        <v>178088.4</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>0</v>
+        <v>178088.4</v>
       </c>
       <c r="H54" s="11" t="n">
         <f aca="false">F54-G54</f>
-        <v>185967.99</v>
+        <v>0</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="J54" s="0" t="s">
         <v>60</v>
@@ -2637,32 +2640,32 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>46246</v>
+        <v>46231</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>2896238.8</v>
+        <v>737597.4</v>
       </c>
       <c r="G55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="11" t="n">
         <f aca="false">F55-G55</f>
-        <v>2896238.8</v>
+        <v>737597.4</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J55" s="0" t="s">
         <v>60</v>
@@ -2670,32 +2673,32 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>46260</v>
+        <v>46233</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>7002</v>
+        <v>8008</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>573945</v>
+        <v>178088.4</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="11" t="n">
         <f aca="false">F56-G56</f>
-        <v>573945</v>
+        <v>178088.4</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J56" s="0" t="s">
         <v>60</v>
@@ -2703,89 +2706,221 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
-        <v>46277</v>
+        <v>46234</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>4766</v>
+        <v>7894</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4880000</v>
+        <v>185968</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="11" t="n">
         <f aca="false">F57-G57</f>
-        <v>4880000</v>
+        <v>185968</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
-        <v>46282</v>
+        <v>46245</v>
       </c>
       <c r="B58" s="9" t="n">
         <v>7894</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>737597.4</v>
+        <v>185967.99</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="11" t="n">
         <f aca="false">F58-G58</f>
-        <v>737597.4</v>
+        <v>185967.99</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J58" s="0" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E59" s="3" t="s">
+      <c r="A59" s="8" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>5910</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F59" s="10" t="n">
+        <v>2896238.8</v>
+      </c>
+      <c r="G59" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <f aca="false">F59-G59</f>
+        <v>2896238.8</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J59" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="8" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>7002</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>573945</v>
+      </c>
+      <c r="G60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="11" t="n">
+        <f aca="false">F60-G60</f>
+        <v>573945</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J60" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F61" s="10" t="n">
+        <v>4880000</v>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="11" t="n">
+        <f aca="false">F61-G61</f>
+        <v>4880000</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J61" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="F59" s="12" t="n">
-        <f aca="false">SUM(F2:F58)</f>
-        <v>84072481.94</v>
-      </c>
-      <c r="G59" s="12" t="n">
-        <f aca="false">SUM(G2:G58)</f>
-        <v>25485690.39</v>
-      </c>
-      <c r="H59" s="12" t="n">
-        <f aca="false">SUM(H2:H58)</f>
-        <v>58586791.55</v>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="8" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B62" s="9" t="n">
+        <v>7894</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>737597.4</v>
+      </c>
+      <c r="G62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="11" t="n">
+        <f aca="false">F62-G62</f>
+        <v>737597.4</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J62" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E63" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <f aca="false">SUM(F2:F62)</f>
+        <v>83776816.96</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <f aca="false">SUM(G2:G62)</f>
+        <v>28509018.41</v>
+      </c>
+      <c r="H63" s="12" t="n">
+        <f aca="false">SUM(H2:H62)</f>
+        <v>55267798.55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I58"/>
+  <autoFilter ref="A1:I62"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2812,7 +2947,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>13</v>
@@ -2824,12 +2959,12 @@
         <v>15</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-04",'Графік надходжень'!F:F)</f>
@@ -2850,15 +2985,15 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-05",'Графік надходжень'!F:F)</f>
-        <v>19935965.5</v>
+        <v>19183165.56</v>
       </c>
       <c r="C3" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-05",'Графік надходжень'!G:G)</f>
-        <v>19935965.5</v>
+        <v>19183165.56</v>
       </c>
       <c r="D3" s="11" t="n">
         <f aca="false">B3-C3</f>
@@ -2871,32 +3006,32 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-06",'Графік надходжень'!F:F)</f>
-        <v>30487961.29</v>
+        <v>30473785.65</v>
       </c>
       <c r="C4" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-06",'Графік надходжень'!G:G)</f>
-        <v>2880983.49</v>
+        <v>6657111.45</v>
       </c>
       <c r="D4" s="11" t="n">
         <f aca="false">B4-C4</f>
-        <v>27606977.8</v>
+        <v>23816674.2</v>
       </c>
       <c r="E4" s="13" t="n">
         <f aca="false">IF(B4=0,0,C4/B4)</f>
-        <v>0.0944957736791984</v>
+        <v>0.218453707276766</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-07",'Графік надходжень'!F:F)</f>
-        <v>17936062.96</v>
+        <v>18407373.56</v>
       </c>
       <c r="C5" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-07",'Графік надходжень'!G:G)</f>
@@ -2904,16 +3039,16 @@
       </c>
       <c r="D5" s="11" t="n">
         <f aca="false">B5-C5</f>
-        <v>17757974.56</v>
+        <v>18229285.16</v>
       </c>
       <c r="E5" s="13" t="n">
         <f aca="false">IF(B5=0,0,C5/B5)</f>
-        <v>0.00992906862543707</v>
+        <v>0.00967484032523758</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-08",'Графік надходжень'!F:F)</f>
@@ -2934,7 +3069,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">SUMIF('Графік надходжень'!J:J,"2026-09",'Графік надходжень'!F:F)</f>
@@ -2955,23 +3090,23 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" s="12" t="n">
         <f aca="false">SUM(B2:B7)</f>
-        <v>84072481.94</v>
+        <v>83776816.96</v>
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">SUM(C2:C7)</f>
-        <v>25485690.39</v>
+        <v>28509018.41</v>
       </c>
       <c r="D8" s="12" t="n">
         <f aca="false">SUM(D2:D7)</f>
-        <v>58586791.55</v>
+        <v>55267798.55</v>
       </c>
       <c r="E8" s="14" t="n">
         <f aca="false">IF(B8=0,0,C8/B8)</f>
-        <v>0.303139502984917</v>
+        <v>0.340297225945119</v>
       </c>
     </row>
   </sheetData>
@@ -2990,7 +3125,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -3020,268 +3155,124 @@
         <v>14</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="n">
-        <v>46197</v>
+        <v>46189</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5910</v>
+        <v>5870</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>10136835.8</v>
+        <v>7800000</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="11" t="n">
         <f aca="false">E2-F2</f>
-        <v>10136835.8</v>
+        <v>7800000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
-        <v>46189</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>5870</v>
+        <v>7068</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>7800000</v>
+        <v>5640128</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G3" s="11" t="n">
         <f aca="false">E3-F3</f>
-        <v>7800000</v>
+        <v>3948090</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
-        <v>46113</v>
+        <v>46189</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7068</v>
+        <v>7002</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5640128</v>
+        <v>573945</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G4" s="11" t="n">
         <f aca="false">E4-F4</f>
-        <v>3948090</v>
+        <v>573945</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>7474</v>
+        <v>8360</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1749999</v>
+        <v>95968.3</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0</v>
+        <v>95936.6</v>
       </c>
       <c r="G5" s="11" t="n">
         <f aca="false">E5-F5</f>
-        <v>1749999</v>
+        <v>31.6999999999971</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>7002</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>573945</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <f aca="false">E6-F6</f>
-        <v>573945</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
-        <v>46195</v>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>8644</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>415900</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <f aca="false">E7-F7</f>
-        <v>415900</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>6406</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>373582</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>155306</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <f aca="false">E8-F8</f>
-        <v>218276</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="n">
-        <v>46185</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>7244</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>132708.6</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <f aca="false">E9-F9</f>
-        <v>132708.6</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
-        <v>46195</v>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>4766</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <f aca="false">E10-F10</f>
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
-        <v>46197</v>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>8360</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>95968.3</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>95936.6</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <f aca="false">E11-F11</f>
-        <v>31.6999999999971</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <f aca="false">SUM(E2:E11)</f>
-        <v>27039066.7</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <f aca="false">SUM(F2:F11)</f>
-        <v>1943280.6</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <f aca="false">SUM(G2:G11)</f>
-        <v>25095786.1</v>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <f aca="false">SUM(E2:E5)</f>
+        <v>14110041.3</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <f aca="false">SUM(F2:F5)</f>
+        <v>1787974.6</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <f aca="false">SUM(G2:G5)</f>
+        <v>12322066.7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G5"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Графік надходжень'!$A$1:$I$62</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Прострочені!$A$1:$G$5</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Прострочені!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="73">
   <si>
     <t xml:space="preserve">Грошовий потік — звіт Pillar</t>
   </si>
@@ -816,7 +816,7 @@
       </c>
       <c r="B8" s="4" t="n">
         <f aca="false">SUMIF(Прострочені!A:A,"&lt;&gt;",Прострочені!G:G)</f>
-        <v>12322066.7</v>
+        <v>12322035</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1932,11 +1932,11 @@
         <v>95968.3</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>96000</v>
+        <v>95968.3</v>
       </c>
       <c r="H33" s="11" t="n">
         <f aca="false">F33-G33</f>
-        <v>-31.6999999999971</v>
+        <v>0</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>25</v>
@@ -2196,14 +2196,14 @@
         <v>95968.3</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>95936.6</v>
+        <v>95968.3</v>
       </c>
       <c r="H41" s="11" t="n">
         <f aca="false">F41-G41</f>
-        <v>31.6999999999971</v>
+        <v>0</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J41" s="0" t="s">
         <v>51</v>
@@ -3125,7 +3125,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -3231,48 +3231,24 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="n">
-        <v>46197</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>8360</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>95968.3</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>95936.6</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <f aca="false">E5-F5</f>
-        <v>31.6999999999971</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D6" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="12" t="n">
-        <f aca="false">SUM(E2:E5)</f>
-        <v>14110041.3</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <f aca="false">SUM(F2:F5)</f>
-        <v>1787974.6</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <f aca="false">SUM(G2:G5)</f>
-        <v>12322066.7</v>
+      <c r="E5" s="12" t="n">
+        <f aca="false">SUM(E2:E4)</f>
+        <v>14014073</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <f aca="false">SUM(F2:F4)</f>
+        <v>1692038</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <f aca="false">SUM(G2:G4)</f>
+        <v>12322035</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G4"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 26.06.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 30.06.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -2133,25 +2133,25 @@
         <v>46189</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>5870</v>
+        <v>7002</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7800000</v>
+        <v>573945</v>
       </c>
       <c r="G36" s="10" t="n">
         <v>0</v>
@@ -2173,31 +2173,31 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>7002</v>
+        <v>8644</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Solars ГШ 1,7+надставки 3,5</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>573945</v>
+        <v>415900</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0</v>
+        <v>415900</v>
       </c>
       <c r="H37" s="11">
         <f>F37-G37</f>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2216,31 +2216,31 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>8644</v>
+        <v>5682</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Solars ГШ 1,7+надставки 3,5</t>
+          <t>А Сцена Корчин</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>415900</v>
+        <v>369984.96</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>415900</v>
+        <v>369984.96</v>
       </c>
       <c r="H38" s="11">
         <f>F38-G38</f>
@@ -2259,19 +2259,19 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>5682</v>
+        <v>7068</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>А Сцена Корчин</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>369984.96</v>
+        <v>0</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>369984.96</v>
+        <v>1153420</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2305,28 +2305,28 @@
         <v>46197</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>7068</v>
+        <v>8360</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>Хаджет Лебедівка</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>0</v>
+        <v>95968.3</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>1153420</v>
+        <v>95968.3</v>
       </c>
       <c r="H40" s="11">
         <f>F40-G40</f>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2345,31 +2345,31 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="B41" s="9" t="n">
-        <v>8360</v>
+        <v>6704</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Хаджет Лебедівка</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>95968.3</v>
+        <v>6396000</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>95968.3</v>
+        <v>0</v>
       </c>
       <c r="H41" s="11">
         <f>F41-G41</f>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2388,14 +2388,14 @@
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>6704</v>
+        <v>5870</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>6396000</v>
+        <v>7800000</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2434,11 +2434,11 @@
         <v>46203</v>
       </c>
       <c r="B43" s="9" t="n">
-        <v>5910</v>
+        <v>8185</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -2448,11 +2448,11 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>10136835.8</v>
+        <v>63313.4</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2474,31 +2474,31 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>8185</v>
+        <v>4766</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>63313.4</v>
+        <v>120000</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2520,16 +2520,16 @@
         <v>46204</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>120000</v>
+        <v>10136835.8</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>0</v>
@@ -2692,11 +2692,11 @@
         <v>46211</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>8185</v>
+        <v>7002</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>63313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>0</v>
@@ -2732,28 +2732,28 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>6406</v>
+        <v>8185</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>218602</v>
+        <v>63313.4</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>0</v>
@@ -2775,19 +2775,19 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>46214</v>
+        <v>46212</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>5910</v>
+        <v>6406</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>15929313.4</v>
+        <v>218602</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>0</v>
@@ -2818,14 +2818,14 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46215</v>
+        <v>46225</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>7002</v>
+        <v>3456</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>126896.64</v>
+        <v>335974.68</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>0</v>
@@ -2864,11 +2864,11 @@
         <v>46225</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>3456</v>
+        <v>8008</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2878,14 +2878,14 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>335974.68</v>
+        <v>178088.4</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>0</v>
+        <v>178088.4</v>
       </c>
       <c r="H53" s="11">
         <f>F53-G53</f>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2904,14 +2904,14 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46225</v>
+        <v>46228</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>8008</v>
+        <v>5910</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>178088.4</v>
+        <v>15929313.4</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>178088.4</v>
+        <v>0</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3119,7 +3119,7 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="B59" s="9" t="n">
         <v>5910</v>
@@ -3205,19 +3205,19 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>46277</v>
+        <v>46282</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>4766</v>
+        <v>7894</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>4880000</v>
+        <v>737597.4</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>0</v>
@@ -3248,19 +3248,19 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>7894</v>
+        <v>4766</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>737597.4</v>
+        <v>4880000</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
@@ -3529,7 +3529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46189</v>
+        <v>46203</v>
       </c>
       <c r="B2" s="9" t="n">
         <v>5870</v>
@@ -3608,26 +3608,26 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46113</v>
+        <v>46202</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>7068</v>
+        <v>6704</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>5640128</v>
+        <v>6396000</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -3636,26 +3636,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46189</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7002</v>
+        <v>7068</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>573945</v>
+        <v>5640128</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -3663,26 +3663,82 @@
       </c>
     </row>
     <row r="5">
-      <c r="D5" s="3" t="inlineStr">
+      <c r="A5" s="8" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>7002</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>А Фора  SCP W 24PS V1</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Четвертий платіж</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>573945</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11">
+        <f>E5-F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>8185</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Фундамент Hytte House Development Славське</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>63313.4</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11">
+        <f>E6-F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E5" s="12">
-        <f>SUM(E2:E4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="12">
-        <f>SUM(F2:F4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="12">
-        <f>SUM(G2:G4)</f>
+      <c r="E7" s="12">
+        <f>SUM(E2:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>SUM(F2:F6)</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>SUM(G2:G6)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 30.06.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 01.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -2130,31 +2130,31 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>7002</v>
+        <v>8644</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Solars ГШ 1,7+надставки 3,5</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>573945</v>
+        <v>415900</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0</v>
+        <v>415900</v>
       </c>
       <c r="H36" s="11">
         <f>F36-G36</f>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2173,31 +2173,31 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>8644</v>
+        <v>5682</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Solars ГШ 1,7+надставки 3,5</t>
+          <t>А Сцена Корчин</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>415900</v>
+        <v>369984.96</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>415900</v>
+        <v>369984.96</v>
       </c>
       <c r="H37" s="11">
         <f>F37-G37</f>
@@ -2216,19 +2216,19 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>5682</v>
+        <v>7068</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>А Сцена Корчин</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>369984.96</v>
+        <v>0</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>369984.96</v>
+        <v>1153420</v>
       </c>
       <c r="H38" s="11">
         <f>F38-G38</f>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2262,28 +2262,28 @@
         <v>46197</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>7068</v>
+        <v>8360</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>Хаджет Лебедівка</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>0</v>
+        <v>95968.3</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1153420</v>
+        <v>95968.3</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2302,31 +2302,31 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>8360</v>
+        <v>6704</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Хаджет Лебедівка</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>95968.3</v>
+        <v>6396000</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>95968.3</v>
+        <v>0</v>
       </c>
       <c r="H40" s="11">
         <f>F40-G40</f>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2345,14 +2345,14 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B41" s="9" t="n">
-        <v>6704</v>
+        <v>5870</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>6396000</v>
+        <v>7800000</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>0</v>
@@ -2391,16 +2391,16 @@
         <v>46203</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>5870</v>
+        <v>8185</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>7800000</v>
+        <v>63313.4</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>0</v>
@@ -2431,31 +2431,31 @@
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B43" s="9" t="n">
-        <v>8185</v>
+        <v>4766</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>63313.4</v>
+        <v>120000</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H43" s="11">
         <f>F43-G43</f>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2477,16 +2477,16 @@
         <v>46204</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>120000</v>
+        <v>10136835.8</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2517,28 +2517,28 @@
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>5910</v>
+        <v>7244</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>10136835.8</v>
+        <v>132708.6</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>0</v>
@@ -2560,28 +2560,28 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>7244</v>
+        <v>8188</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F46" s="10" t="n">
-        <v>132708.6</v>
+        <v>73926</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>0</v>
@@ -2603,19 +2603,19 @@
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>8188</v>
+        <v>7002</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>73926</v>
+        <v>126896.64</v>
       </c>
       <c r="G47" s="10" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B48" s="9" t="n">
         <v>7002</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
@@ -2692,11 +2692,11 @@
         <v>46211</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>7002</v>
+        <v>8185</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>0</v>
@@ -2732,28 +2732,28 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>8185</v>
+        <v>6406</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>63313.4</v>
+        <v>218602</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>0</v>
@@ -2775,28 +2775,28 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>6406</v>
+        <v>3456</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>218602</v>
+        <v>335974.68</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>0</v>
@@ -2821,11 +2821,11 @@
         <v>46225</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>3456</v>
+        <v>8008</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -2835,14 +2835,14 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>335974.68</v>
+        <v>178088.4</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>0</v>
+        <v>178088.4</v>
       </c>
       <c r="H52" s="11">
         <f>F52-G52</f>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2861,14 +2861,14 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>46225</v>
+        <v>46228</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>8008</v>
+        <v>5910</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>178088.4</v>
+        <v>15929313.4</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>178088.4</v>
+        <v>0</v>
       </c>
       <c r="H53" s="11">
         <f>F53-G53</f>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2904,14 +2904,14 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -2921,11 +2921,11 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>15929313.4</v>
+        <v>737597.4</v>
       </c>
       <c r="G54" s="10" t="n">
         <v>0</v>
@@ -2947,14 +2947,14 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>7894</v>
+        <v>8008</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -2964,11 +2964,11 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>737597.4</v>
+        <v>178088.4</v>
       </c>
       <c r="G55" s="10" t="n">
         <v>0</v>
@@ -2990,14 +2990,14 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>8008</v>
+        <v>7894</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -3007,11 +3007,11 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>178088.4</v>
+        <v>185968</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46234</v>
+        <v>46245</v>
       </c>
       <c r="B57" s="9" t="n">
         <v>7894</v>
@@ -3050,11 +3050,11 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>185968</v>
+        <v>185967.99</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>0</v>
@@ -3070,20 +3070,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>7894</v>
+        <v>7002</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>185967.99</v>
+        <v>573945</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>0</v>
@@ -3529,7 +3529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3580,23 +3580,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5870</v>
+        <v>5910</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>7800000</v>
+        <v>10136835.8</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -3608,14 +3608,14 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6704</v>
+        <v>5870</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>6396000</v>
+        <v>7800000</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -3636,26 +3636,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46113</v>
+        <v>46202</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7068</v>
+        <v>6704</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5640128</v>
+        <v>6396000</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -3664,26 +3664,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46189</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>7002</v>
+        <v>7068</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>573945</v>
+        <v>5640128</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -3692,26 +3692,26 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>8185</v>
+        <v>4766</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>63313.4</v>
+        <v>120000</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G6" s="11">
         <f>E6-F6</f>
@@ -3719,26 +3719,54 @@
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="3" t="inlineStr">
+      <c r="A7" s="8" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>8185</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Фундамент Hytte House Development Славське</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>63313.4</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
+        <f>E7-F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E7" s="12">
-        <f>SUM(E2:E6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
-        <f>SUM(F2:F6)</f>
-        <v/>
-      </c>
-      <c r="G7" s="12">
-        <f>SUM(G2:G6)</f>
+      <c r="E8" s="12">
+        <f>SUM(E2:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="12">
+        <f>SUM(F2:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>SUM(G2:G7)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 01.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 07.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2388,31 +2388,31 @@
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>8185</v>
+        <v>4766</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>63313.4</v>
+        <v>20000</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2420,18 +2420,18 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="B43" s="9" t="n">
         <v>4766</v>
@@ -2448,14 +2448,14 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H43" s="11">
         <f>F43-G43</f>
@@ -2474,14 +2474,14 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>5910</v>
+        <v>8185</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
@@ -2491,11 +2491,11 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>10136835.8</v>
+        <v>63313.4</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
@@ -2517,28 +2517,28 @@
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>7244</v>
+        <v>8188</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>132708.6</v>
+        <v>73926</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>0</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2560,28 +2560,28 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>8188</v>
+        <v>5910</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F46" s="10" t="n">
-        <v>73926</v>
+        <v>8517966.4</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>0</v>
@@ -2603,14 +2603,14 @@
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>7002</v>
+        <v>8185</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2620,11 +2620,11 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="G47" s="10" t="n">
         <v>0</v>
@@ -2646,28 +2646,28 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>7002</v>
+        <v>6406</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
-        <v>126896.64</v>
+        <v>218602</v>
       </c>
       <c r="G48" s="10" t="n">
         <v>0</v>
@@ -2689,14 +2689,14 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>8185</v>
+        <v>7002</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2706,11 +2706,11 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>63313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>0</v>
@@ -2732,28 +2732,28 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46212</v>
+        <v>46217</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>6406</v>
+        <v>7002</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>218602</v>
+        <v>126896.64</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>15929313.4</v>
+        <v>17035932.8</v>
       </c>
       <c r="G53" s="10" t="n">
         <v>0</v>
@@ -2993,25 +2993,25 @@
         <v>46234</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>7894</v>
+        <v>7244</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>185968</v>
+        <v>132708.6</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46245</v>
+        <v>46234</v>
       </c>
       <c r="B57" s="9" t="n">
         <v>7894</v>
@@ -3050,11 +3050,11 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>185967.99</v>
+        <v>185968</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>0</v>
@@ -3070,20 +3070,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46249</v>
+        <v>46245</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>7002</v>
+        <v>7894</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>573945</v>
+        <v>185967.99</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>0</v>
@@ -3119,14 +3119,14 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46260</v>
+        <v>46249</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -3136,11 +3136,11 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>2896238.8</v>
+        <v>573945</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0</v>
@@ -3165,11 +3165,11 @@
         <v>46260</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>7002</v>
+        <v>5910</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -3179,11 +3179,11 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>573945</v>
+        <v>2896238.8</v>
       </c>
       <c r="G60" s="10" t="n">
         <v>0</v>
@@ -3205,14 +3205,14 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>7894</v>
+        <v>7002</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>737597.4</v>
+        <v>573945</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>0</v>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>4766</v>
+        <v>7894</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>4880000</v>
+        <v>737597.4</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
@@ -3290,26 +3290,69 @@
       </c>
     </row>
     <row r="63">
-      <c r="E63" s="3" t="inlineStr">
+      <c r="A63" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="n">
+        <v>4880000</v>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="11">
+        <f>F63-G63</f>
+        <v/>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F63" s="12">
-        <f>SUM(F2:F62)</f>
-        <v/>
-      </c>
-      <c r="G63" s="12">
-        <f>SUM(G2:G62)</f>
-        <v/>
-      </c>
-      <c r="H63" s="12">
-        <f>SUM(H2:H62)</f>
+      <c r="F64" s="12">
+        <f>SUM(F2:F63)</f>
+        <v/>
+      </c>
+      <c r="G64" s="12">
+        <f>SUM(G2:G63)</f>
+        <v/>
+      </c>
+      <c r="H64" s="12">
+        <f>SUM(H2:H63)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I62"/>
+  <autoFilter ref="A1:I63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3320,7 +3363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3496,25 +3539,48 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>жов 2026</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
+        <f>SUMIF('Графік надходжень'!J:J,"2026-10",'Графік надходжень'!F:F)</f>
+        <v/>
+      </c>
+      <c r="C8" s="11">
+        <f>SUMIF('Графік надходжень'!J:J,"2026-10",'Графік надходжень'!G:G)</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="13">
+        <f>IF(B8=0,0,C8/B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="B8" s="12">
-        <f>SUM(B2:B7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="12">
-        <f>SUM(C2:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="12">
-        <f>SUM(D2:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="14">
-        <f>IF(B8=0,0,C8/B8)</f>
+      <c r="B9" s="12">
+        <f>SUM(B2:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="12">
+        <f>SUM(C2:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="12">
+        <f>SUM(D2:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="14">
+        <f>IF(B9=0,0,C9/B9)</f>
         <v/>
       </c>
     </row>
@@ -3580,23 +3646,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5910</v>
+        <v>5870</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>10136835.8</v>
+        <v>7800000</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -3608,14 +3674,14 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>5870</v>
+        <v>6704</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -3624,7 +3690,7 @@
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>7800000</v>
+        <v>6396000</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -3636,26 +3702,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46202</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6704</v>
+        <v>7068</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>6396000</v>
+        <v>5640128</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -3664,26 +3730,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46113</v>
+        <v>46206</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>7068</v>
+        <v>4766</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>5640128</v>
+        <v>100000</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -3692,26 +3758,26 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>4766</v>
+        <v>8188</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>120000</v>
+        <v>73926</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="G6" s="11">
         <f>E6-F6</f>
@@ -3720,7 +3786,7 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>8185</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 07.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 09.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -2477,16 +2477,16 @@
         <v>46209</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>8185</v>
+        <v>8188</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>63313.4</v>
+        <v>73926</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
@@ -2517,14 +2517,14 @@
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>8188</v>
+        <v>6406</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>73926</v>
+        <v>218602</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>0</v>
@@ -2560,7 +2560,7 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B46" s="9" t="n">
         <v>5910</v>
@@ -2603,14 +2603,14 @@
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>8185</v>
+        <v>7002</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2620,11 +2620,11 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>63313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="G47" s="10" t="n">
         <v>0</v>
@@ -2646,19 +2646,19 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>6406</v>
+        <v>8185</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="F48" s="10" t="n">
-        <v>218602</v>
+        <v>63313.4</v>
       </c>
       <c r="G48" s="10" t="n">
         <v>0</v>
@@ -2692,11 +2692,11 @@
         <v>46213</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>7002</v>
+        <v>8185</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2706,11 +2706,11 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>0</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46217</v>
+        <v>46214</v>
       </c>
       <c r="B50" s="9" t="n">
         <v>7002</v>
@@ -3291,7 +3291,7 @@
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>46307</v>
+        <v>46287</v>
       </c>
       <c r="B63" s="9" t="n">
         <v>4766</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3539,48 +3539,25 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>жов 2026</t>
-        </is>
-      </c>
-      <c r="B8" s="11">
-        <f>SUMIF('Графік надходжень'!J:J,"2026-10",'Графік надходжень'!F:F)</f>
-        <v/>
-      </c>
-      <c r="C8" s="11">
-        <f>SUMIF('Графік надходжень'!J:J,"2026-10",'Графік надходжень'!G:G)</f>
-        <v/>
-      </c>
-      <c r="D8" s="11">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="13">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="B8" s="12">
+        <f>SUM(B2:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="12">
+        <f>SUM(C2:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="12">
+        <f>SUM(D2:D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="14">
         <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Разом</t>
-        </is>
-      </c>
-      <c r="B9" s="12">
-        <f>SUM(B2:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="12">
-        <f>SUM(C2:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="12">
-        <f>SUM(D2:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>IF(B9=0,0,C9/B9)</f>
         <v/>
       </c>
     </row>
@@ -3730,14 +3707,14 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46206</v>
+        <v>46212</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>4766</v>
+        <v>6406</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -3746,7 +3723,7 @@
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>100000</v>
+        <v>218602</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0</v>
@@ -3758,14 +3735,14 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>8188</v>
+        <v>4766</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -3774,7 +3751,7 @@
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>73926</v>
+        <v>100000</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -3789,11 +3766,11 @@
         <v>46209</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>8185</v>
+        <v>8188</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -3802,7 +3779,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>63313.4</v>
+        <v>73926</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 09.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 10.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2993,28 +2993,28 @@
         <v>46234</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>7244</v>
+        <v>7068</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>132708.6</v>
+        <v>0</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>0</v>
+        <v>2794670</v>
       </c>
       <c r="H56" s="11">
         <f>F56-G56</f>
@@ -3036,25 +3036,25 @@
         <v>46234</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>7894</v>
+        <v>7244</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>185968</v>
+        <v>132708.6</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46245</v>
+        <v>46234</v>
       </c>
       <c r="B58" s="9" t="n">
         <v>7894</v>
@@ -3093,11 +3093,11 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>185967.99</v>
+        <v>185968</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>0</v>
@@ -3113,20 +3113,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46249</v>
+        <v>46245</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>7002</v>
+        <v>7894</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -3136,11 +3136,11 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>573945</v>
+        <v>185967.99</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0</v>
@@ -3162,14 +3162,14 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46260</v>
+        <v>46249</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -3179,11 +3179,11 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>2896238.8</v>
+        <v>573945</v>
       </c>
       <c r="G60" s="10" t="n">
         <v>0</v>
@@ -3208,11 +3208,11 @@
         <v>46260</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>7002</v>
+        <v>5910</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
@@ -3222,11 +3222,11 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>573945</v>
+        <v>2896238.8</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>7894</v>
+        <v>7002</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>737597.4</v>
+        <v>573945</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
@@ -3285,25 +3285,25 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>4766</v>
+        <v>7894</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>4880000</v>
+        <v>737597.4</v>
       </c>
       <c r="G63" s="10" t="n">
         <v>0</v>
@@ -3333,26 +3333,69 @@
       </c>
     </row>
     <row r="64">
-      <c r="E64" s="3" t="inlineStr">
+      <c r="A64" s="8" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>4880000</v>
+      </c>
+      <c r="G64" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="11">
+        <f>F64-G64</f>
+        <v/>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F64" s="12">
-        <f>SUM(F2:F63)</f>
-        <v/>
-      </c>
-      <c r="G64" s="12">
-        <f>SUM(G2:G63)</f>
-        <v/>
-      </c>
-      <c r="H64" s="12">
-        <f>SUM(H2:H63)</f>
+      <c r="F65" s="12">
+        <f>SUM(F2:F64)</f>
+        <v/>
+      </c>
+      <c r="G65" s="12">
+        <f>SUM(G2:G64)</f>
+        <v/>
+      </c>
+      <c r="H65" s="12">
+        <f>SUM(H2:H64)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I63"/>
+  <autoFilter ref="A1:I64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3572,7 +3615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3623,23 +3666,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46203</v>
+        <v>46213</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5870</v>
+        <v>5910</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>7800000</v>
+        <v>8517966.4</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -3651,14 +3694,14 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6704</v>
+        <v>5870</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -3667,7 +3710,7 @@
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>6396000</v>
+        <v>7800000</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -3679,26 +3722,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46113</v>
+        <v>46202</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7068</v>
+        <v>6704</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5640128</v>
+        <v>6396000</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -3707,26 +3750,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46212</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>6406</v>
+        <v>7068</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>218602</v>
+        <v>5640128</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -3735,14 +3778,14 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46206</v>
+        <v>46212</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>4766</v>
+        <v>6406</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -3751,7 +3794,7 @@
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>100000</v>
+        <v>218602</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -3763,14 +3806,14 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>8188</v>
+        <v>7002</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -3779,7 +3822,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>73926</v>
+        <v>126896.64</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0</v>
@@ -3790,26 +3833,138 @@
       </c>
     </row>
     <row r="8">
-      <c r="D8" s="3" t="inlineStr">
+      <c r="A8" s="8" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <f>E8-F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>8188</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Фундамент Ужгород Стефанія</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>73926</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <f>E9-F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>8185</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Фундамент Hytte House Development Славське</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>63313.4</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <f>E10-F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>8185</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Фундамент Hytte House Development Славське</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>63313.4</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <f>E11-F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E8" s="12">
-        <f>SUM(E2:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
-        <f>SUM(F2:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="12">
-        <f>SUM(G2:G7)</f>
+      <c r="E12" s="12">
+        <f>SUM(E2:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>SUM(F2:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="12">
+        <f>SUM(G2:G11)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 10.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 13.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1399,31 +1399,31 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>46167</v>
+        <v>46165</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>7508</v>
+        <v>6704</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>1245999.94</v>
+        <v>4524000</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>1245999.94</v>
+        <v>0</v>
       </c>
       <c r="H19" s="11">
         <f>F19-G19</f>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>7508</v>
@@ -1459,14 +1459,14 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>751000.0600000001</v>
+        <v>1245999.94</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>751000.0600000001</v>
+        <v>1245999.94</v>
       </c>
       <c r="H20" s="11">
         <f>F20-G20</f>
@@ -1485,31 +1485,31 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>6842</v>
+        <v>7508</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>3308968</v>
+        <v>751000.0600000001</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>3308968</v>
+        <v>751000.0600000001</v>
       </c>
       <c r="H21" s="11">
         <f>F21-G21</f>
@@ -1531,16 +1531,16 @@
         <v>46169</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>7960</v>
+        <v>6842</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Сірокко Sirocco вітрова ел ст Львів</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>99610.8</v>
+        <v>3308968</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>99610.8</v>
+        <v>3308968</v>
       </c>
       <c r="H22" s="11">
         <f>F22-G22</f>
@@ -1574,16 +1574,16 @@
         <v>46169</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>8454</v>
+        <v>7960</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Олександр каркасний Верховина</t>
+          <t>Сірокко Sirocco вітрова ел ст Львів</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>103606.2</v>
+        <v>99610.8</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>103606.2</v>
+        <v>99610.8</v>
       </c>
       <c r="H23" s="11">
         <f>F23-G23</f>
@@ -1614,19 +1614,19 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>8188</v>
+        <v>8454</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Олександр каркасний Верховина</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>206200</v>
+        <v>103606.2</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>206200</v>
+        <v>103606.2</v>
       </c>
       <c r="H24" s="11">
         <f>F24-G24</f>
@@ -1660,28 +1660,28 @@
         <v>46170</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>8454</v>
+        <v>8188</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Олександр каркасний Верховина</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>69666</v>
+        <v>206200</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>69666</v>
+        <v>206200</v>
       </c>
       <c r="H25" s="11">
         <f>F25-G25</f>
@@ -1703,11 +1703,11 @@
         <v>46170</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>8544</v>
+        <v>8454</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Isolar фланець Хмельницький</t>
+          <t>Олександр каркасний Верховина</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>261990</v>
+        <v>69666</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>261990</v>
+        <v>69666</v>
       </c>
       <c r="H26" s="11">
         <f>F26-G26</f>
@@ -1743,19 +1743,19 @@
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>5682</v>
+        <v>8544</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>А Сцена Корчин</t>
+          <t>Isolar фланець Хмельницький</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>87150</v>
+        <v>261990</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>87150</v>
+        <v>261990</v>
       </c>
       <c r="H27" s="11">
         <f>F27-G27</f>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -1789,16 +1789,16 @@
         <v>46175</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>8185</v>
+        <v>5682</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>А Сцена Корчин</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>168024</v>
+        <v>87150</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>168024</v>
+        <v>87150</v>
       </c>
       <c r="H28" s="11">
         <f>F28-G28</f>
@@ -1829,14 +1829,14 @@
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>7894</v>
+        <v>8185</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1487743.97</v>
+        <v>168024</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>1487743.97</v>
+        <v>168024</v>
       </c>
       <c r="H29" s="11">
         <f>F29-G29</f>
@@ -1872,14 +1872,14 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>8544</v>
+        <v>7894</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Isolar фланець Хмельницький</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1889,14 +1889,14 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>7990.8</v>
+        <v>1487743.97</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>7990.8</v>
+        <v>1487743.97</v>
       </c>
       <c r="H30" s="11">
         <f>F30-G30</f>
@@ -1915,19 +1915,19 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>8140</v>
+        <v>8544</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>В Газинвестпроект фундамент Киев</t>
+          <t>Isolar фланець Хмельницький</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>86041.2</v>
+        <v>7990.8</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>86041.2</v>
+        <v>7990.8</v>
       </c>
       <c r="H31" s="11">
         <f>F31-G31</f>
@@ -1958,19 +1958,19 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>3456</v>
+        <v>8140</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>В Газинвестпроект фундамент Киев</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>783940.92</v>
+        <v>86041.2</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>783940.92</v>
+        <v>86041.2</v>
       </c>
       <c r="H32" s="11">
         <f>F32-G32</f>
@@ -2004,11 +2004,11 @@
         <v>46184</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>8360</v>
+        <v>3456</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Хаджет Лебедівка</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>95968.3</v>
+        <v>783940.92</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>95968.3</v>
+        <v>783940.92</v>
       </c>
       <c r="H33" s="11">
         <f>F33-G33</f>
@@ -2044,31 +2044,31 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>7474</v>
+        <v>8360</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>А Головне управління Національної поліції в Одеській області  SCP  15PS</t>
+          <t>Хаджет Лебедівка</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F34" s="10" t="n">
-        <v>1749999</v>
+        <v>95968.3</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>1749999</v>
+        <v>95968.3</v>
       </c>
       <c r="H34" s="11">
         <f>F34-G34</f>
@@ -2087,31 +2087,31 @@
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>6406</v>
+        <v>7474</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А Головне управління Національної поліції в Одеській області  SCP  15PS</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>154980</v>
+        <v>1749999</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>154980</v>
+        <v>1749999</v>
       </c>
       <c r="H35" s="11">
         <f>F35-G35</f>
@@ -2130,14 +2130,14 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>8644</v>
+        <v>6406</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Solars ГШ 1,7+надставки 3,5</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>415900</v>
+        <v>154980</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>415900</v>
+        <v>154980</v>
       </c>
       <c r="H36" s="11">
         <f>F36-G36</f>
@@ -2173,31 +2173,31 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>5682</v>
+        <v>8644</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>А Сцена Корчин</t>
+          <t>Solars ГШ 1,7+надставки 3,5</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>369984.96</v>
+        <v>415900</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>369984.96</v>
+        <v>415900</v>
       </c>
       <c r="H37" s="11">
         <f>F37-G37</f>
@@ -2216,19 +2216,19 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>7068</v>
+        <v>5682</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>А Сцена Корчин</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>0</v>
+        <v>369984.96</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>1153420</v>
+        <v>369984.96</v>
       </c>
       <c r="H38" s="11">
         <f>F38-G38</f>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2262,28 +2262,28 @@
         <v>46197</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>8360</v>
+        <v>7068</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Хаджет Лебедівка</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>95968.3</v>
+        <v>0</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>95968.3</v>
+        <v>1153420</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2302,31 +2302,31 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>46202</v>
+        <v>46197</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>6704</v>
+        <v>8360</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>Хаджет Лебедівка</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>6396000</v>
+        <v>95968.3</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>0</v>
+        <v>95968.3</v>
       </c>
       <c r="H40" s="11">
         <f>F40-G40</f>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2345,14 +2345,14 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="B41" s="9" t="n">
-        <v>5870</v>
+        <v>6704</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>7800000</v>
+        <v>1872000</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>0</v>
+        <v>1872000</v>
       </c>
       <c r="H41" s="11">
         <f>F41-G41</f>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2388,31 +2388,31 @@
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>4766</v>
+        <v>5870</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>20000</v>
+        <v>7800000</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2420,18 +2420,18 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="B43" s="9" t="n">
         <v>4766</v>
@@ -2448,14 +2448,14 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H43" s="11">
         <f>F43-G43</f>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2474,19 +2474,19 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>8188</v>
+        <v>4766</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>73926</v>
+        <v>100000</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
@@ -2517,14 +2517,14 @@
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>6406</v>
+        <v>8188</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>218602</v>
+        <v>73926</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>0</v>
@@ -2560,28 +2560,28 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>5910</v>
+        <v>6406</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F46" s="10" t="n">
-        <v>8517966.4</v>
+        <v>218602</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>0</v>
@@ -2606,11 +2606,11 @@
         <v>46213</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>7002</v>
+        <v>5910</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2620,11 +2620,11 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>126896.64</v>
+        <v>8517966.4</v>
       </c>
       <c r="G47" s="10" t="n">
         <v>0</v>
@@ -2649,11 +2649,11 @@
         <v>46213</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>8185</v>
+        <v>7002</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="F48" s="10" t="n">
-        <v>63313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="G48" s="10" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
@@ -2732,14 +2732,14 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46214</v>
+        <v>46213</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>7002</v>
+        <v>8185</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>0</v>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2775,14 +2775,14 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>46225</v>
+        <v>46214</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>3456</v>
+        <v>7002</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>335974.68</v>
+        <v>126896.64</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2821,11 +2821,11 @@
         <v>46225</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>8008</v>
+        <v>3456</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -2835,14 +2835,14 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>178088.4</v>
+        <v>335974.68</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>178088.4</v>
+        <v>0</v>
       </c>
       <c r="H52" s="11">
         <f>F52-G52</f>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2861,14 +2861,14 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>5910</v>
+        <v>8008</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>17035932.8</v>
+        <v>178088.4</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>0</v>
+        <v>178088.4</v>
       </c>
       <c r="H53" s="11">
         <f>F53-G53</f>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2904,14 +2904,14 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46231</v>
+        <v>46228</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -2921,11 +2921,11 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>737597.4</v>
+        <v>17035932.8</v>
       </c>
       <c r="G54" s="10" t="n">
         <v>0</v>
@@ -2947,14 +2947,14 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>8008</v>
+        <v>7894</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -2964,11 +2964,11 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>178088.4</v>
+        <v>737597.4</v>
       </c>
       <c r="G55" s="10" t="n">
         <v>0</v>
@@ -2990,19 +2990,19 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>7068</v>
+        <v>8008</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="F56" s="10" t="n">
+        <v>178088.4</v>
+      </c>
+      <c r="G56" s="10" t="n">
         <v>0</v>
-      </c>
-      <c r="G56" s="10" t="n">
-        <v>2794670</v>
       </c>
       <c r="H56" s="11">
         <f>F56-G56</f>
@@ -3036,28 +3036,28 @@
         <v>46234</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>7244</v>
+        <v>7068</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>132708.6</v>
+        <v>0</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>0</v>
+        <v>2794670</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3079,25 +3079,25 @@
         <v>46234</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>7894</v>
+        <v>7244</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>185968</v>
+        <v>132708.6</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46245</v>
+        <v>46234</v>
       </c>
       <c r="B59" s="9" t="n">
         <v>7894</v>
@@ -3136,11 +3136,11 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>185967.99</v>
+        <v>185968</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0</v>
@@ -3156,20 +3156,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46249</v>
+        <v>46245</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>7002</v>
+        <v>7894</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -3179,11 +3179,11 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>573945</v>
+        <v>185967.99</v>
       </c>
       <c r="G60" s="10" t="n">
         <v>0</v>
@@ -3205,14 +3205,14 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>46260</v>
+        <v>46249</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
@@ -3222,11 +3222,11 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>2896238.8</v>
+        <v>573945</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>0</v>
@@ -3251,11 +3251,11 @@
         <v>46260</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>7002</v>
+        <v>5910</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -3265,11 +3265,11 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>573945</v>
+        <v>2896238.8</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
@@ -3291,14 +3291,14 @@
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>7894</v>
+        <v>7002</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>737597.4</v>
+        <v>573945</v>
       </c>
       <c r="G63" s="10" t="n">
         <v>0</v>
@@ -3328,25 +3328,25 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>4766</v>
+        <v>7894</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4880000</v>
+        <v>737597.4</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>0</v>
@@ -3376,26 +3376,69 @@
       </c>
     </row>
     <row r="65">
-      <c r="E65" s="3" t="inlineStr">
+      <c r="A65" s="8" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n">
+        <v>4880000</v>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="11">
+        <f>F65-G65</f>
+        <v/>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F65" s="12">
-        <f>SUM(F2:F64)</f>
-        <v/>
-      </c>
-      <c r="G65" s="12">
-        <f>SUM(G2:G64)</f>
-        <v/>
-      </c>
-      <c r="H65" s="12">
-        <f>SUM(H2:H64)</f>
+      <c r="F66" s="12">
+        <f>SUM(F2:F65)</f>
+        <v/>
+      </c>
+      <c r="G66" s="12">
+        <f>SUM(G2:G65)</f>
+        <v/>
+      </c>
+      <c r="H66" s="12">
+        <f>SUM(H2:H65)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I64"/>
+  <autoFilter ref="A1:I65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3615,7 +3658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3722,7 +3765,7 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46202</v>
+        <v>46165</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>6704</v>
@@ -3734,11 +3777,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>6396000</v>
+        <v>4524000</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>0</v>
@@ -3834,23 +3877,23 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46206</v>
+        <v>46214</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>100000</v>
+        <v>126896.64</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>0</v>
@@ -3862,14 +3905,14 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>8188</v>
+        <v>4766</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -3878,7 +3921,7 @@
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>73926</v>
+        <v>100000</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>0</v>
@@ -3890,14 +3933,14 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46213</v>
+        <v>46209</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>8185</v>
+        <v>8188</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -3906,7 +3949,7 @@
         </is>
       </c>
       <c r="E10" s="11" t="n">
-        <v>63313.4</v>
+        <v>73926</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>0</v>
@@ -3930,7 +3973,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -3945,26 +3988,54 @@
       </c>
     </row>
     <row r="12">
-      <c r="D12" s="3" t="inlineStr">
+      <c r="A12" s="8" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>8185</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Фундамент Hytte House Development Славське</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>63313.4</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <f>E12-F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E12" s="12">
-        <f>SUM(E2:E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="12">
-        <f>SUM(F2:F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="12">
-        <f>SUM(G2:G11)</f>
+      <c r="E13" s="12">
+        <f>SUM(E2:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="12">
+        <f>SUM(F2:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>SUM(G2:G12)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2474,19 +2474,19 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>4766</v>
+        <v>8188</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>100000</v>
+        <v>73926</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
@@ -2520,28 +2520,28 @@
         <v>46209</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>8188</v>
+        <v>8878</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>73926</v>
+        <v>410320</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>0</v>
+        <v>410320</v>
       </c>
       <c r="H45" s="11">
         <f>F45-G45</f>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2818,28 +2818,28 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46225</v>
+        <v>46217</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>3456</v>
+        <v>4766</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>335974.68</v>
+        <v>100000</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>0</v>
@@ -2864,11 +2864,11 @@
         <v>46225</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>8008</v>
+        <v>3456</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2878,14 +2878,14 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>178088.4</v>
+        <v>335974.68</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>178088.4</v>
+        <v>0</v>
       </c>
       <c r="H53" s="11">
         <f>F53-G53</f>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2904,14 +2904,14 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>5910</v>
+        <v>8008</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>17035932.8</v>
+        <v>178088.4</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>0</v>
+        <v>178088.4</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2947,14 +2947,14 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>46231</v>
+        <v>46228</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -2964,11 +2964,11 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>737597.4</v>
+        <v>17035932.8</v>
       </c>
       <c r="G55" s="10" t="n">
         <v>0</v>
@@ -2990,14 +2990,14 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>8008</v>
+        <v>7894</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -3007,11 +3007,11 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>178088.4</v>
+        <v>737597.4</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>7068</v>
+        <v>8008</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
+        <v>178088.4</v>
+      </c>
+      <c r="G57" s="10" t="n">
         <v>0</v>
-      </c>
-      <c r="G57" s="10" t="n">
-        <v>2794670</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3079,28 +3079,28 @@
         <v>46234</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>7244</v>
+        <v>7068</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>132708.6</v>
+        <v>0</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>0</v>
+        <v>2794670</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3122,25 +3122,25 @@
         <v>46234</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>7894</v>
+        <v>7244</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>185968</v>
+        <v>132708.6</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46245</v>
+        <v>46234</v>
       </c>
       <c r="B60" s="9" t="n">
         <v>7894</v>
@@ -3179,11 +3179,11 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>185967.99</v>
+        <v>185968</v>
       </c>
       <c r="G60" s="10" t="n">
         <v>0</v>
@@ -3199,34 +3199,34 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>46249</v>
+        <v>46237</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>7002</v>
+        <v>8878</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>573945</v>
+        <v>12823</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46260</v>
+        <v>46245</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>2896238.8</v>
+        <v>185967.99</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>46260</v>
+        <v>46249</v>
       </c>
       <c r="B63" s="9" t="n">
         <v>7002</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
@@ -3334,14 +3334,14 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -3351,11 +3351,11 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>737597.4</v>
+        <v>2896238.8</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>0</v>
@@ -3371,25 +3371,25 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46287</v>
+        <v>46260</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>4880000</v>
+        <v>573945</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3414,31 +3414,117 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B66" s="9" t="n">
+        <v>7894</v>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>А Фора  SCP  32PS</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>737597.4</v>
+      </c>
+      <c r="G66" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="11">
+        <f>F66-G66</f>
+        <v/>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="E66" s="3" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="8" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="n">
+        <v>4880000</v>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="11">
+        <f>F67-G67</f>
+        <v/>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F66" s="12">
-        <f>SUM(F2:F65)</f>
-        <v/>
-      </c>
-      <c r="G66" s="12">
-        <f>SUM(G2:G65)</f>
-        <v/>
-      </c>
-      <c r="H66" s="12">
-        <f>SUM(H2:H65)</f>
+      <c r="F68" s="12">
+        <f>SUM(F2:F67)</f>
+        <v/>
+      </c>
+      <c r="G68" s="12">
+        <f>SUM(G2:G67)</f>
+        <v/>
+      </c>
+      <c r="H68" s="12">
+        <f>SUM(H2:H67)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I65"/>
+  <autoFilter ref="A1:I67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3658,7 +3744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3905,14 +3991,14 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>4766</v>
+        <v>8188</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -3921,7 +4007,7 @@
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>100000</v>
+        <v>73926</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>0</v>
@@ -3933,14 +4019,14 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>8188</v>
+        <v>8185</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -3949,7 +4035,7 @@
         </is>
       </c>
       <c r="E10" s="11" t="n">
-        <v>73926</v>
+        <v>63313.4</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>0</v>
@@ -3973,7 +4059,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -3988,54 +4074,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>8185</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Фундамент Hytte House Development Славське</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>63313.4</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="11">
-        <f>E12-F12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E13" s="12">
-        <f>SUM(E2:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
-        <f>SUM(F2:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="12">
-        <f>SUM(G2:G12)</f>
+      <c r="E12" s="12">
+        <f>SUM(E2:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>SUM(F2:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="12">
+        <f>SUM(G2:G11)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2818,31 +2818,31 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>4766</v>
+        <v>8496</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Greensource  SGM  110MWp</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж (€8 800)</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>100000</v>
+        <v>447568</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>0</v>
+        <v>447568</v>
       </c>
       <c r="H52" s="11">
         <f>F52-G52</f>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2861,28 +2861,28 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>46225</v>
+        <v>46217</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>3456</v>
+        <v>4766</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>335974.68</v>
+        <v>100000</v>
       </c>
       <c r="G53" s="10" t="n">
         <v>0</v>
@@ -2907,11 +2907,11 @@
         <v>46225</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>8008</v>
+        <v>3456</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -2921,14 +2921,14 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>178088.4</v>
+        <v>335974.68</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>178088.4</v>
+        <v>0</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2947,14 +2947,14 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>5910</v>
+        <v>8008</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>17035932.8</v>
+        <v>178088.4</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>0</v>
+        <v>178088.4</v>
       </c>
       <c r="H55" s="11">
         <f>F55-G55</f>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2990,14 +2990,14 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46231</v>
+        <v>46228</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -3007,11 +3007,11 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>737597.4</v>
+        <v>17035932.8</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>0</v>
@@ -3033,14 +3033,14 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>8008</v>
+        <v>7894</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -3050,11 +3050,11 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>178088.4</v>
+        <v>737597.4</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>0</v>
@@ -3076,19 +3076,19 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>7068</v>
+        <v>8008</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F58" s="10" t="n">
+        <v>178088.4</v>
+      </c>
+      <c r="G58" s="10" t="n">
         <v>0</v>
-      </c>
-      <c r="G58" s="10" t="n">
-        <v>2794670</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3122,28 +3122,28 @@
         <v>46234</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>7244</v>
+        <v>7068</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>132708.6</v>
+        <v>0</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>0</v>
+        <v>2794670</v>
       </c>
       <c r="H59" s="11">
         <f>F59-G59</f>
@@ -3165,25 +3165,25 @@
         <v>46234</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>7894</v>
+        <v>7244</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>185968</v>
+        <v>132708.6</v>
       </c>
       <c r="G60" s="10" t="n">
         <v>0</v>
@@ -3205,28 +3205,28 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>8878</v>
+        <v>7894</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>12823</v>
+        <v>185968</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>0</v>
@@ -3242,34 +3242,34 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>7894</v>
+        <v>8878</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>185967.99</v>
+        <v>12823</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
@@ -3291,14 +3291,14 @@
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>46249</v>
+        <v>46245</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>7002</v>
+        <v>7894</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -3308,11 +3308,11 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>573945</v>
+        <v>185967.99</v>
       </c>
       <c r="G63" s="10" t="n">
         <v>0</v>
@@ -3334,14 +3334,14 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46260</v>
+        <v>46249</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -3351,11 +3351,11 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>2896238.8</v>
+        <v>573945</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>0</v>
@@ -3380,11 +3380,11 @@
         <v>46260</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>7002</v>
+        <v>5910</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -3394,11 +3394,11 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>573945</v>
+        <v>2896238.8</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3420,14 +3420,14 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>7894</v>
+        <v>7002</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>737597.4</v>
+        <v>573945</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3457,25 +3457,25 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>4766</v>
+        <v>7894</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>4880000</v>
+        <v>737597.4</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -3505,26 +3505,69 @@
       </c>
     </row>
     <row r="68">
-      <c r="E68" s="3" t="inlineStr">
+      <c r="A68" s="8" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>4880000</v>
+      </c>
+      <c r="G68" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="11">
+        <f>F68-G68</f>
+        <v/>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F68" s="12">
-        <f>SUM(F2:F67)</f>
-        <v/>
-      </c>
-      <c r="G68" s="12">
-        <f>SUM(G2:G67)</f>
-        <v/>
-      </c>
-      <c r="H68" s="12">
-        <f>SUM(H2:H67)</f>
+      <c r="F69" s="12">
+        <f>SUM(F2:F68)</f>
+        <v/>
+      </c>
+      <c r="G69" s="12">
+        <f>SUM(G2:G68)</f>
+        <v/>
+      </c>
+      <c r="H69" s="12">
+        <f>SUM(H2:H68)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I67"/>
+  <autoFilter ref="A1:I68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,6 +133,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -599,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -612,6 +613,7 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="9" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -665,6 +667,11 @@
           <t>YM</t>
         </is>
       </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>У валюті</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
@@ -708,6 +715,7 @@
           <t>2026-04</t>
         </is>
       </c>
+      <c r="K2" s="12" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
@@ -751,6 +759,7 @@
           <t>2026-04</t>
         </is>
       </c>
+      <c r="K3" s="12" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
@@ -794,6 +803,7 @@
           <t>2026-04</t>
         </is>
       </c>
+      <c r="K4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -837,6 +847,7 @@
           <t>2026-04</t>
         </is>
       </c>
+      <c r="K5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -880,6 +891,7 @@
           <t>2026-04</t>
         </is>
       </c>
+      <c r="K6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -923,6 +935,7 @@
           <t>2026-04</t>
         </is>
       </c>
+      <c r="K7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -966,6 +979,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -1009,6 +1023,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -1052,6 +1067,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -1095,6 +1111,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -1138,6 +1155,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -1181,6 +1199,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -1224,6 +1243,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
@@ -1267,6 +1287,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -1310,6 +1331,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
@@ -1353,6 +1375,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -1396,6 +1419,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -1439,6 +1463,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
@@ -1482,6 +1507,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
@@ -1525,6 +1551,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -1568,6 +1595,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
@@ -1611,6 +1639,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
@@ -1654,6 +1683,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
@@ -1697,6 +1727,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
@@ -1740,6 +1771,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
@@ -1783,6 +1815,7 @@
           <t>2026-05</t>
         </is>
       </c>
+      <c r="K27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
@@ -1826,6 +1859,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
@@ -1869,6 +1903,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
@@ -1912,6 +1947,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
@@ -1955,6 +1991,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
@@ -1998,6 +2035,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
@@ -2041,6 +2079,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
@@ -2084,6 +2123,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
@@ -2127,6 +2167,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
@@ -2170,6 +2211,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
@@ -2213,6 +2255,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K37" s="12" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
@@ -2256,6 +2299,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K38" s="12" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
@@ -2299,6 +2343,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K39" s="12" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
@@ -2342,6 +2387,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
@@ -2385,6 +2431,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
@@ -2428,6 +2475,7 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="K42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
@@ -2471,6 +2519,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
@@ -2514,6 +2563,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
@@ -2557,6 +2607,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
@@ -2600,6 +2651,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
@@ -2643,6 +2695,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
@@ -2686,6 +2739,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
@@ -2729,6 +2783,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
@@ -2772,6 +2827,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K50" s="12" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
@@ -2815,6 +2871,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K51" s="12" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
@@ -2835,7 +2892,7 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж (€8 800)</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
@@ -2856,6 +2913,11 @@
       <c r="J52" t="inlineStr">
         <is>
           <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>€8 800</t>
         </is>
       </c>
     </row>
@@ -2901,6 +2963,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
@@ -2944,6 +3007,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K54" s="12" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
@@ -2987,6 +3051,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K55" s="12" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
@@ -3030,6 +3095,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
@@ -3073,6 +3139,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K57" s="12" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
@@ -3116,6 +3183,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K58" s="12" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
@@ -3159,6 +3227,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K59" s="12" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
@@ -3202,6 +3271,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K60" s="12" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
@@ -3245,6 +3315,7 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K61" s="12" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
@@ -3288,6 +3359,7 @@
           <t>2026-08</t>
         </is>
       </c>
+      <c r="K62" s="12" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
@@ -3331,6 +3403,7 @@
           <t>2026-08</t>
         </is>
       </c>
+      <c r="K63" s="12" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
@@ -3374,6 +3447,7 @@
           <t>2026-08</t>
         </is>
       </c>
+      <c r="K64" s="12" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
@@ -3417,6 +3491,7 @@
           <t>2026-08</t>
         </is>
       </c>
+      <c r="K65" s="12" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
@@ -3460,6 +3535,7 @@
           <t>2026-08</t>
         </is>
       </c>
+      <c r="K66" s="12" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
@@ -3503,6 +3579,7 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="K67" s="12" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
@@ -3546,6 +3623,7 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="K68" s="12" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="E69" s="3" t="inlineStr">
@@ -3553,15 +3631,15 @@
           <t>Разом</t>
         </is>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="13">
         <f>SUM(F2:F68)</f>
         <v/>
       </c>
-      <c r="G69" s="12">
+      <c r="G69" s="13">
         <f>SUM(G2:G68)</f>
         <v/>
       </c>
-      <c r="H69" s="12">
+      <c r="H69" s="13">
         <f>SUM(H2:H68)</f>
         <v/>
       </c>
@@ -3633,7 +3711,7 @@
         <f>B2-C2</f>
         <v/>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="14">
         <f>IF(B2=0,0,C2/B2)</f>
         <v/>
       </c>
@@ -3656,7 +3734,7 @@
         <f>B3-C3</f>
         <v/>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="14">
         <f>IF(B3=0,0,C3/B3)</f>
         <v/>
       </c>
@@ -3679,7 +3757,7 @@
         <f>B4-C4</f>
         <v/>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="14">
         <f>IF(B4=0,0,C4/B4)</f>
         <v/>
       </c>
@@ -3702,7 +3780,7 @@
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="14">
         <f>IF(B5=0,0,C5/B5)</f>
         <v/>
       </c>
@@ -3725,7 +3803,7 @@
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <f>IF(B6=0,0,C6/B6)</f>
         <v/>
       </c>
@@ -3748,7 +3826,7 @@
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="14">
         <f>IF(B7=0,0,C7/B7)</f>
         <v/>
       </c>
@@ -3759,19 +3837,19 @@
           <t>Разом</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <f>SUM(B2:B7)</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>SUM(C2:C7)</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>SUM(D2:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="15">
         <f>IF(B8=0,0,C8/B8)</f>
         <v/>
       </c>
@@ -4122,15 +4200,15 @@
           <t>Разом</t>
         </is>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="13">
         <f>SUM(E2:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <f>SUM(F2:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="13">
         <f>SUM(G2:G11)</f>
         <v/>
       </c>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 13.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 15.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -2526,28 +2526,28 @@
         <v>46209</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>8188</v>
+        <v>8878</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>73926</v>
+        <v>410320</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>0</v>
+        <v>410320</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2567,31 +2567,31 @@
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>8878</v>
+        <v>6406</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>410320</v>
+        <v>218602</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>410320</v>
+        <v>0</v>
       </c>
       <c r="H45" s="11">
         <f>F45-G45</f>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2611,14 +2611,14 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>6406</v>
+        <v>8188</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="F46" s="10" t="n">
-        <v>218602</v>
+        <v>73926</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>0</v>
@@ -2655,19 +2655,19 @@
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>5910</v>
+        <v>8496</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Greensource  SGM  110MWp</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>8517966.4</v>
+        <v>450545.92</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>0</v>
+        <v>450545.92</v>
       </c>
       <c r="H47" s="11">
         <f>F47-G47</f>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2695,23 +2695,27 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr"/>
+      <c r="K47" s="12" t="inlineStr">
+        <is>
+          <t>€8 800</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>7002</v>
+        <v>4766</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2720,10 +2724,10 @@
         </is>
       </c>
       <c r="F48" s="10" t="n">
-        <v>126896.64</v>
+        <v>100000</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H48" s="11">
         <f>F48-G48</f>
@@ -2731,7 +2735,7 @@
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2743,14 +2747,14 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>8185</v>
+        <v>5910</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2760,11 +2764,11 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>63313.4</v>
+        <v>8554776.49488</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>0</v>
@@ -2783,11 +2787,15 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr"/>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>€167 091</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B50" s="9" t="n">
         <v>8185</v>
@@ -2804,7 +2812,7 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
@@ -2831,14 +2839,14 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>46214</v>
+        <v>46217</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>7002</v>
+        <v>8185</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -2852,7 +2860,7 @@
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>0</v>
@@ -2875,31 +2883,31 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>8496</v>
+        <v>7002</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>А Greensource  SGM  110MWp</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>447568</v>
+        <v>126896.64</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>447568</v>
+        <v>0</v>
       </c>
       <c r="H52" s="11">
         <f>F52-G52</f>
@@ -2907,7 +2915,7 @@
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2915,36 +2923,32 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K52" s="12" t="inlineStr">
-        <is>
-          <t>€8 800</t>
-        </is>
-      </c>
+      <c r="K52" s="12" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>100000</v>
+        <v>126896.64</v>
       </c>
       <c r="G53" s="10" t="n">
         <v>0</v>
@@ -3055,14 +3059,14 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -3072,11 +3076,11 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>17035932.8</v>
+        <v>737597.4</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>0</v>
@@ -3099,14 +3103,14 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -3116,11 +3120,11 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>737597.4</v>
+        <v>17109552.98976</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>0</v>
@@ -3139,7 +3143,11 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K57" s="12" t="inlineStr"/>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
@@ -3167,7 +3175,7 @@
         <v>178088.4</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>0</v>
+        <v>178088.4</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3175,7 +3183,7 @@
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3454,11 +3462,11 @@
         <v>46260</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -3468,11 +3476,11 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>2896238.8</v>
+        <v>573945</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3495,14 +3503,14 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>7002</v>
+        <v>5910</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -3512,11 +3520,11 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>573945</v>
+        <v>2851592.16496</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3535,7 +3543,11 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K66" s="12" t="inlineStr"/>
+      <c r="K66" s="12" t="inlineStr">
+        <is>
+          <t>€55 697</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
@@ -3865,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3916,7 +3928,7 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B2" s="9" t="n">
         <v>5910</v>
@@ -3932,7 +3944,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>8517966.4</v>
+        <v>8554776.49488</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -4059,11 +4071,11 @@
         <v>46213</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>7002</v>
+        <v>8188</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -4072,7 +4084,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>126896.64</v>
+        <v>73926</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0</v>
@@ -4084,23 +4096,23 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46214</v>
+        <v>46217</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>7002</v>
+        <v>8185</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>0</v>
@@ -4112,23 +4124,23 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>46209</v>
+        <v>46217</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>8188</v>
+        <v>8185</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>73926</v>
+        <v>63313.4</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>0</v>
@@ -4139,82 +4151,26 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>8185</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Фундамент Hytte House Development Славське</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>63313.4</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <f>E10-F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>8185</v>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Фундамент Hytte House Development Славське</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>63313.4</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="11">
-        <f>E11-F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E12" s="13">
-        <f>SUM(E2:E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="13">
-        <f>SUM(F2:F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="13">
-        <f>SUM(G2:G11)</f>
+      <c r="E10" s="13">
+        <f>SUM(E2:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="13">
+        <f>SUM(F2:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="13">
+        <f>SUM(G2:G9)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 15.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 16.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2215,31 +2215,31 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>46195</v>
+        <v>46190</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>8644</v>
+        <v>8008</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Solars ГШ 1,7+надставки 3,5</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>415900</v>
+        <v>178088.4</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>415900</v>
+        <v>178088.4</v>
       </c>
       <c r="H37" s="11">
         <f>F37-G37</f>
@@ -2259,31 +2259,31 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>5682</v>
+        <v>8644</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>А Сцена Корчин</t>
+          <t>Solars ГШ 1,7+надставки 3,5</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>369984.96</v>
+        <v>415900</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>369984.96</v>
+        <v>415900</v>
       </c>
       <c r="H38" s="11">
         <f>F38-G38</f>
@@ -2303,19 +2303,19 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>7068</v>
+        <v>5682</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>А Сцена Корчин</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>0</v>
+        <v>369984.96</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1153420</v>
+        <v>369984.96</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2350,28 +2350,28 @@
         <v>46197</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>8360</v>
+        <v>7068</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Хаджет Лебедівка</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>95968.3</v>
+        <v>0</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>95968.3</v>
+        <v>1153420</v>
       </c>
       <c r="H40" s="11">
         <f>F40-G40</f>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2391,31 +2391,31 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>46202</v>
+        <v>46197</v>
       </c>
       <c r="B41" s="9" t="n">
-        <v>6704</v>
+        <v>8360</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>Хаджет Лебедівка</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>1872000</v>
+        <v>95968.3</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>1872000</v>
+        <v>95968.3</v>
       </c>
       <c r="H41" s="11">
         <f>F41-G41</f>
@@ -2435,19 +2435,19 @@
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>5870</v>
+        <v>6704</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>7800000</v>
+        <v>1872000</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>0</v>
+        <v>1872000</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2479,31 +2479,31 @@
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="B43" s="9" t="n">
-        <v>4766</v>
+        <v>5870</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>20000</v>
+        <v>7800000</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H43" s="11">
         <f>F43-G43</f>
@@ -2511,26 +2511,26 @@
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>8878</v>
+        <v>4766</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>410320</v>
+        <v>20000</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>410320</v>
+        <v>20000</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -2567,31 +2567,31 @@
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>6406</v>
+        <v>8878</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>218602</v>
+        <v>410320</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>0</v>
+        <v>410320</v>
       </c>
       <c r="H45" s="11">
         <f>F45-G45</f>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2611,31 +2611,31 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>8188</v>
+        <v>8008</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F46" s="10" t="n">
-        <v>73926</v>
+        <v>178088.4</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>0</v>
+        <v>178088.4</v>
       </c>
       <c r="H46" s="11">
         <f>F46-G46</f>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2655,14 +2655,14 @@
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>8496</v>
+        <v>6406</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>А Greensource  SGM  110MWp</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2672,14 +2672,14 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>450545.92</v>
+        <v>218602</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>450545.92</v>
+        <v>0</v>
       </c>
       <c r="H47" s="11">
         <f>F47-G47</f>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2695,27 +2695,23 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>€8 800</t>
-        </is>
-      </c>
+      <c r="K47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>4766</v>
+        <v>8188</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2724,10 +2720,10 @@
         </is>
       </c>
       <c r="F48" s="10" t="n">
-        <v>100000</v>
+        <v>73926</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H48" s="11">
         <f>F48-G48</f>
@@ -2735,7 +2731,7 @@
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2747,19 +2743,19 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>5910</v>
+        <v>8496</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Greensource  SGM  110MWp</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2768,10 +2764,10 @@
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>8554776.49488</v>
+        <v>449328</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>0</v>
+        <v>449328</v>
       </c>
       <c r="H49" s="11">
         <f>F49-G49</f>
@@ -2779,7 +2775,7 @@
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2789,7 +2785,7 @@
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>€167 091</t>
+          <t>€8 800</t>
         </is>
       </c>
     </row>
@@ -2798,16 +2794,16 @@
         <v>46217</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>8185</v>
+        <v>4766</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -2816,10 +2812,10 @@
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>63313.4</v>
+        <v>100000</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H50" s="11">
         <f>F50-G50</f>
@@ -2827,7 +2823,7 @@
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2856,7 +2852,7 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F51" s="10" t="n">
@@ -2883,14 +2879,14 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>7002</v>
+        <v>8185</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -2900,11 +2896,11 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>0</v>
@@ -2915,7 +2911,7 @@
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2944,14 +2940,14 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
         <v>126896.64</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>0</v>
+        <v>126896.64</v>
       </c>
       <c r="H53" s="11">
         <f>F53-G53</f>
@@ -2959,7 +2955,7 @@
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2971,14 +2967,14 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46225</v>
+        <v>46219</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>3456</v>
+        <v>7002</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -2992,10 +2988,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>335974.68</v>
+        <v>126896.64</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>0</v>
+        <v>126896.64</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3003,7 +2999,7 @@
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3015,14 +3011,14 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>46225</v>
+        <v>46219</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>8008</v>
+        <v>7002</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -3032,14 +3028,14 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>178088.4</v>
+        <v>573945</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>178088.4</v>
+        <v>573945</v>
       </c>
       <c r="H55" s="11">
         <f>F55-G55</f>
@@ -3059,14 +3055,14 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -3076,11 +3072,11 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>737597.4</v>
+        <v>8531651.142000001</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>0</v>
@@ -3099,18 +3095,22 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K56" s="12" t="inlineStr"/>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>€167 091</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>5910</v>
+        <v>3456</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -3120,11 +3120,11 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>17109552.98976</v>
+        <v>335974.68</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>0</v>
@@ -3143,22 +3143,18 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K57" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K57" s="12" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>8008</v>
+        <v>7894</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -3168,14 +3164,14 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>178088.4</v>
+        <v>737597.4</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>178088.4</v>
+        <v>0</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3183,7 +3179,7 @@
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3195,31 +3191,31 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>7068</v>
+        <v>5910</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
+        <v>17063302.284</v>
+      </c>
+      <c r="G59" s="10" t="n">
         <v>0</v>
-      </c>
-      <c r="G59" s="10" t="n">
-        <v>2794670</v>
       </c>
       <c r="H59" s="11">
         <f>F59-G59</f>
@@ -3235,35 +3231,39 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K59" s="12" t="inlineStr"/>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
         <v>46234</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>7244</v>
+        <v>7068</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>132708.6</v>
+        <v>0</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>0</v>
+        <v>2794670</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3286,25 +3286,25 @@
         <v>46234</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>7894</v>
+        <v>7244</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>185968</v>
+        <v>132708.6</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>0</v>
@@ -3327,28 +3327,28 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>8878</v>
+        <v>7894</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>12823</v>
+        <v>185968</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
@@ -3364,35 +3364,35 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>7894</v>
+        <v>8878</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>185967.99</v>
+        <v>12823</v>
       </c>
       <c r="G63" s="10" t="n">
         <v>0</v>
@@ -3415,14 +3415,14 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46249</v>
+        <v>46245</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>7002</v>
+        <v>7894</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -3432,11 +3432,11 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>573945</v>
+        <v>185967.99</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2851592.16496</v>
+        <v>2843883.714</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3551,19 +3551,19 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>46282</v>
+        <v>46267</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>7894</v>
+        <v>4766</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>737597.4</v>
+        <v>1199397.42</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -3595,19 +3595,19 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>4766</v>
+        <v>7894</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>4880000</v>
+        <v>737597.4</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3928,23 +3928,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46217</v>
+        <v>46203</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5910</v>
+        <v>5870</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>8554776.49488</v>
+        <v>7800000</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -3956,23 +3956,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46203</v>
+        <v>46165</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>5870</v>
+        <v>6704</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>7800000</v>
+        <v>4524000</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -3984,26 +3984,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46165</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6704</v>
+        <v>7068</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>4524000</v>
+        <v>5640128</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -4012,26 +4012,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46113</v>
+        <v>46212</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>7068</v>
+        <v>6406</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>5640128</v>
+        <v>218602</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -4040,14 +4040,14 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>6406</v>
+        <v>8188</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>218602</v>
+        <v>73926</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -4068,14 +4068,14 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>8188</v>
+        <v>8185</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>73926</v>
+        <v>63313.4</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0</v>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E8" s="11" t="n">
@@ -4123,54 +4123,26 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>8185</v>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Фундамент Hytte House Development Славське</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>63313.4</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
-        <f>E9-F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E10" s="13">
-        <f>SUM(E2:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="13">
-        <f>SUM(F2:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="13">
-        <f>SUM(G2:G9)</f>
+      <c r="E9" s="13">
+        <f>SUM(E2:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="13">
+        <f>SUM(F2:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="13">
+        <f>SUM(G2:G8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 16.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 21.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2743,31 +2743,31 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>8496</v>
+        <v>8454</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>А Greensource  SGM  110MWp</t>
+          <t>Олександр каркасний Верховина</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>449328</v>
+        <v>69666</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>449328</v>
+        <v>69666</v>
       </c>
       <c r="H49" s="11">
         <f>F49-G49</f>
@@ -2783,39 +2783,35 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>€8 800</t>
-        </is>
-      </c>
+      <c r="K49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>4766</v>
+        <v>8496</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Greensource  SGM  110MWp</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>100000</v>
+        <v>449592.0000000001</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>100000</v>
+        <v>449592.0000000001</v>
       </c>
       <c r="H50" s="11">
         <f>F50-G50</f>
@@ -2831,23 +2827,27 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K50" s="12" t="inlineStr"/>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>€8 800</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
         <v>46217</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>8185</v>
+        <v>4766</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>63313.4</v>
+        <v>100000</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H51" s="11">
         <f>F51-G51</f>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2896,14 +2896,14 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
         <v>63313.4</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>0</v>
+        <v>63313.4</v>
       </c>
       <c r="H52" s="11">
         <f>F52-G52</f>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2923,14 +2923,14 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>7002</v>
+        <v>8185</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2940,14 +2940,14 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="H53" s="11">
         <f>F53-G53</f>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
@@ -3028,14 +3028,14 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>573945</v>
+        <v>126896.64</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>573945</v>
+        <v>126896.64</v>
       </c>
       <c r="H55" s="11">
         <f>F55-G55</f>
@@ -3055,14 +3055,14 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>8531651.142000001</v>
+        <v>573945</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>0</v>
+        <v>573945</v>
       </c>
       <c r="H56" s="11">
         <f>F56-G56</f>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3095,22 +3095,18 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K56" s="12" t="inlineStr">
-        <is>
-          <t>€167 091</t>
-        </is>
-      </c>
+      <c r="K56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>3456</v>
+        <v>5910</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -3120,11 +3116,11 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>335974.68</v>
+        <v>8536663.863000002</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>0</v>
@@ -3135,7 +3131,7 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3143,18 +3139,22 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K57" s="12" t="inlineStr"/>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>€167 091</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>7894</v>
+        <v>3456</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -3164,11 +3164,11 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>737597.4</v>
+        <v>335974.68</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>0</v>
@@ -3191,14 +3191,14 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -3208,11 +3208,11 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>17063302.284</v>
+        <v>737597.4</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0</v>
@@ -3231,11 +3231,7 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K59" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K59" s="12" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
@@ -3327,7 +3323,7 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B62" s="9" t="n">
         <v>7894</v>
@@ -3364,7 +3360,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr"/>
@@ -3415,14 +3411,14 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -3432,11 +3428,11 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>185967.99</v>
+        <v>17073327.726</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>0</v>
@@ -3455,18 +3451,22 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K64" s="12" t="inlineStr"/>
+      <c r="K64" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46260</v>
+        <v>46245</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>7002</v>
+        <v>7894</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -3476,11 +3476,11 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>573945</v>
+        <v>185967.99</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3503,14 +3503,14 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46264</v>
+        <v>46260</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -3520,11 +3520,11 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2843883.714</v>
+        <v>573945</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3543,11 +3543,7 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K66" s="12" t="inlineStr">
-        <is>
-          <t>€55 697</t>
-        </is>
-      </c>
+      <c r="K66" s="12" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
@@ -3595,14 +3591,14 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46282</v>
+        <v>46271</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -3612,11 +3608,11 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>737597.4</v>
+        <v>2845554.621</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3635,29 +3631,77 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K68" s="12" t="inlineStr"/>
+      <c r="K68" s="12" t="inlineStr">
+        <is>
+          <t>€55 697</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="E69" s="3" t="inlineStr">
+      <c r="A69" s="8" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B69" s="9" t="n">
+        <v>7894</v>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>А Фора  SCP  32PS</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="n">
+        <v>737597.4</v>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="11">
+        <f>F69-G69</f>
+        <v/>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K69" s="12" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F69" s="13">
-        <f>SUM(F2:F68)</f>
-        <v/>
-      </c>
-      <c r="G69" s="13">
-        <f>SUM(G2:G68)</f>
-        <v/>
-      </c>
-      <c r="H69" s="13">
-        <f>SUM(H2:H68)</f>
+      <c r="F70" s="13">
+        <f>SUM(F2:F69)</f>
+        <v/>
+      </c>
+      <c r="G70" s="13">
+        <f>SUM(G2:G69)</f>
+        <v/>
+      </c>
+      <c r="H70" s="13">
+        <f>SUM(H2:H69)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I68"/>
+  <autoFilter ref="A1:I69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3877,7 +3921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3928,23 +3972,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46203</v>
+        <v>46224</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5870</v>
+        <v>5910</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>7800000</v>
+        <v>8536663.863000002</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -3956,23 +4000,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46165</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6704</v>
+        <v>5870</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4524000</v>
+        <v>7800000</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -3984,26 +4028,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46113</v>
+        <v>46165</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7068</v>
+        <v>6704</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5640128</v>
+        <v>4524000</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -4012,26 +4056,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46212</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>6406</v>
+        <v>7068</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>218602</v>
+        <v>5640128</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -4040,14 +4084,14 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>8188</v>
+        <v>6406</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -4056,7 +4100,7 @@
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>73926</v>
+        <v>218602</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -4068,14 +4112,14 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>8185</v>
+        <v>8188</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -4084,7 +4128,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>63313.4</v>
+        <v>73926</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0</v>
@@ -4095,54 +4139,26 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>8185</v>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Фундамент Hytte House Development Славське</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>63313.4</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <f>E8-F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E9" s="13">
-        <f>SUM(E2:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="13">
-        <f>SUM(F2:F8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="13">
-        <f>SUM(G2:G8)</f>
+      <c r="E8" s="13">
+        <f>SUM(E2:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="13">
+        <f>SUM(F2:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="13">
+        <f>SUM(G2:G7)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3191,28 +3191,28 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46231</v>
+        <v>46227</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>7894</v>
+        <v>4766</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>737597.4</v>
+        <v>4368478.98</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0</v>
@@ -3235,31 +3235,31 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>7068</v>
+        <v>7894</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
+        <v>737597.4</v>
+      </c>
+      <c r="G60" s="10" t="n">
         <v>0</v>
-      </c>
-      <c r="G60" s="10" t="n">
-        <v>2794670</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3282,28 +3282,28 @@
         <v>46234</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>7244</v>
+        <v>7068</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>132708.6</v>
+        <v>0</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>0</v>
+        <v>2794670</v>
       </c>
       <c r="H61" s="11">
         <f>F61-G61</f>
@@ -3323,28 +3323,28 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>7894</v>
+        <v>7244</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>185968</v>
+        <v>132708.6</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr"/>
@@ -3370,25 +3370,25 @@
         <v>46237</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>8878</v>
+        <v>7894</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>12823</v>
+        <v>185968</v>
       </c>
       <c r="G63" s="10" t="n">
         <v>0</v>
@@ -3411,28 +3411,28 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>5910</v>
+        <v>8878</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>17073327.726</v>
+        <v>12823</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>0</v>
@@ -3451,22 +3451,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K64" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K64" s="12" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -3476,11 +3472,11 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>185967.99</v>
+        <v>17073327.726</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3499,18 +3495,22 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K65" s="12" t="inlineStr"/>
+      <c r="K65" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46260</v>
+        <v>46245</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>7002</v>
+        <v>7894</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -3520,11 +3520,11 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>573945</v>
+        <v>185967.99</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3547,19 +3547,19 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>46267</v>
+        <v>46260</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>1199397.42</v>
+        <v>573945</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -3584,35 +3584,35 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K67" s="12" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46271</v>
+        <v>46266</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>2845554.621</v>
+        <v>128100</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3631,27 +3631,23 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K68" s="12" t="inlineStr">
-        <is>
-          <t>€55 697</t>
-        </is>
-      </c>
+      <c r="K68" s="12" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46282</v>
+        <v>46267</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>7894</v>
+        <v>4766</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -3660,7 +3656,7 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>737597.4</v>
+        <v>1199397.42</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0</v>
@@ -3682,26 +3678,118 @@
       <c r="K69" s="12" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="E70" s="3" t="inlineStr">
+      <c r="A70" s="8" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>5910</v>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>А   AGM 2V</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>2845554.621</v>
+      </c>
+      <c r="G70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="11">
+        <f>F70-G70</f>
+        <v/>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K70" s="12" t="inlineStr">
+        <is>
+          <t>€55 697</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>7894</v>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>А Фора  SCP  32PS</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="n">
+        <v>737597.4</v>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="11">
+        <f>F71-G71</f>
+        <v/>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F70" s="13">
-        <f>SUM(F2:F69)</f>
-        <v/>
-      </c>
-      <c r="G70" s="13">
-        <f>SUM(G2:G69)</f>
-        <v/>
-      </c>
-      <c r="H70" s="13">
-        <f>SUM(H2:H69)</f>
+      <c r="F72" s="13">
+        <f>SUM(F2:F71)</f>
+        <v/>
+      </c>
+      <c r="G72" s="13">
+        <f>SUM(G2:G71)</f>
+        <v/>
+      </c>
+      <c r="H72" s="13">
+        <f>SUM(H2:H71)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I69"/>
+  <autoFilter ref="A1:I71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 21.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 22.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -3102,28 +3102,28 @@
         <v>46224</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>8536663.863000002</v>
+        <v>4368478.98</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>0</v>
+        <v>4368478.98</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3139,11 +3139,7 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K57" s="12" t="inlineStr">
-        <is>
-          <t>€167 091</t>
-        </is>
-      </c>
+      <c r="K57" s="12" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
@@ -3179,7 +3175,7 @@
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3191,28 +3187,28 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>4368478.98</v>
+        <v>8536663.863000002</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0</v>
@@ -3223,7 +3219,7 @@
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3231,7 +3227,11 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K59" s="12" t="inlineStr"/>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>€167 091</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
@@ -3455,7 +3455,7 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B65" s="9" t="n">
         <v>5910</v>
@@ -3679,7 +3679,7 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B70" s="9" t="n">
         <v>5910</v>
@@ -4009,7 +4009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4060,7 +4060,7 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B2" s="9" t="n">
         <v>5910</v>
@@ -4172,23 +4172,23 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>6406</v>
+        <v>3456</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>218602</v>
+        <v>335974.68</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -4200,14 +4200,14 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>8188</v>
+        <v>6406</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>73926</v>
+        <v>218602</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0</v>
@@ -4227,26 +4227,54 @@
       </c>
     </row>
     <row r="8">
-      <c r="D8" s="3" t="inlineStr">
+      <c r="A8" s="8" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>8188</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Фундамент Ужгород Стефанія</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>73926</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <f>E8-F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E8" s="13">
-        <f>SUM(E2:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="13">
-        <f>SUM(F2:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="13">
-        <f>SUM(G2:G7)</f>
+      <c r="E9" s="13">
+        <f>SUM(E2:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="13">
+        <f>SUM(F2:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="13">
+        <f>SUM(G2:G8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 22.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 23.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>449592.0000000001</v>
+        <v>449328</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>449592.0000000001</v>
+        <v>449328</v>
       </c>
       <c r="H50" s="11">
         <f>F50-G50</f>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>8536663.863000002</v>
+        <v>8531651.142000001</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>17073327.726</v>
+        <v>17063302.284</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>2845554.621</v>
+        <v>2843883.714</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>8536663.863000002</v>
+        <v>8531651.142000001</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2600000</v>
+        <v>2553000</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2600000</v>
+        <v>2553000</v>
       </c>
       <c r="H12" s="11">
         <f>F12-G12</f>
@@ -1155,7 +1155,11 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>€50 000</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -1180,10 +1184,10 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5200000</v>
+        <v>5106000</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>5200000</v>
+        <v>5106000</v>
       </c>
       <c r="H13" s="11">
         <f>F13-G13</f>
@@ -1199,7 +1203,11 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr"/>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>€100 000</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -1444,7 +1452,7 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>4524000</v>
+        <v>4442220</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>0</v>
@@ -1463,7 +1471,11 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>€87 000</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
@@ -2456,10 +2468,10 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1872000</v>
+        <v>1838160</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>1872000</v>
+        <v>1838160</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2475,7 +2487,11 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="K42" s="12" t="inlineStr"/>
+      <c r="K42" s="12" t="inlineStr">
+        <is>
+          <t>€36 000</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
@@ -2500,7 +2516,7 @@
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>7800000</v>
+        <v>7659000</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>0</v>
@@ -2519,7 +2535,11 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="K43" s="12" t="inlineStr"/>
+      <c r="K43" s="12" t="inlineStr">
+        <is>
+          <t>€150 000</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
@@ -4104,7 +4124,7 @@
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>7800000</v>
+        <v>7659000</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -4132,7 +4152,7 @@
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>4524000</v>
+        <v>4442220</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 23.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 24.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2553000</v>
+        <v>2582308.44</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2553000</v>
+        <v>2582308.44</v>
       </c>
       <c r="H12" s="11">
         <f>F12-G12</f>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>€50 000</t>
+          <t>€50 574</t>
         </is>
       </c>
     </row>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5106000</v>
+        <v>5248968</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>5106000</v>
+        <v>5248968</v>
       </c>
       <c r="H13" s="11">
         <f>F13-G13</f>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>€100 000</t>
+          <t>€102 800</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>4442220</v>
+        <v>4566551.100000001</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>€87 000</t>
+          <t>€89 435</t>
         </is>
       </c>
     </row>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1838160</v>
+        <v>1889373.18</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>1838160</v>
+        <v>1889373.18</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>€36 000</t>
+          <t>€37 003</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>7659000</v>
+        <v>7746874.260000001</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>€150 000</t>
+          <t>€151 721</t>
         </is>
       </c>
     </row>
@@ -3119,19 +3119,19 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>4766</v>
+        <v>3456</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4368478.98</v>
+        <v>335974.68</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4368478.98</v>
+        <v>0</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3166,11 +3166,11 @@
         <v>46225</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>3456</v>
+        <v>5910</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -3180,14 +3180,14 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>335974.68</v>
+        <v>8531651.142000001</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>0</v>
+        <v>8531651.142000001</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3203,32 +3203,36 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K58" s="12" t="inlineStr"/>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>€167 091</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>8531651.142000001</v>
+        <v>4368478.98</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0</v>
@@ -3247,11 +3251,7 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K59" s="12" t="inlineStr">
-        <is>
-          <t>€167 091</t>
-        </is>
-      </c>
+      <c r="K59" s="12" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
@@ -3475,7 +3475,7 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B65" s="9" t="n">
         <v>5910</v>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B70" s="9" t="n">
         <v>5910</v>
@@ -4080,23 +4080,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46225</v>
+        <v>46203</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5910</v>
+        <v>5870</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>8531651.142000001</v>
+        <v>7746874.260000001</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -4108,23 +4108,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46203</v>
+        <v>46165</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>5870</v>
+        <v>6704</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>7659000</v>
+        <v>4566551.100000001</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -4136,14 +4136,14 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46165</v>
+        <v>46227</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6704</v>
+        <v>4766</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>4442220</v>
+        <v>4368478.98</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3119,19 +3119,19 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>3456</v>
+        <v>4766</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>335974.68</v>
+        <v>4368478.98</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>0</v>
+        <v>4368478.98</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3166,11 +3166,11 @@
         <v>46225</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>5910</v>
+        <v>3456</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -3180,14 +3180,14 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>8531651.142000001</v>
+        <v>335974.68</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>8531651.142000001</v>
+        <v>0</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3203,39 +3203,35 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K58" s="12" t="inlineStr">
-        <is>
-          <t>€167 091</t>
-        </is>
-      </c>
+      <c r="K58" s="12" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>4368478.98</v>
+        <v>8531651.142000001</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>0</v>
+        <v>8531651.142000001</v>
       </c>
       <c r="H59" s="11">
         <f>F59-G59</f>
@@ -3243,7 +3239,7 @@
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3251,7 +3247,11 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K59" s="12" t="inlineStr"/>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>€167 091</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
@@ -4029,7 +4029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4136,26 +4136,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46227</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>4766</v>
+        <v>7068</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>4368478.98</v>
+        <v>5640128</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -4164,26 +4164,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46113</v>
+        <v>46225</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>7068</v>
+        <v>3456</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>5640128</v>
+        <v>335974.68</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -4192,23 +4192,23 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>3456</v>
+        <v>6406</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>335974.68</v>
+        <v>218602</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -4220,14 +4220,14 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>6406</v>
+        <v>8188</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>218602</v>
+        <v>73926</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0</v>
@@ -4247,54 +4247,26 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>8188</v>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Фундамент Ужгород Стефанія</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>73926</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <f>E8-F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E9" s="13">
-        <f>SUM(E2:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="13">
-        <f>SUM(F2:F8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="13">
-        <f>SUM(G2:G8)</f>
+      <c r="E8" s="13">
+        <f>SUM(E2:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="13">
+        <f>SUM(F2:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="13">
+        <f>SUM(G2:G7)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 24.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 26.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -2675,14 +2675,14 @@
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>6406</v>
+        <v>8188</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>218602</v>
+        <v>73926</v>
       </c>
       <c r="G47" s="10" t="n">
         <v>0</v>
@@ -2722,28 +2722,28 @@
         <v>46213</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>8188</v>
+        <v>8454</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Олександр каркасний Верховина</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
-        <v>73926</v>
+        <v>69666</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>0</v>
+        <v>69666</v>
       </c>
       <c r="H48" s="11">
         <f>F48-G48</f>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2763,31 +2763,31 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>8454</v>
+        <v>8496</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Олександр каркасний Верховина</t>
+          <t>А Greensource  SGM  110MWp</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>69666</v>
+        <v>449328</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>69666</v>
+        <v>449328</v>
       </c>
       <c r="H49" s="11">
         <f>F49-G49</f>
@@ -2803,35 +2803,39 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr"/>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>€8 800</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>8496</v>
+        <v>4766</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>А Greensource  SGM  110MWp</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>449328</v>
+        <v>100000</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>449328</v>
+        <v>100000</v>
       </c>
       <c r="H50" s="11">
         <f>F50-G50</f>
@@ -2847,27 +2851,23 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>€8 800</t>
-        </is>
-      </c>
+      <c r="K50" s="12" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
         <v>46217</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>4766</v>
+        <v>8185</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>100000</v>
+        <v>63313.4</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>100000</v>
+        <v>63313.4</v>
       </c>
       <c r="H51" s="11">
         <f>F51-G51</f>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
@@ -2943,14 +2943,14 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>8185</v>
+        <v>7002</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2960,14 +2960,14 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>63313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>63313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="H53" s="11">
         <f>F53-G53</f>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
@@ -3048,14 +3048,14 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>126896.64</v>
+        <v>573945</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>126896.64</v>
+        <v>573945</v>
       </c>
       <c r="H55" s="11">
         <f>F55-G55</f>
@@ -3075,31 +3075,31 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>7002</v>
+        <v>4766</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>573945</v>
+        <v>4368478.98</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>573945</v>
+        <v>4368478.98</v>
       </c>
       <c r="H56" s="11">
         <f>F56-G56</f>
@@ -3119,19 +3119,19 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>4766</v>
+        <v>3456</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4368478.98</v>
+        <v>335974.68</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4368478.98</v>
+        <v>0</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3166,11 +3166,11 @@
         <v>46225</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>3456</v>
+        <v>5910</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -3180,14 +3180,14 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>335974.68</v>
+        <v>8531651.142000001</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>0</v>
+        <v>8531651.142000001</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3203,18 +3203,22 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K58" s="12" t="inlineStr"/>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>€167 091</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -3224,14 +3228,14 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>8531651.142000001</v>
+        <v>737597.4</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>8531651.142000001</v>
+        <v>0</v>
       </c>
       <c r="H59" s="11">
         <f>F59-G59</f>
@@ -3239,7 +3243,7 @@
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3247,39 +3251,35 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K59" s="12" t="inlineStr">
-        <is>
-          <t>€167 091</t>
-        </is>
-      </c>
+      <c r="K59" s="12" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>7894</v>
+        <v>7068</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>737597.4</v>
+        <v>0</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>0</v>
+        <v>2794670</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3302,28 +3302,28 @@
         <v>46234</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>7068</v>
+        <v>7244</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
+        <v>132708.6</v>
+      </c>
+      <c r="G61" s="10" t="n">
         <v>0</v>
-      </c>
-      <c r="G61" s="10" t="n">
-        <v>2794670</v>
       </c>
       <c r="H61" s="11">
         <f>F61-G61</f>
@@ -3343,28 +3343,28 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>7244</v>
+        <v>6406</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>132708.6</v>
+        <v>218602</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr"/>
@@ -4029,7 +4029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4192,14 +4192,14 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>6406</v>
+        <v>8188</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>218602</v>
+        <v>73926</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -4219,54 +4219,26 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>8188</v>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Фундамент Ужгород Стефанія</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>73926</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="11">
-        <f>E7-F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E8" s="13">
-        <f>SUM(E2:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="13">
-        <f>SUM(F2:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="13">
-        <f>SUM(G2:G7)</f>
+      <c r="E7" s="13">
+        <f>SUM(E2:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="13">
+        <f>SUM(F2:F6)</f>
+        <v/>
+      </c>
+      <c r="G7" s="13">
+        <f>SUM(G2:G6)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 26.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 27.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2582308.44</v>
+        <v>2577756.78</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2582308.44</v>
+        <v>2577756.78</v>
       </c>
       <c r="H12" s="11">
         <f>F12-G12</f>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5248968</v>
+        <v>5239716</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>5248968</v>
+        <v>5239716</v>
       </c>
       <c r="H13" s="11">
         <f>F13-G13</f>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>4566551.100000001</v>
+        <v>4558501.95</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>0</v>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1889373.18</v>
+        <v>1886042.91</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>1889373.18</v>
+        <v>1886042.91</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>7746874.260000001</v>
+        <v>7733219.37</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>0</v>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>449328</v>
+        <v>448536</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>449328</v>
+        <v>448536</v>
       </c>
       <c r="H49" s="11">
         <f>F49-G49</f>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>8531651.142000001</v>
+        <v>8516612.979</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>8531651.142000001</v>
+        <v>8516612.979</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3475,14 +3475,14 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -3492,11 +3492,11 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>17063302.284</v>
+        <v>185967.99</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3515,22 +3515,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K65" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K65" s="12" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -3540,11 +3536,11 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>185967.99</v>
+        <v>17033225.958</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3563,7 +3559,11 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K66" s="12" t="inlineStr"/>
+      <c r="K66" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
@@ -3699,7 +3699,7 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B70" s="9" t="n">
         <v>5910</v>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>2843883.714</v>
+        <v>2838870.993</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>7746874.260000001</v>
+        <v>7733219.37</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4566551.100000001</v>
+        <v>4558501.95</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 27.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 28.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2811,31 +2811,31 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>4766</v>
+        <v>8898</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>(6022-26 - ГШ Фундамент домобудування)</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>100000</v>
+        <v>259395.65</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>100000</v>
+        <v>259395.65</v>
       </c>
       <c r="H50" s="11">
         <f>F50-G50</f>
@@ -2858,16 +2858,16 @@
         <v>46217</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>8185</v>
+        <v>4766</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>63313.4</v>
+        <v>100000</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>63313.4</v>
+        <v>100000</v>
       </c>
       <c r="H51" s="11">
         <f>F51-G51</f>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
@@ -2943,14 +2943,14 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>7002</v>
+        <v>8185</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2960,14 +2960,14 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>126896.64</v>
+        <v>63313.4</v>
       </c>
       <c r="H53" s="11">
         <f>F53-G53</f>
@@ -2990,11 +2990,11 @@
         <v>46219</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>7002</v>
+        <v>6352</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А АБМК ТОВ  SCP Blade 10PS</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>126896.64</v>
+        <v>80000.03999999999</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>126896.64</v>
+        <v>80000.03999999999</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3048,14 +3048,14 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>573945</v>
+        <v>126896.64</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>573945</v>
+        <v>126896.64</v>
       </c>
       <c r="H55" s="11">
         <f>F55-G55</f>
@@ -3075,19 +3075,19 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>4368478.98</v>
+        <v>126896.64</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>4368478.98</v>
+        <v>126896.64</v>
       </c>
       <c r="H56" s="11">
         <f>F56-G56</f>
@@ -3119,14 +3119,14 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46225</v>
+        <v>46219</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>3456</v>
+        <v>7002</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -3136,14 +3136,14 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>335974.68</v>
+        <v>573945</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>0</v>
+        <v>573945</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3163,31 +3163,31 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>8516612.979</v>
+        <v>4368478.98</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>8516612.979</v>
+        <v>4368478.98</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3203,22 +3203,18 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K58" s="12" t="inlineStr">
-        <is>
-          <t>€167 091</t>
-        </is>
-      </c>
+      <c r="K58" s="12" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>7894</v>
+        <v>3456</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -3228,11 +3224,11 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>737597.4</v>
+        <v>335974.68</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0</v>
@@ -3243,7 +3239,7 @@
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3255,31 +3251,31 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46234</v>
+        <v>46225</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>7068</v>
+        <v>5910</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>0</v>
+        <v>8516612.979</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>2794670</v>
+        <v>8516612.979</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3287,7 +3283,7 @@
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3295,32 +3291,36 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K60" s="12" t="inlineStr"/>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>€167 091</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>7244</v>
+        <v>7894</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>132708.6</v>
+        <v>737597.4</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3343,19 +3343,19 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46237</v>
+        <v>46232</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>6406</v>
+        <v>8898</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>(6022-26 - ГШ Фундамент домобудування)</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>218602</v>
+        <v>27768</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
@@ -3380,38 +3380,38 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>7894</v>
+        <v>7068</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>185968</v>
+        <v>0</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>0</v>
+        <v>2794670</v>
       </c>
       <c r="H63" s="11">
         <f>F63-G63</f>
@@ -3424,21 +3424,21 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K63" s="12" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>8878</v>
+        <v>7244</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>12823</v>
+        <v>132708.6</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>0</v>
@@ -3468,21 +3468,21 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K64" s="12" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>7894</v>
+        <v>6352</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А АБМК ТОВ  SCP Blade 10PS</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -3492,11 +3492,11 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>185967.99</v>
+        <v>1399046.58</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3519,19 +3519,19 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46247</v>
+        <v>46237</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>5910</v>
+        <v>6406</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>17033225.958</v>
+        <v>218602</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3559,22 +3559,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K66" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K66" s="12" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>46260</v>
+        <v>46237</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>7002</v>
+        <v>7894</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
@@ -3584,11 +3580,11 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>573945</v>
+        <v>185968</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -3611,14 +3607,14 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46266</v>
+        <v>46237</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>4766</v>
+        <v>8878</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -3628,11 +3624,11 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>128100</v>
+        <v>12823</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3648,35 +3644,35 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K68" s="12" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46267</v>
+        <v>46245</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>4766</v>
+        <v>7894</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>1199397.42</v>
+        <v>185967.99</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0</v>
@@ -3692,14 +3688,14 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K69" s="12" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46279</v>
+        <v>46247</v>
       </c>
       <c r="B70" s="9" t="n">
         <v>5910</v>
@@ -3716,11 +3712,11 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>2838870.993</v>
+        <v>17033225.958</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -3736,25 +3732,25 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K70" s="12" t="inlineStr">
         <is>
-          <t>€55 697</t>
+          <t>€334 181</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>46282</v>
+        <v>46248</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>7894</v>
+        <v>8898</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>(6022-26 - ГШ Фундамент домобудування)</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -3764,11 +3760,11 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>737597.4</v>
+        <v>189603.75</v>
       </c>
       <c r="G71" s="10" t="n">
         <v>0</v>
@@ -3784,32 +3780,428 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B72" s="9" t="n">
+        <v>7002</v>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>А Фора  SCP W 24PS V1</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>573945</v>
+      </c>
+      <c r="G72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="11">
+        <f>F72-G72</f>
+        <v/>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K72" s="12" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B73" s="9" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>Четвертий платіж</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="n">
+        <v>128100</v>
+      </c>
+      <c r="G73" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="11">
+        <f>F73-G73</f>
+        <v/>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K71" s="12" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="E72" s="3" t="inlineStr">
+      <c r="K73" s="12" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>8898</v>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>(6022-26 - ГШ Фундамент домобудування)</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>Четвертий платіж</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>189603.75</v>
+      </c>
+      <c r="G74" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="11">
+        <f>F74-G74</f>
+        <v/>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K74" s="12" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="n">
+        <v>1199397.42</v>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="11">
+        <f>F75-G75</f>
+        <v/>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K75" s="12" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>5910</v>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>А   AGM 2V</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>2838870.993</v>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="11">
+        <f>F76-G76</f>
+        <v/>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="inlineStr">
+        <is>
+          <t>€55 697</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>7894</v>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>А Фора  SCP  32PS</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="n">
+        <v>737597.4</v>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="11">
+        <f>F77-G77</f>
+        <v/>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K77" s="12" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B78" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>А АБМК ТОВ  SCP Blade 10PS</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="11">
+        <f>F78-G78</f>
+        <v/>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K78" s="12" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="n"/>
+      <c r="B79" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>А АБМК ТОВ  SCP Blade 10PS</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="n">
+        <v>1119237.26</v>
+      </c>
+      <c r="G79" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="11">
+        <f>F79-G79</f>
+        <v/>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>без дати</t>
+        </is>
+      </c>
+      <c r="K79" s="12" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="n"/>
+      <c r="B80" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>А АБМК ТОВ  SCP Blade 10PS</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>Четвертий платіж</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>371982.96</v>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="11">
+        <f>F80-G80</f>
+        <v/>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>без дати</t>
+        </is>
+      </c>
+      <c r="K80" s="12" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F72" s="13">
-        <f>SUM(F2:F71)</f>
-        <v/>
-      </c>
-      <c r="G72" s="13">
-        <f>SUM(G2:G71)</f>
-        <v/>
-      </c>
-      <c r="H72" s="13">
-        <f>SUM(H2:H71)</f>
+      <c r="F81" s="13">
+        <f>SUM(F2:F80)</f>
+        <v/>
+      </c>
+      <c r="G81" s="13">
+        <f>SUM(G2:G80)</f>
+        <v/>
+      </c>
+      <c r="H81" s="13">
+        <f>SUM(H2:H80)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I71"/>
+  <autoFilter ref="A1:I80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3820,7 +4212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3996,25 +4388,71 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>жов 2026</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
+        <f>SUMIF('Графік надходжень'!J:J,"2026-10",'Графік надходжень'!F:F)</f>
+        <v/>
+      </c>
+      <c r="C8" s="11">
+        <f>SUMIF('Графік надходжень'!J:J,"2026-10",'Графік надходжень'!G:G)</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="14">
+        <f>IF(B8=0,0,C8/B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>без дати</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>SUMIF('Графік надходжень'!J:J,"без дати",'Графік надходжень'!F:F)</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>SUMIF('Графік надходжень'!J:J,"без дати",'Графік надходжень'!G:G)</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="14">
+        <f>IF(B9=0,0,C9/B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="B8" s="13">
-        <f>SUM(B2:B7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="13">
-        <f>SUM(C2:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="13">
-        <f>SUM(D2:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="15">
-        <f>IF(B8=0,0,C8/B8)</f>
+      <c r="B10" s="13">
+        <f>SUM(B2:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="13">
+        <f>SUM(C2:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="13">
+        <f>SUM(D2:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>IF(B10=0,0,C10/B10)</f>
         <v/>
       </c>
     </row>
@@ -4029,7 +4467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4164,23 +4602,23 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>3456</v>
+        <v>7894</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>335974.68</v>
+        <v>737597.4</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0</v>
@@ -4192,23 +4630,23 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46213</v>
+        <v>46225</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>8188</v>
+        <v>3456</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>73926</v>
+        <v>335974.68</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -4219,26 +4657,54 @@
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="3" t="inlineStr">
+      <c r="A7" s="8" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>8188</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Фундамент Ужгород Стефанія</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>73926</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
+        <f>E7-F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E7" s="13">
-        <f>SUM(E2:E6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>SUM(F2:F6)</f>
-        <v/>
-      </c>
-      <c r="G7" s="13">
-        <f>SUM(G2:G6)</f>
+      <c r="E8" s="13">
+        <f>SUM(E2:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="13">
+        <f>SUM(F2:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="13">
+        <f>SUM(G2:G7)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -2818,7 +2818,7 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>(6022-26 - ГШ Фундамент домобудування)</t>
+          <t>6022-26 - ГШ Фундамент домобудування</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>(6022-26 - ГШ Фундамент домобудування)</t>
+          <t>6022-26 - ГШ Фундамент домобудування</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -3743,14 +3743,14 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>46248</v>
+        <v>46258</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>8898</v>
+        <v>6352</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>(6022-26 - ГШ Фундамент домобудування)</t>
+          <t>А АБМК ТОВ  SCP Blade 10PS</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>189603.75</v>
+        <v>1119237.26</v>
       </c>
       <c r="G71" s="10" t="n">
         <v>0</v>
@@ -3875,28 +3875,28 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>8898</v>
+        <v>4766</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>(6022-26 - ГШ Фундамент домобудування)</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>189603.75</v>
+        <v>1199397.42</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>0</v>
@@ -3922,25 +3922,25 @@
         <v>46267</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>4766</v>
+        <v>8898</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>6022-26 - ГШ Фундамент домобудування</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1199397.42</v>
+        <v>189603.75</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>0</v>
@@ -4011,14 +4011,14 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>7894</v>
+        <v>8898</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>6022-26 - ГШ Фундамент домобудування</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -4028,11 +4028,11 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>737597.4</v>
+        <v>189603.75</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4055,14 +4055,14 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46320</v>
+        <v>46282</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>6352</v>
+        <v>7894</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 10PS</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>651792.28</v>
+        <v>737597.4</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4092,13 +4092,15 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="n"/>
+      <c r="A79" s="8" t="n">
+        <v>46308</v>
+      </c>
       <c r="B79" s="9" t="n">
         <v>6352</v>
       </c>
@@ -4114,11 +4116,11 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>1119237.26</v>
+        <v>371982.96</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4134,13 +4136,15 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>без дати</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K79" s="12" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="n"/>
+      <c r="A80" s="8" t="n">
+        <v>46321</v>
+      </c>
       <c r="B80" s="9" t="n">
         <v>6352</v>
       </c>
@@ -4156,11 +4160,11 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>371982.96</v>
+        <v>651792.28</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4176,7 +4180,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>без дати</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K80" s="12" t="inlineStr"/>
@@ -4212,7 +4216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4411,48 +4415,25 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>без дати</t>
-        </is>
-      </c>
-      <c r="B9" s="11">
-        <f>SUMIF('Графік надходжень'!J:J,"без дати",'Графік надходжень'!F:F)</f>
-        <v/>
-      </c>
-      <c r="C9" s="11">
-        <f>SUMIF('Графік надходжень'!J:J,"без дати",'Графік надходжень'!G:G)</f>
-        <v/>
-      </c>
-      <c r="D9" s="11">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="B9" s="13">
+        <f>SUM(B2:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="13">
+        <f>SUM(C2:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="13">
+        <f>SUM(D2:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
         <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Разом</t>
-        </is>
-      </c>
-      <c r="B10" s="13">
-        <f>SUM(B2:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="13">
-        <f>SUM(C2:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="13">
-        <f>SUM(D2:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="15">
-        <f>IF(B10=0,0,C10/B10)</f>
         <v/>
       </c>
     </row>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 28.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 29.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2577756.78</v>
+        <v>2582814.18</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2577756.78</v>
+        <v>2582814.18</v>
       </c>
       <c r="H12" s="11">
         <f>F12-G12</f>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5239716</v>
+        <v>5249996</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>5239716</v>
+        <v>5249996</v>
       </c>
       <c r="H13" s="11">
         <f>F13-G13</f>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>4558501.95</v>
+        <v>4567445.45</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>0</v>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1886042.91</v>
+        <v>1889743.21</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>1886042.91</v>
+        <v>1889743.21</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>7733219.37</v>
+        <v>7748391.47</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>0</v>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>448536</v>
+        <v>449416</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>448536</v>
+        <v>449416</v>
       </c>
       <c r="H49" s="11">
         <f>F49-G49</f>
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>8516612.979</v>
+        <v>8533322.049000001</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>8516612.979</v>
+        <v>8533322.049000001</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>17033225.958</v>
+        <v>17066644.098</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>2838870.993</v>
+        <v>2844440.683</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>7733219.37</v>
+        <v>7748391.47</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4558501.95</v>
+        <v>4567445.45</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -4666,26 +4666,54 @@
       </c>
     </row>
     <row r="8">
-      <c r="D8" s="3" t="inlineStr">
+      <c r="A8" s="8" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>8898</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>6022-26 - ГШ Фундамент домобудування</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>27768</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <f>E8-F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E8" s="13">
-        <f>SUM(E2:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="13">
-        <f>SUM(F2:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="13">
-        <f>SUM(G2:G7)</f>
+      <c r="E9" s="13">
+        <f>SUM(E2:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="13">
+        <f>SUM(F2:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="13">
+        <f>SUM(G2:G8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 29.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 30.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2582814.18</v>
+        <v>2583319.92</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2582814.18</v>
+        <v>2583319.92</v>
       </c>
       <c r="H12" s="11">
         <f>F12-G12</f>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5249996</v>
+        <v>5251024</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>5249996</v>
+        <v>5251024</v>
       </c>
       <c r="H13" s="11">
         <f>F13-G13</f>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>4567445.45</v>
+        <v>4568339.8</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>0</v>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1889743.21</v>
+        <v>1890113.24</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>1889743.21</v>
+        <v>1890113.24</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>7748391.47</v>
+        <v>7749908.68</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>0</v>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>449416</v>
+        <v>449504</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>449416</v>
+        <v>449504</v>
       </c>
       <c r="H49" s="11">
         <f>F49-G49</f>
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>8533322.049000001</v>
+        <v>8534992.956</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>8533322.049000001</v>
+        <v>8534992.956</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3431,7 +3431,7 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B64" s="9" t="n">
         <v>7244</v>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K64" s="12" t="inlineStr"/>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>17066644.098</v>
+        <v>17069985.912</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>2844440.683</v>
+        <v>2844997.652</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>7748391.47</v>
+        <v>7749908.68</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4567445.45</v>
+        <v>4568339.8</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 30.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 31.07.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2583319.92</v>
+        <v>2592928.98</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2583319.92</v>
+        <v>2592928.98</v>
       </c>
       <c r="H12" s="11">
         <f>F12-G12</f>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5251024</v>
+        <v>5270556</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>5251024</v>
+        <v>5270556</v>
       </c>
       <c r="H13" s="11">
         <f>F13-G13</f>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>4568339.8</v>
+        <v>4585332.45</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>0</v>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1890113.24</v>
+        <v>1897143.81</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>1890113.24</v>
+        <v>1897143.81</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>7749908.68</v>
+        <v>7778735.670000001</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>0</v>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>449504</v>
+        <v>451176</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>449504</v>
+        <v>451176</v>
       </c>
       <c r="H49" s="11">
         <f>F49-G49</f>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 10PS</t>
+          <t>А АБМК ТОВ  SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -3034,11 +3034,11 @@
         <v>46219</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>7002</v>
+        <v>6352</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А АБМК ТОВ  SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -3048,14 +3048,14 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>126896.64</v>
+        <v>80000.03999999999</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>126896.64</v>
+        <v>80000.03999999999</v>
       </c>
       <c r="H55" s="11">
         <f>F55-G55</f>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
@@ -3136,14 +3136,14 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>573945</v>
+        <v>126896.64</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>573945</v>
+        <v>126896.64</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3163,31 +3163,31 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>4368478.98</v>
+        <v>573945</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>4368478.98</v>
+        <v>573945</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3207,19 +3207,19 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>3456</v>
+        <v>4766</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>335974.68</v>
+        <v>4368478.98</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>0</v>
+        <v>4368478.98</v>
       </c>
       <c r="H59" s="11">
         <f>F59-G59</f>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>8534992.956</v>
+        <v>8566740.189000001</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>8534992.956</v>
+        <v>8566740.189000001</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3299,31 +3299,31 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>7894</v>
+        <v>7068</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>737597.4</v>
+        <v>0</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>0</v>
+        <v>2794670</v>
       </c>
       <c r="H61" s="11">
         <f>F61-G61</f>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3343,28 +3343,28 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46232</v>
+        <v>46235</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>8898</v>
+        <v>7244</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>6022-26 - ГШ Фундамент домобудування</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>27768</v>
+        <v>132708.6</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
@@ -3375,43 +3375,43 @@
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>7068</v>
+        <v>5910</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
+        <v>17133480.378</v>
+      </c>
+      <c r="G63" s="10" t="n">
         <v>0</v>
-      </c>
-      <c r="G63" s="10" t="n">
-        <v>2794670</v>
       </c>
       <c r="H63" s="11">
         <f>F63-G63</f>
@@ -3424,35 +3424,39 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="K63" s="12" t="inlineStr"/>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K63" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>7244</v>
+        <v>6352</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А АБМК ТОВ  SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>132708.6</v>
+        <v>1399046.58</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>0</v>
@@ -3478,16 +3482,16 @@
         <v>46237</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>6352</v>
+        <v>6406</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 10PS</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -3496,7 +3500,7 @@
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>1399046.58</v>
+        <v>218602</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3522,16 +3526,16 @@
         <v>46237</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>6406</v>
+        <v>7894</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -3540,7 +3544,7 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>218602</v>
+        <v>185968</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3566,25 +3570,25 @@
         <v>46237</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>7894</v>
+        <v>8878</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>185968</v>
+        <v>12823</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -3607,28 +3611,28 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>8878</v>
+        <v>6352</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>А АБМК ТОВ  SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>12823</v>
+        <v>1399046.58</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3695,14 +3699,14 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>5910</v>
+        <v>8898</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>6022-26 - ГШ Фундамент домобудування</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -3716,7 +3720,7 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>17069985.912</v>
+        <v>27768</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -3735,22 +3739,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K70" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K70" s="12" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
         <v>46258</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>6352</v>
+        <v>3456</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 10PS</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>1119237.26</v>
+        <v>335974.68</v>
       </c>
       <c r="G71" s="10" t="n">
         <v>0</v>
@@ -3787,14 +3787,14 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>7002</v>
+        <v>6352</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А АБМК ТОВ  SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -3804,11 +3804,11 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>573945</v>
+        <v>1119237.26</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>0</v>
@@ -3831,28 +3831,28 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>4766</v>
+        <v>6352</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А АБМК ТОВ  SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>128100</v>
+        <v>1119237.26</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -3868,26 +3868,26 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K73" s="12" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46267</v>
+        <v>46260</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Фора  SCP W 24PS V1</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>1199397.42</v>
+        <v>573945</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>0</v>
@@ -3912,26 +3912,26 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K74" s="12" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>8898</v>
+        <v>4766</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>6022-26 - ГШ Фундамент домобудування</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>189603.75</v>
+        <v>128100</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>0</v>
@@ -3963,28 +3963,28 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46279</v>
+        <v>46267</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>2844997.652</v>
+        <v>1199397.42</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4003,22 +4003,18 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K76" s="12" t="inlineStr">
-        <is>
-          <t>€55 697</t>
-        </is>
-      </c>
+      <c r="K76" s="12" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46280</v>
+        <v>46270</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>8898</v>
+        <v>5910</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>6022-26 - ГШ Фундамент домобудування</t>
+          <t>А   AGM 2V</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -4032,7 +4028,7 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>189603.75</v>
+        <v>2855580.063</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4051,18 +4047,22 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K77" s="12" t="inlineStr"/>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>€55 697</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>7894</v>
+        <v>8898</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>6022-26 - ГШ Фундамент домобудування</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -4072,11 +4072,11 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>737597.4</v>
+        <v>189603.75</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4099,14 +4099,14 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46308</v>
+        <v>46282</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>6352</v>
+        <v>7894</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 10PS</t>
+          <t>А Фора  SCP  32PS</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4116,11 +4116,11 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>371982.96</v>
+        <v>737597.4</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4136,21 +4136,21 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K79" s="12" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46321</v>
+        <v>46308</v>
       </c>
       <c r="B80" s="9" t="n">
         <v>6352</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 10PS</t>
+          <t>А АБМК ТОВ  SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>651792.28</v>
+        <v>371982.96</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4186,26 +4186,158 @@
       <c r="K80" s="12" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="E81" s="3" t="inlineStr">
+      <c r="A81" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B81" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>Четвертий платіж</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="n">
+        <v>371982.96</v>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="11">
+        <f>F81-G81</f>
+        <v/>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K81" s="12" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B82" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="11">
+        <f>F82-G82</f>
+        <v/>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K82" s="12" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B83" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="11">
+        <f>F83-G83</f>
+        <v/>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K83" s="12" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F81" s="13">
-        <f>SUM(F2:F80)</f>
-        <v/>
-      </c>
-      <c r="G81" s="13">
-        <f>SUM(G2:G80)</f>
-        <v/>
-      </c>
-      <c r="H81" s="13">
-        <f>SUM(H2:H80)</f>
+      <c r="F84" s="13">
+        <f>SUM(F2:F83)</f>
+        <v/>
+      </c>
+      <c r="G84" s="13">
+        <f>SUM(G2:G83)</f>
+        <v/>
+      </c>
+      <c r="H84" s="13">
+        <f>SUM(H2:H83)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I80"/>
+  <autoFilter ref="A1:I83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4448,7 +4580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4515,7 +4647,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>7749908.68</v>
+        <v>7778735.670000001</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -4543,7 +4675,7 @@
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4568339.8</v>
+        <v>4585332.45</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -4583,23 +4715,23 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46231</v>
+        <v>46213</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>7894</v>
+        <v>8188</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>737597.4</v>
+        <v>73926</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0</v>
@@ -4610,110 +4742,26 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>46225</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>3456</v>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>А Підселання фундаменту</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>335974.68</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="11">
-        <f>E6-F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>8188</v>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Фундамент Ужгород Стефанія</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>73926</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="11">
-        <f>E7-F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>46232</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>8898</v>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>6022-26 - ГШ Фундамент домобудування</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>27768</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <f>E8-F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E9" s="13">
-        <f>SUM(E2:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="13">
-        <f>SUM(F2:F8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="13">
-        <f>SUM(G2:G8)</f>
+      <c r="E6" s="13">
+        <f>SUM(E2:E5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="13">
+        <f>SUM(F2:F5)</f>
+        <v/>
+      </c>
+      <c r="G6" s="13">
+        <f>SUM(G2:G5)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 31.07.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 03.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -2678,28 +2678,28 @@
         <v>46213</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>8188</v>
+        <v>8454</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Олександр каркасний Верховина</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>73926</v>
+        <v>69666</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>0</v>
+        <v>69666</v>
       </c>
       <c r="H47" s="11">
         <f>F47-G47</f>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2719,31 +2719,31 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>8454</v>
+        <v>8188</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Олександр каркасний Верховина</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
-        <v>69666</v>
+        <v>73926</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>69666</v>
+        <v>0</v>
       </c>
       <c r="H48" s="11">
         <f>F48-G48</f>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>6022-26 - ГШ Фундамент домобудування</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>259395.65</v>
+        <v>290403.65</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>259395.65</v>
+        <v>290403.65</v>
       </c>
       <c r="H50" s="11">
         <f>F50-G50</f>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -3034,11 +3034,11 @@
         <v>46219</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>6352</v>
+        <v>7002</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -3048,14 +3048,14 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>80000.03999999999</v>
+        <v>126896.64</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>80000.03999999999</v>
+        <v>126896.64</v>
       </c>
       <c r="H55" s="11">
         <f>F55-G55</f>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -3136,14 +3136,14 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>126896.64</v>
+        <v>573945</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>126896.64</v>
+        <v>573945</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3163,31 +3163,31 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>7002</v>
+        <v>4766</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>573945</v>
+        <v>4368478.98</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>573945</v>
+        <v>4368478.98</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3207,31 +3207,31 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>4368478.98</v>
+        <v>8566740.189000001</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>4368478.98</v>
+        <v>8566740.189000001</v>
       </c>
       <c r="H59" s="11">
         <f>F59-G59</f>
@@ -3247,23 +3247,27 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K59" s="12" t="inlineStr"/>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>€167 091</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>5910</v>
+        <v>6312</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>-26 ГШ Фундамент домобудування Георгій</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -3272,10 +3276,10 @@
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>8566740.189000001</v>
+        <v>543429</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>8566740.189000001</v>
+        <v>543429</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3291,39 +3295,35 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K60" s="12" t="inlineStr">
-        <is>
-          <t>€167 091</t>
-        </is>
-      </c>
+      <c r="K60" s="12" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>7068</v>
+        <v>6130</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>0</v>
+        <v>56056</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>2794670</v>
+        <v>56056</v>
       </c>
       <c r="H61" s="11">
         <f>F61-G61</f>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3343,14 +3343,14 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46235</v>
+        <v>46232</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>7244</v>
+        <v>6130</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>132708.6</v>
+        <v>50964</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>0</v>
+        <v>50964</v>
       </c>
       <c r="H62" s="11">
         <f>F62-G62</f>
@@ -3375,43 +3375,43 @@
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>5910</v>
+        <v>6130</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>17133480.378</v>
+        <v>75762</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>0</v>
+        <v>75762</v>
       </c>
       <c r="H63" s="11">
         <f>F63-G63</f>
@@ -3419,47 +3419,43 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="K63" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K63" s="12" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>6352</v>
+        <v>7068</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1399046.58</v>
+        <v>0</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>0</v>
+        <v>2794670</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3472,35 +3468,35 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K64" s="12" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>6406</v>
+        <v>7244</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>218602</v>
+        <v>132708.6</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3511,7 +3507,7 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3526,11 +3522,11 @@
         <v>46237</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -3544,7 +3540,7 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>185968</v>
+        <v>17133480.378</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3555,7 +3551,7 @@
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3563,18 +3559,22 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K66" s="12" t="inlineStr"/>
+      <c r="K66" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
         <v>46237</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>8878</v>
+        <v>6130</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>12823</v>
+        <v>36665</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3611,14 +3611,14 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="B68" s="9" t="n">
         <v>6352</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -3635,7 +3635,7 @@
         <v>1399046.58</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>0</v>
+        <v>1399046.58</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3655,28 +3655,28 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>7894</v>
+        <v>6406</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>185967.99</v>
+        <v>218602</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0</v>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3699,14 +3699,14 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46248</v>
+        <v>46238</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>8898</v>
+        <v>7894</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>6022-26 - ГШ Фундамент домобудування</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>27768</v>
+        <v>185968</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -3743,28 +3743,28 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>3456</v>
+        <v>8878</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>335974.68</v>
+        <v>12823</v>
       </c>
       <c r="G71" s="10" t="n">
         <v>0</v>
@@ -3787,14 +3787,14 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46258</v>
+        <v>46245</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>6352</v>
+        <v>7894</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>1119237.26</v>
+        <v>185967.99</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>0</v>
@@ -3831,14 +3831,14 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>6352</v>
+        <v>8898</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -3848,11 +3848,11 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>1119237.26</v>
+        <v>188043.75</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -3875,14 +3875,14 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>7002</v>
+        <v>3456</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP W 24PS V1</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
@@ -3892,11 +3892,11 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>573945</v>
+        <v>335974.68</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>0</v>
@@ -3919,28 +3919,28 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>4766</v>
+        <v>6352</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>128100</v>
+        <v>1119237.26</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>0</v>
@@ -3956,26 +3956,26 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K75" s="12" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46267</v>
+        <v>46263</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>1199397.42</v>
+        <v>573945</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4000,35 +4000,35 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46270</v>
+        <v>46265</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>5910</v>
+        <v>6130</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>А   AGM 2V</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>2855580.063</v>
+        <v>73335</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4044,39 +4044,35 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="K77" s="12" t="inlineStr">
-        <is>
-          <t>€55 697</t>
-        </is>
-      </c>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K77" s="12" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46280</v>
+        <v>46266</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>8898</v>
+        <v>4766</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>6022-26 - ГШ Фундамент домобудування</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>189603.75</v>
+        <v>128100</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4099,19 +4095,19 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46282</v>
+        <v>46267</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>7894</v>
+        <v>4766</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>А Фора  SCP  32PS</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -4120,7 +4116,7 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>737597.4</v>
+        <v>1199397.42</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4143,14 +4139,14 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46308</v>
+        <v>46270</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>6352</v>
+        <v>5910</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -4160,11 +4156,11 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>371982.96</v>
+        <v>2855580.063</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4180,21 +4176,25 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K80" s="12" t="inlineStr"/>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K80" s="12" t="inlineStr">
+        <is>
+          <t>€55 697</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46308</v>
+        <v>46280</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>6352</v>
+        <v>8898</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -4204,11 +4204,11 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>371982.96</v>
+        <v>188043.75</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4224,21 +4224,21 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46321</v>
+        <v>46282</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>6352</v>
+        <v>7894</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>651792.28</v>
+        <v>737597.4</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4268,35 +4268,35 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K82" s="12" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46321</v>
+        <v>46283</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>6352</v>
+        <v>7508</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>А АБМК ТОВ  SCP Blade 8PS</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>651792.28</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4312,32 +4312,120 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K83" s="12" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B84" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>АБМК SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Четвертий платіж</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>371982.96</v>
+      </c>
+      <c r="G84" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="11">
+        <f>F84-G84</f>
+        <v/>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K83" s="12" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="E84" s="3" t="inlineStr">
+      <c r="K84" s="12" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>АБМК SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="11">
+        <f>F85-G85</f>
+        <v/>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K85" s="12" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F84" s="13">
-        <f>SUM(F2:F83)</f>
-        <v/>
-      </c>
-      <c r="G84" s="13">
-        <f>SUM(G2:G83)</f>
-        <v/>
-      </c>
-      <c r="H84" s="13">
-        <f>SUM(H2:H83)</f>
+      <c r="F86" s="13">
+        <f>SUM(F2:F85)</f>
+        <v/>
+      </c>
+      <c r="G86" s="13">
+        <f>SUM(G2:G85)</f>
+        <v/>
+      </c>
+      <c r="H86" s="13">
+        <f>SUM(H2:H85)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I83"/>
+  <autoFilter ref="A1:I85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4580,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4631,14 +4719,14 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46203</v>
+        <v>46237</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5870</v>
+        <v>5910</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
@@ -4647,7 +4735,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>7778735.670000001</v>
+        <v>17133480.378</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -4659,23 +4747,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46165</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6704</v>
+        <v>5870</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4585332.45</v>
+        <v>7778735.670000001</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -4687,26 +4775,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46113</v>
+        <v>46165</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7068</v>
+        <v>6704</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5640128</v>
+        <v>4585332.45</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -4715,26 +4803,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46213</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>8188</v>
+        <v>7068</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>73926</v>
+        <v>5640128</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -4742,26 +4830,110 @@
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="3" t="inlineStr">
+      <c r="A6" s="8" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11">
+        <f>E6-F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>7244</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>В Модулекс модульна будівля Чернігів</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>132708.6</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
+        <f>E7-F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>8188</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Фундамент Ужгород Стефанія</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>73926</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <f>E8-F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E6" s="13">
-        <f>SUM(E2:E5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="13">
-        <f>SUM(F2:F5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>SUM(G2:G5)</f>
+      <c r="E9" s="13">
+        <f>SUM(E2:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="13">
+        <f>SUM(F2:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="13">
+        <f>SUM(G2:G8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 03.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 04.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2592928.98</v>
+        <v>2611641.36</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2592928.98</v>
+        <v>2611641.36</v>
       </c>
       <c r="H12" s="11">
         <f>F12-G12</f>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5270556</v>
+        <v>5308592</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>5270556</v>
+        <v>5308592</v>
       </c>
       <c r="H13" s="11">
         <f>F13-G13</f>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>4585332.45</v>
+        <v>4618423.4</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>0</v>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1897143.81</v>
+        <v>1910834.92</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>1897143.81</v>
+        <v>1910834.92</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>7778735.670000001</v>
+        <v>7834872.44</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>0</v>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>451176</v>
+        <v>454432</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>451176</v>
+        <v>454432</v>
       </c>
       <c r="H49" s="11">
         <f>F49-G49</f>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>8566740.189000001</v>
+        <v>8628563.748000002</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>8566740.189000001</v>
+        <v>8628563.748000002</v>
       </c>
       <c r="H59" s="11">
         <f>F59-G59</f>
@@ -3522,28 +3522,28 @@
         <v>46237</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>5910</v>
+        <v>6130</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>17133480.378</v>
+        <v>36665</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3559,39 +3559,35 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K66" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K66" s="12" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
         <v>46237</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>6130</v>
+        <v>6352</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>36665</v>
+        <v>1399046.58</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>36665</v>
+        <v>1399046.58</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3614,16 +3610,16 @@
         <v>46237</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>6352</v>
+        <v>6406</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3632,10 +3628,10 @@
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1399046.58</v>
+        <v>218602</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>1399046.58</v>
+        <v>0</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3643,7 +3639,7 @@
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3655,19 +3651,19 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>6406</v>
+        <v>7894</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -3676,7 +3672,7 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>218602</v>
+        <v>185968</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0</v>
@@ -3699,31 +3695,31 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>7894</v>
+        <v>4766</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>185968</v>
+        <v>64050</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>0</v>
+        <v>64050</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3731,7 +3727,7 @@
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3875,14 +3871,14 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>3456</v>
+        <v>5910</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
@@ -3892,14 +3888,14 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>335974.68</v>
+        <v>17257127.496</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>0</v>
+        <v>2965168.8</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3915,18 +3911,22 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K74" s="12" t="inlineStr"/>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
         <v>46258</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>6352</v>
+        <v>3456</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1119237.26</v>
+        <v>335974.68</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>0</v>
@@ -3963,14 +3963,14 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46263</v>
+        <v>46258</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>7002</v>
+        <v>6352</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -3980,11 +3980,11 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>573945</v>
+        <v>1119237.26</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4007,19 +4007,19 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>6130</v>
+        <v>7002</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>73335</v>
+        <v>573945</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4051,14 +4051,14 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>4766</v>
+        <v>6130</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -4068,14 +4068,14 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>128100</v>
+        <v>73335</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr"/>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>1199397.42</v>
+        <v>1263447.42</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>2855580.063</v>
+        <v>2876187.916</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4719,14 +4719,14 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46237</v>
+        <v>46203</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5910</v>
+        <v>5870</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>17133480.378</v>
+        <v>7834872.44</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -4747,23 +4747,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46203</v>
+        <v>46165</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>5870</v>
+        <v>6704</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>7778735.670000001</v>
+        <v>4618423.4</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -4775,26 +4775,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46165</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6704</v>
+        <v>7068</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>4585332.45</v>
+        <v>5640128</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -4803,26 +4803,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46113</v>
+        <v>46237</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>7068</v>
+        <v>6406</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>5640128</v>
+        <v>218602</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -4831,14 +4831,14 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>6406</v>
+        <v>7894</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>218602</v>
+        <v>185968</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 04.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 05.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>8628563.748000002</v>
+        <v>8628527.6</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>8628563.748000002</v>
+        <v>8628527.6</v>
       </c>
       <c r="H59" s="11">
         <f>F59-G59</f>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>€167 091</t>
+          <t>€167 090</t>
         </is>
       </c>
     </row>
@@ -3390,28 +3390,28 @@
         <v>46234</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>6130</v>
+        <v>5910</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>75762</v>
+        <v>17257106.84</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>75762</v>
+        <v>2965168.8</v>
       </c>
       <c r="H63" s="11">
         <f>F63-G63</f>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3427,23 +3427,27 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K63" s="12" t="inlineStr"/>
+      <c r="K63" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
         <v>46234</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>7068</v>
+        <v>6130</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3452,10 +3456,10 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>0</v>
+        <v>75762</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>2794670</v>
+        <v>75762</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3463,7 +3467,7 @@
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3475,31 +3479,31 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>7244</v>
+        <v>7068</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>132708.6</v>
+        <v>0</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>0</v>
+        <v>2794670</v>
       </c>
       <c r="H65" s="11">
         <f>F65-G65</f>
@@ -3507,26 +3511,26 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>6130</v>
+        <v>7244</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -3536,14 +3540,14 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>36665</v>
+        <v>132708.6</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>36665</v>
+        <v>0</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3551,7 +3555,7 @@
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3566,28 +3570,28 @@
         <v>46237</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>6352</v>
+        <v>6130</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>1399046.58</v>
+        <v>36665</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>1399046.58</v>
+        <v>36665</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3610,16 +3614,16 @@
         <v>46237</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>6406</v>
+        <v>6352</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3628,10 +3632,10 @@
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>218602</v>
+        <v>1399046.58</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>0</v>
+        <v>1399046.58</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3639,7 +3643,7 @@
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3651,19 +3655,19 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>7894</v>
+        <v>6406</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -3672,7 +3676,7 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>185968</v>
+        <v>218602</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0</v>
@@ -3695,31 +3699,31 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>4766</v>
+        <v>7894</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>64050</v>
+        <v>185968</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>64050</v>
+        <v>0</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3727,7 +3731,7 @@
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3739,28 +3743,28 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>8878</v>
+        <v>5910</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>12823</v>
+        <v>2876038.16</v>
       </c>
       <c r="G71" s="10" t="n">
         <v>0</v>
@@ -3779,35 +3783,39 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K71" s="12" t="inlineStr"/>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>7894</v>
+        <v>4766</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>185967.99</v>
+        <v>64050</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>0</v>
+        <v>64050</v>
       </c>
       <c r="H72" s="11">
         <f>F72-G72</f>
@@ -3815,7 +3823,7 @@
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3827,28 +3835,28 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>8898</v>
+        <v>8878</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>188043.75</v>
+        <v>12823</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -3871,14 +3879,14 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46254</v>
+        <v>46245</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
@@ -3888,14 +3896,14 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>17257127.496</v>
+        <v>185967.99</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>2965168.8</v>
+        <v>0</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3911,22 +3919,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K74" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K74" s="12" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>3456</v>
+        <v>8898</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -3936,11 +3940,11 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>335974.68</v>
+        <v>188043.75</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>0</v>
@@ -3966,11 +3970,11 @@
         <v>46258</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>6352</v>
+        <v>3456</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -3984,7 +3988,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>1119237.26</v>
+        <v>335974.68</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4007,14 +4011,14 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46263</v>
+        <v>46258</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>7002</v>
+        <v>6352</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -4024,11 +4028,11 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>573945</v>
+        <v>1119237.26</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4051,19 +4055,19 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>6130</v>
+        <v>7002</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -4072,10 +4076,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>73335</v>
+        <v>573945</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>36665</v>
+        <v>0</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4095,14 +4099,14 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>4766</v>
+        <v>6130</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4116,10 +4120,10 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>1263447.42</v>
+        <v>73335</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4132,35 +4136,35 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K79" s="12" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46270</v>
+        <v>46267</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>2876187.916</v>
+        <v>1263447.42</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4179,11 +4183,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K80" s="12" t="inlineStr">
-        <is>
-          <t>€55 697</t>
-        </is>
-      </c>
+      <c r="K80" s="12" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
@@ -4668,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4719,26 +4719,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5870</v>
+        <v>5910</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>7834872.44</v>
+        <v>17257106.84</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>0</v>
+        <v>2965168.8</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -4747,23 +4747,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46165</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6704</v>
+        <v>5870</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4618423.4</v>
+        <v>7834872.44</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -4775,26 +4775,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46113</v>
+        <v>46165</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7068</v>
+        <v>6704</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5640128</v>
+        <v>4618423.4</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -4803,26 +4803,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46237</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>6406</v>
+        <v>7068</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>218602</v>
+        <v>5640128</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -4831,14 +4831,14 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>7894</v>
+        <v>6406</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>185968</v>
+        <v>218602</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -4859,23 +4859,23 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>7244</v>
+        <v>7894</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>132708.6</v>
+        <v>185968</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0</v>
@@ -4887,23 +4887,23 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46214</v>
+        <v>46235</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>8188</v>
+        <v>7244</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>73926</v>
+        <v>132708.6</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>0</v>
@@ -4914,26 +4914,54 @@
       </c>
     </row>
     <row r="9">
-      <c r="D9" s="3" t="inlineStr">
+      <c r="A9" s="8" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>8188</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Фундамент Ужгород Стефанія</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>73926</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <f>E9-F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E9" s="13">
-        <f>SUM(E2:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="13">
-        <f>SUM(F2:F8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="13">
-        <f>SUM(G2:G8)</f>
+      <c r="E10" s="13">
+        <f>SUM(E2:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="13">
+        <f>SUM(F2:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="13">
+        <f>SUM(G2:G9)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -763,19 +763,19 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7536</v>
+        <v>7244</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="F4" s="10" t="n">
-        <v>244374</v>
+        <v>77600</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>244374</v>
+        <v>77600</v>
       </c>
       <c r="H4" s="11">
         <f>F4-G4</f>
@@ -807,19 +807,19 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>7244</v>
+        <v>7536</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="F5" s="10" t="n">
-        <v>77600</v>
+        <v>244374</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>77600</v>
+        <v>244374</v>
       </c>
       <c r="H5" s="11">
         <f>F5-G5</f>
@@ -851,19 +851,19 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>8140</v>
+        <v>3456</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>В Газинвестпроект фундамент Киев</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>150000</v>
+        <v>421968</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>150000</v>
+        <v>421968</v>
       </c>
       <c r="H6" s="11">
         <f>F6-G6</f>
@@ -888,14 +888,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>7536</v>
@@ -932,21 +932,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>3456</v>
+        <v>8360</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Хаджет Лебедівка</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>421968</v>
+        <v>231000</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>421968</v>
+        <v>231000</v>
       </c>
       <c r="H8" s="11">
         <f>F8-G8</f>
@@ -983,7 +983,7 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>7536</v>
@@ -1027,14 +1027,14 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>8360</v>
+        <v>8008</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Хаджет Лебедівка</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>231000</v>
+        <v>430850.64</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>231000</v>
+        <v>430850.64</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1071,19 +1071,19 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>8008</v>
+        <v>5870</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>430850.64</v>
+        <v>2611641.36</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>430850.64</v>
+        <v>2611641.36</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -1111,18 +1111,22 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr"/>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>€50 574</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
         <v>46161</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>5870</v>
+        <v>6704</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -1136,10 +1140,10 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2611641.36</v>
+        <v>5308592</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2611641.36</v>
+        <v>5308592</v>
       </c>
       <c r="H12" s="11">
         <f>F12-G12</f>
@@ -1157,7 +1161,7 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>€50 574</t>
+          <t>€102 800</t>
         </is>
       </c>
     </row>
@@ -1166,16 +1170,16 @@
         <v>46161</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>6704</v>
+        <v>7002</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1184,10 +1188,10 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5308592</v>
+        <v>1015173.12</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>5308592</v>
+        <v>1015173.12</v>
       </c>
       <c r="H13" s="11">
         <f>F13-G13</f>
@@ -1203,27 +1207,23 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>€102 800</t>
-        </is>
-      </c>
+      <c r="K13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
         <v>46161</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>7002</v>
+        <v>8438</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1015173.12</v>
+        <v>758160</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>1015173.12</v>
+        <v>758160</v>
       </c>
       <c r="H14" s="11">
         <f>F14-G14</f>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>7536</v>
@@ -1299,19 +1299,19 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>8438</v>
+        <v>8238</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>758160</v>
+        <v>2011000</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>758160</v>
+        <v>2011000</v>
       </c>
       <c r="H16" s="11">
         <f>F16-G16</f>
@@ -1343,31 +1343,31 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>8238</v>
+        <v>6704</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>2011000</v>
+        <v>4618423.4</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>2011000</v>
+        <v>0</v>
       </c>
       <c r="H17" s="11">
         <f>F17-G17</f>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1383,11 +1383,15 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>€89 435</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>7536</v>
@@ -1431,31 +1435,31 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>6704</v>
+        <v>7508</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>4618423.4</v>
+        <v>1245999.94</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>0</v>
+        <v>1245999.94</v>
       </c>
       <c r="H19" s="11">
         <f>F19-G19</f>
@@ -1463,7 +1467,7 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1471,15 +1475,11 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>€89 435</t>
-        </is>
-      </c>
+      <c r="K19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>7508</v>
@@ -1496,14 +1496,14 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1245999.94</v>
+        <v>751000.0600000001</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>1245999.94</v>
+        <v>751000.0600000001</v>
       </c>
       <c r="H20" s="11">
         <f>F20-G20</f>
@@ -1526,11 +1526,11 @@
         <v>46168</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>7508</v>
+        <v>8140</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>В Газинвестпроект фундамент Киев</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1540,14 +1540,14 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>751000.0600000001</v>
+        <v>150000</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>751000.0600000001</v>
+        <v>150000</v>
       </c>
       <c r="H21" s="11">
         <f>F21-G21</f>
@@ -2007,19 +2007,19 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>8140</v>
+        <v>3456</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>В Газинвестпроект фундамент Киев</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>86041.2</v>
+        <v>783940.92</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>86041.2</v>
+        <v>783940.92</v>
       </c>
       <c r="H32" s="11">
         <f>F32-G32</f>
@@ -2054,11 +2054,11 @@
         <v>46184</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>3456</v>
+        <v>8360</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Хаджет Лебедівка</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>783940.92</v>
+        <v>95968.3</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>783940.92</v>
+        <v>95968.3</v>
       </c>
       <c r="H33" s="11">
         <f>F33-G33</f>
@@ -2095,31 +2095,31 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>8360</v>
+        <v>7474</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Хаджет Лебедівка</t>
+          <t>А Головне управління Національної поліції в Одеській області  SCP  15PS</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F34" s="10" t="n">
-        <v>95968.3</v>
+        <v>1749999</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>95968.3</v>
+        <v>1749999</v>
       </c>
       <c r="H34" s="11">
         <f>F34-G34</f>
@@ -2139,31 +2139,31 @@
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>46185</v>
+        <v>46187</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>7474</v>
+        <v>8140</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>А Головне управління Національної поліції в Одеській області  SCP  15PS</t>
+          <t>В Газинвестпроект фундамент Киев</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>1749999</v>
+        <v>86041.2</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>1749999</v>
+        <v>86041.2</v>
       </c>
       <c r="H35" s="11">
         <f>F35-G35</f>
@@ -2719,14 +2719,14 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46214</v>
+        <v>46216</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>8188</v>
+        <v>8496</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>А Greensource  SGM  110MWp</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
-        <v>73926</v>
+        <v>454432</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>0</v>
+        <v>454432</v>
       </c>
       <c r="H48" s="11">
         <f>F48-G48</f>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2759,23 +2759,27 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K48" s="12" t="inlineStr"/>
+      <c r="K48" s="12" t="inlineStr">
+        <is>
+          <t>€8 800</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
         <v>46216</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>8496</v>
+        <v>8898</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>А Greensource  SGM  110MWp</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2784,10 +2788,10 @@
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>454432</v>
+        <v>290403.65</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>454432</v>
+        <v>290403.65</v>
       </c>
       <c r="H49" s="11">
         <f>F49-G49</f>
@@ -2803,39 +2807,35 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>€8 800</t>
-        </is>
-      </c>
+      <c r="K49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>8898</v>
+        <v>4766</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>290403.65</v>
+        <v>100000</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>290403.65</v>
+        <v>100000</v>
       </c>
       <c r="H50" s="11">
         <f>F50-G50</f>
@@ -2858,16 +2858,16 @@
         <v>46217</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>4766</v>
+        <v>8185</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>100000</v>
+        <v>63313.4</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>100000</v>
+        <v>63313.4</v>
       </c>
       <c r="H51" s="11">
         <f>F51-G51</f>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
@@ -2943,14 +2943,14 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>8185</v>
+        <v>6352</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2960,14 +2960,14 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>63313.4</v>
+        <v>80000.03999999999</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>63313.4</v>
+        <v>80000.03999999999</v>
       </c>
       <c r="H53" s="11">
         <f>F53-G53</f>
@@ -2990,11 +2990,11 @@
         <v>46219</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>6352</v>
+        <v>7002</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>80000.03999999999</v>
+        <v>126896.64</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>80000.03999999999</v>
+        <v>126896.64</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
@@ -3092,14 +3092,14 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>126896.64</v>
+        <v>573945</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>126896.64</v>
+        <v>573945</v>
       </c>
       <c r="H56" s="11">
         <f>F56-G56</f>
@@ -3119,31 +3119,31 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>7002</v>
+        <v>4766</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>573945</v>
+        <v>4368478.98</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>573945</v>
+        <v>4368478.98</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3163,31 +3163,31 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>4368478.98</v>
+        <v>8628527.6</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>4368478.98</v>
+        <v>8628527.6</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3203,23 +3203,27 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K58" s="12" t="inlineStr"/>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>€167 090</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>5910</v>
+        <v>6312</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>-26 ГШ Фундамент домобудування Георгій</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -3228,10 +3232,10 @@
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>8628527.6</v>
+        <v>543429</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>8628527.6</v>
+        <v>543429</v>
       </c>
       <c r="H59" s="11">
         <f>F59-G59</f>
@@ -3247,22 +3251,18 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K59" s="12" t="inlineStr">
-        <is>
-          <t>€167 090</t>
-        </is>
-      </c>
+      <c r="K59" s="12" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>6312</v>
+        <v>6130</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Георгій</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>543429</v>
+        <v>56056</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>543429</v>
+        <v>56056</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B61" s="9" t="n">
         <v>6130</v>
@@ -3316,14 +3316,14 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>56056</v>
+        <v>50964</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>56056</v>
+        <v>50964</v>
       </c>
       <c r="H61" s="11">
         <f>F61-G61</f>
@@ -3343,7 +3343,7 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B62" s="9" t="n">
         <v>6130</v>
@@ -3360,14 +3360,14 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>50964</v>
+        <v>75762</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>50964</v>
+        <v>75762</v>
       </c>
       <c r="H62" s="11">
         <f>F62-G62</f>
@@ -3390,28 +3390,28 @@
         <v>46234</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>5910</v>
+        <v>7068</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>17257106.84</v>
+        <v>0</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>2965168.8</v>
+        <v>2794670</v>
       </c>
       <c r="H63" s="11">
         <f>F63-G63</f>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3427,15 +3427,11 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K63" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K63" s="12" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B64" s="9" t="n">
         <v>6130</v>
@@ -3452,14 +3448,14 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>75762</v>
+        <v>36665</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>75762</v>
+        <v>36665</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3472,38 +3468,38 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K64" s="12" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>7068</v>
+        <v>6352</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>0</v>
+        <v>1399046.58</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>2794670</v>
+        <v>1399046.58</v>
       </c>
       <c r="H65" s="11">
         <f>F65-G65</f>
@@ -3511,40 +3507,40 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>7244</v>
+        <v>8188</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>132708.6</v>
+        <v>73926</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3567,14 +3563,14 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>6130</v>
+        <v>4766</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
@@ -3588,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>36665</v>
+        <v>64050</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>36665</v>
+        <v>64050</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3611,14 +3607,14 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>6352</v>
+        <v>7894</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -3632,10 +3628,10 @@
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1399046.58</v>
+        <v>185968</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>1399046.58</v>
+        <v>0</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3643,7 +3639,7 @@
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3655,28 +3651,28 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>6406</v>
+        <v>8878</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>218602</v>
+        <v>12823</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0</v>
@@ -3687,7 +3683,7 @@
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3699,7 +3695,7 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="B70" s="9" t="n">
         <v>7894</v>
@@ -3716,11 +3712,11 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>185968</v>
+        <v>185967.99</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -3731,7 +3727,7 @@
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3743,28 +3739,28 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>5910</v>
+        <v>6406</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>2876038.16</v>
+        <v>218602</v>
       </c>
       <c r="G71" s="10" t="n">
         <v>0</v>
@@ -3783,39 +3779,35 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K71" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K71" s="12" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>4766</v>
+        <v>8898</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>64050</v>
+        <v>188043.75</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>64050</v>
+        <v>0</v>
       </c>
       <c r="H72" s="11">
         <f>F72-G72</f>
@@ -3823,7 +3815,7 @@
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3835,28 +3827,28 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>8878</v>
+        <v>3456</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>12823</v>
+        <v>335974.68</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -3879,14 +3871,14 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46245</v>
+        <v>46258</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
@@ -3896,14 +3888,14 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>185967.99</v>
+        <v>17257106.84</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>0</v>
+        <v>2965168.8</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3919,18 +3911,22 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K74" s="12" t="inlineStr"/>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46248</v>
+        <v>46258</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>8898</v>
+        <v>6352</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -3940,11 +3936,11 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>188043.75</v>
+        <v>1119237.26</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>0</v>
@@ -3967,14 +3963,14 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>3456</v>
+        <v>7002</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -3984,11 +3980,11 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>335974.68</v>
+        <v>573945</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4011,31 +4007,31 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>6352</v>
+        <v>6130</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>1119237.26</v>
+        <v>73335</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="H77" s="11">
         <f>F77-G77</f>
@@ -4055,19 +4051,19 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>7002</v>
+        <v>7244</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -4076,7 +4072,7 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>573945</v>
+        <v>132708.6</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4099,14 +4095,14 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>6130</v>
+        <v>4766</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4120,10 +4116,10 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>73335</v>
+        <v>1263447.42</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>36665</v>
+        <v>0</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4136,7 +4132,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K79" s="12" t="inlineStr"/>
@@ -4146,25 +4142,25 @@
         <v>46267</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1263447.42</v>
+        <v>2876038.16</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4183,7 +4179,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K80" s="12" t="inlineStr"/>
+      <c r="K80" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
@@ -4668,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4719,26 +4719,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5910</v>
+        <v>5870</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>17257106.84</v>
+        <v>7834872.44</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2965168.8</v>
+        <v>0</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -4747,23 +4747,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46203</v>
+        <v>46165</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>5870</v>
+        <v>6704</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>7834872.44</v>
+        <v>4618423.4</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -4775,26 +4775,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46165</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6704</v>
+        <v>7068</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>4618423.4</v>
+        <v>5640128</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -4803,26 +4803,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46113</v>
+        <v>46238</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>7068</v>
+        <v>8188</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>5640128</v>
+        <v>73926</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1692038</v>
+        <v>0</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -4830,138 +4830,26 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>6406</v>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Максим Яловий Чинадієво</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>218602</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="11">
-        <f>E6-F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>46238</v>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>7894</v>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>SCP Фора  Хотів</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>185968</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="11">
-        <f>E7-F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>7244</v>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>П'ятий платіж</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>132708.6</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <f>E8-F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>46214</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>8188</v>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Фундамент Ужгород Стефанія</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>73926</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
-        <f>E9-F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E10" s="13">
-        <f>SUM(E2:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="13">
-        <f>SUM(F2:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="13">
-        <f>SUM(G2:G9)</f>
+      <c r="E6" s="13">
+        <f>SUM(E2:E5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="13">
+        <f>SUM(F2:F5)</f>
+        <v/>
+      </c>
+      <c r="G6" s="13">
+        <f>SUM(G2:G5)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>2611641.36</v>
+        <v>2606583.96</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>2611641.36</v>
+        <v>2606583.96</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>5308592</v>
+        <v>5298312</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>5308592</v>
+        <v>5298312</v>
       </c>
       <c r="H12" s="11">
         <f>F12-G12</f>
@@ -1170,16 +1170,16 @@
         <v>46161</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>7002</v>
+        <v>8438</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>1015173.12</v>
+        <v>758160</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>1015173.12</v>
+        <v>758160</v>
       </c>
       <c r="H13" s="11">
         <f>F13-G13</f>
@@ -1211,31 +1211,31 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>8438</v>
+        <v>7536</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F14" s="10" t="n">
-        <v>758160</v>
+        <v>200000</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>758160</v>
+        <v>200000</v>
       </c>
       <c r="H14" s="11">
         <f>F14-G14</f>
@@ -1255,14 +1255,14 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>7536</v>
+        <v>8238</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
+          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1272,14 +1272,14 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>200000</v>
+        <v>2011000</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>200000</v>
+        <v>2011000</v>
       </c>
       <c r="H15" s="11">
         <f>F15-G15</f>
@@ -1299,14 +1299,14 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>8238</v>
+        <v>7536</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
+          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -1316,14 +1316,14 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>2011000</v>
+        <v>67972.8</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>2011000</v>
+        <v>67972.8</v>
       </c>
       <c r="H16" s="11">
         <f>F16-G16</f>
@@ -1343,31 +1343,31 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>6704</v>
+        <v>7508</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>4618423.4</v>
+        <v>1245999.94</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0</v>
+        <v>1245999.94</v>
       </c>
       <c r="H17" s="11">
         <f>F17-G17</f>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1383,39 +1383,35 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>€89 435</t>
-        </is>
-      </c>
+      <c r="K17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>7536</v>
+        <v>7508</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>67972.8</v>
+        <v>751000.0600000001</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>67972.8</v>
+        <v>751000.0600000001</v>
       </c>
       <c r="H18" s="11">
         <f>F18-G18</f>
@@ -1435,14 +1431,14 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>7508</v>
+        <v>8140</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>В Газинвестпроект фундамент Киев</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -1456,10 +1452,10 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>1245999.94</v>
+        <v>150000</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>1245999.94</v>
+        <v>150000</v>
       </c>
       <c r="H19" s="11">
         <f>F19-G19</f>
@@ -1479,31 +1475,31 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>7508</v>
+        <v>6842</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>751000.0600000001</v>
+        <v>3308968</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>751000.0600000001</v>
+        <v>3308968</v>
       </c>
       <c r="H20" s="11">
         <f>F20-G20</f>
@@ -1523,19 +1519,19 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>8140</v>
+        <v>7960</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>В Газинвестпроект фундамент Киев</t>
+          <t>Сірокко Sirocco вітрова ел ст Львів</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1544,10 +1540,10 @@
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>150000</v>
+        <v>99610.8</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>150000</v>
+        <v>99610.8</v>
       </c>
       <c r="H21" s="11">
         <f>F21-G21</f>
@@ -1570,16 +1566,16 @@
         <v>46169</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>6842</v>
+        <v>8454</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Олександр каркасний Верховина</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1588,10 +1584,10 @@
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>3308968</v>
+        <v>103606.2</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>3308968</v>
+        <v>103606.2</v>
       </c>
       <c r="H22" s="11">
         <f>F22-G22</f>
@@ -1611,14 +1607,14 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>7960</v>
+        <v>8188</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Сірокко Sirocco вітрова ел ст Львів</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -1632,10 +1628,10 @@
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>99610.8</v>
+        <v>206200</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>99610.8</v>
+        <v>206200</v>
       </c>
       <c r="H23" s="11">
         <f>F23-G23</f>
@@ -1655,7 +1651,7 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>8454</v>
@@ -1672,14 +1668,14 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>103606.2</v>
+        <v>69666</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>103606.2</v>
+        <v>69666</v>
       </c>
       <c r="H24" s="11">
         <f>F24-G24</f>
@@ -1702,16 +1698,16 @@
         <v>46170</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>8188</v>
+        <v>8544</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Isolar фланець Хмельницький</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -1720,10 +1716,10 @@
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>206200</v>
+        <v>261990</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>206200</v>
+        <v>261990</v>
       </c>
       <c r="H25" s="11">
         <f>F25-G25</f>
@@ -1743,31 +1739,31 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>8454</v>
+        <v>5682</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Олександр каркасний Верховина</t>
+          <t>А Сцена Корчин</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>69666</v>
+        <v>87150</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>69666</v>
+        <v>87150</v>
       </c>
       <c r="H26" s="11">
         <f>F26-G26</f>
@@ -1780,21 +1776,21 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>8544</v>
+        <v>8185</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Isolar фланець Хмельницький</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -1808,10 +1804,10 @@
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>261990</v>
+        <v>168024</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>261990</v>
+        <v>168024</v>
       </c>
       <c r="H27" s="11">
         <f>F27-G27</f>
@@ -1824,26 +1820,26 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>5682</v>
+        <v>7894</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>А Сцена Корчин</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1852,10 +1848,10 @@
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>87150</v>
+        <v>1487743.97</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>87150</v>
+        <v>1487743.97</v>
       </c>
       <c r="H28" s="11">
         <f>F28-G28</f>
@@ -1875,14 +1871,14 @@
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>8185</v>
+        <v>8544</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>Isolar фланець Хмельницький</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -1892,14 +1888,14 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>168024</v>
+        <v>7990.8</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>168024</v>
+        <v>7990.8</v>
       </c>
       <c r="H29" s="11">
         <f>F29-G29</f>
@@ -1919,14 +1915,14 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>7894</v>
+        <v>3456</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1936,14 +1932,14 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1487743.97</v>
+        <v>783940.92</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>1487743.97</v>
+        <v>783940.92</v>
       </c>
       <c r="H30" s="11">
         <f>F30-G30</f>
@@ -1963,14 +1959,14 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>8544</v>
+        <v>8360</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Isolar фланець Хмельницький</t>
+          <t>Хаджет Лебедівка</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -1984,10 +1980,10 @@
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>7990.8</v>
+        <v>95968.3</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>7990.8</v>
+        <v>95968.3</v>
       </c>
       <c r="H31" s="11">
         <f>F31-G31</f>
@@ -2007,31 +2003,31 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>3456</v>
+        <v>7474</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>А Головне управління Національної поліції в Одеській області  SCP  15PS</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>783940.92</v>
+        <v>1749999</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>783940.92</v>
+        <v>1749999</v>
       </c>
       <c r="H32" s="11">
         <f>F32-G32</f>
@@ -2051,19 +2047,19 @@
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
-        <v>46184</v>
+        <v>46187</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>8360</v>
+        <v>8140</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Хаджет Лебедівка</t>
+          <t>В Газинвестпроект фундамент Киев</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2072,10 +2068,10 @@
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>95968.3</v>
+        <v>86041.2</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>95968.3</v>
+        <v>86041.2</v>
       </c>
       <c r="H33" s="11">
         <f>F33-G33</f>
@@ -2095,14 +2091,14 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>7474</v>
+        <v>6406</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>А Головне управління Національної поліції в Одеській області  SCP  15PS</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
@@ -2112,14 +2108,14 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F34" s="10" t="n">
-        <v>1749999</v>
+        <v>154980</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>1749999</v>
+        <v>154980</v>
       </c>
       <c r="H34" s="11">
         <f>F34-G34</f>
@@ -2139,19 +2135,19 @@
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>46187</v>
+        <v>46190</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>8140</v>
+        <v>8008</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>В Газинвестпроект фундамент Киев</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2160,10 +2156,10 @@
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>86041.2</v>
+        <v>178088.4</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>86041.2</v>
+        <v>178088.4</v>
       </c>
       <c r="H35" s="11">
         <f>F35-G35</f>
@@ -2183,19 +2179,19 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>6406</v>
+        <v>8644</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Solars ГШ 1,7+надставки 3,5</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2204,10 +2200,10 @@
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>154980</v>
+        <v>415900</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>154980</v>
+        <v>415900</v>
       </c>
       <c r="H36" s="11">
         <f>F36-G36</f>
@@ -2227,19 +2223,19 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>8008</v>
+        <v>5682</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>А Сцена Корчин</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2248,10 +2244,10 @@
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>178088.4</v>
+        <v>369984.96</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>178088.4</v>
+        <v>369984.96</v>
       </c>
       <c r="H37" s="11">
         <f>F37-G37</f>
@@ -2271,31 +2267,31 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>8644</v>
+        <v>7068</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Solars ГШ 1,7+надставки 3,5</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>415900</v>
+        <v>0</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>415900</v>
+        <v>1153420</v>
       </c>
       <c r="H38" s="11">
         <f>F38-G38</f>
@@ -2303,7 +2299,7 @@
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2315,31 +2311,31 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>5682</v>
+        <v>8360</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>А Сцена Корчин</t>
+          <t>Хаджет Лебедівка</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>369984.96</v>
+        <v>95968.3</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>369984.96</v>
+        <v>95968.3</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2359,19 +2355,19 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>7068</v>
+        <v>6704</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -2380,10 +2376,10 @@
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>0</v>
+        <v>1907134.62</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>1153420</v>
+        <v>1907134.62</v>
       </c>
       <c r="H40" s="11">
         <f>F40-G40</f>
@@ -2391,7 +2387,7 @@
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2399,35 +2395,39 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="K40" s="12" t="inlineStr"/>
+      <c r="K40" s="12" t="inlineStr">
+        <is>
+          <t>€37 003</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="B41" s="9" t="n">
-        <v>8360</v>
+        <v>4766</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Хаджет Лебедівка</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>95968.3</v>
+        <v>20000</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>95968.3</v>
+        <v>20000</v>
       </c>
       <c r="H41" s="11">
         <f>F41-G41</f>
@@ -2440,38 +2440,38 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>6704</v>
+        <v>8878</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1910834.92</v>
+        <v>410320</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>1910834.92</v>
+        <v>410320</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2484,42 +2484,38 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="K42" s="12" t="inlineStr">
-        <is>
-          <t>€37 003</t>
-        </is>
-      </c>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B43" s="9" t="n">
-        <v>5870</v>
+        <v>8008</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>7834872.44</v>
+        <v>178088.4</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>0</v>
+        <v>178088.4</v>
       </c>
       <c r="H43" s="11">
         <f>F43-G43</f>
@@ -2527,47 +2523,43 @@
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="K43" s="12" t="inlineStr">
-        <is>
-          <t>€151 721</t>
-        </is>
-      </c>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>4766</v>
+        <v>8454</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Олександр каркасний Верховина</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>20000</v>
+        <v>69666</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>20000</v>
+        <v>69666</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -2587,19 +2579,19 @@
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>8878</v>
+        <v>8496</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>А Greensource  SGM  110MWp</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2608,10 +2600,10 @@
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>410320</v>
+        <v>453552</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>410320</v>
+        <v>453552</v>
       </c>
       <c r="H45" s="11">
         <f>F45-G45</f>
@@ -2627,18 +2619,22 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr"/>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>€8 800</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>8008</v>
+        <v>8898</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
@@ -2648,14 +2644,14 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F46" s="10" t="n">
-        <v>178088.4</v>
+        <v>290403.65</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>178088.4</v>
+        <v>290403.65</v>
       </c>
       <c r="H46" s="11">
         <f>F46-G46</f>
@@ -2675,31 +2671,31 @@
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>8454</v>
+        <v>4766</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Олександр каркасний Верховина</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>69666</v>
+        <v>100000</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>69666</v>
+        <v>100000</v>
       </c>
       <c r="H47" s="11">
         <f>F47-G47</f>
@@ -2719,31 +2715,31 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>8496</v>
+        <v>8185</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>А Greensource  SGM  110MWp</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
-        <v>454432</v>
+        <v>63313.4</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>454432</v>
+        <v>63313.4</v>
       </c>
       <c r="H48" s="11">
         <f>F48-G48</f>
@@ -2759,22 +2755,18 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>€8 800</t>
-        </is>
-      </c>
+      <c r="K48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>8898</v>
+        <v>8185</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2784,14 +2776,14 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>290403.65</v>
+        <v>63313.4</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>290403.65</v>
+        <v>63313.4</v>
       </c>
       <c r="H49" s="11">
         <f>F49-G49</f>
@@ -2811,31 +2803,31 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>4766</v>
+        <v>6352</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>100000</v>
+        <v>80000.03999999999</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>100000</v>
+        <v>80000.03999999999</v>
       </c>
       <c r="H50" s="11">
         <f>F50-G50</f>
@@ -2855,14 +2847,14 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>8185</v>
+        <v>7002</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -2872,14 +2864,14 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>63313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>63313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="H51" s="11">
         <f>F51-G51</f>
@@ -2899,14 +2891,14 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>8185</v>
+        <v>7002</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -2920,10 +2912,10 @@
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>63313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>63313.4</v>
+        <v>126896.64</v>
       </c>
       <c r="H52" s="11">
         <f>F52-G52</f>
@@ -2946,11 +2938,11 @@
         <v>46219</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>6352</v>
+        <v>7002</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2960,14 +2952,14 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>80000.03999999999</v>
+        <v>573945</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>80000.03999999999</v>
+        <v>573945</v>
       </c>
       <c r="H53" s="11">
         <f>F53-G53</f>
@@ -2987,31 +2979,31 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>7002</v>
+        <v>4766</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>126896.64</v>
+        <v>4368478.98</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>126896.64</v>
+        <v>4368478.98</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3031,14 +3023,14 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>7002</v>
+        <v>5910</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -3048,14 +3040,14 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>126896.64</v>
+        <v>8611818.6</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>126896.64</v>
+        <v>8611818.6</v>
       </c>
       <c r="H55" s="11">
         <f>F55-G55</f>
@@ -3071,35 +3063,39 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K55" s="12" t="inlineStr"/>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>€167 090</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46219</v>
+        <v>46230</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>7002</v>
+        <v>6312</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>-26 ГШ Фундамент домобудування Георгій</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>573945</v>
+        <v>543429</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>573945</v>
+        <v>543429</v>
       </c>
       <c r="H56" s="11">
         <f>F56-G56</f>
@@ -3119,14 +3115,14 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46224</v>
+        <v>46231</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>4766</v>
+        <v>6130</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -3136,14 +3132,14 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4368478.98</v>
+        <v>56056</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4368478.98</v>
+        <v>56056</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3163,31 +3159,31 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>5910</v>
+        <v>6130</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>8628527.6</v>
+        <v>50964</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>8628527.6</v>
+        <v>50964</v>
       </c>
       <c r="H58" s="11">
         <f>F58-G58</f>
@@ -3203,22 +3199,18 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K58" s="12" t="inlineStr">
-        <is>
-          <t>€167 090</t>
-        </is>
-      </c>
+      <c r="K58" s="12" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>6312</v>
+        <v>6130</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Георгій</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -3228,14 +3220,14 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>543429</v>
+        <v>75762</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>543429</v>
+        <v>75762</v>
       </c>
       <c r="H59" s="11">
         <f>F59-G59</f>
@@ -3255,31 +3247,31 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>6130</v>
+        <v>7068</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>56056</v>
+        <v>0</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>56056</v>
+        <v>2794670</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3287,7 +3279,7 @@
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3299,7 +3291,7 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B61" s="9" t="n">
         <v>6130</v>
@@ -3316,14 +3308,14 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>50964</v>
+        <v>36665</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>50964</v>
+        <v>36665</v>
       </c>
       <c r="H61" s="11">
         <f>F61-G61</f>
@@ -3336,38 +3328,38 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K61" s="12" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>6130</v>
+        <v>6352</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>75762</v>
+        <v>1399046.58</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>75762</v>
+        <v>1399046.58</v>
       </c>
       <c r="H62" s="11">
         <f>F62-G62</f>
@@ -3380,38 +3372,38 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>7068</v>
+        <v>4766</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>0</v>
+        <v>64050</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>2794670</v>
+        <v>64050</v>
       </c>
       <c r="H63" s="11">
         <f>F63-G63</f>
@@ -3419,43 +3411,43 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K63" s="12" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>6130</v>
+        <v>8188</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>36665</v>
+        <v>73926</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>36665</v>
+        <v>0</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3463,7 +3455,7 @@
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3475,31 +3467,31 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>6352</v>
+        <v>8878</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>1399046.58</v>
+        <v>12823</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>1399046.58</v>
+        <v>0</v>
       </c>
       <c r="H65" s="11">
         <f>F65-G65</f>
@@ -3507,7 +3499,7 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3519,14 +3511,14 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>8188</v>
+        <v>6406</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -3540,7 +3532,7 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>73926</v>
+        <v>218602</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3551,7 +3543,7 @@
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3563,31 +3555,31 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>4766</v>
+        <v>7894</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>64050</v>
+        <v>185968</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>64050</v>
+        <v>0</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3595,7 +3587,7 @@
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3607,7 +3599,7 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B68" s="9" t="n">
         <v>7894</v>
@@ -3624,11 +3616,11 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>185968</v>
+        <v>185967.99</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3651,28 +3643,28 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>8878</v>
+        <v>8898</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>12823</v>
+        <v>188043.75</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0</v>
@@ -3695,14 +3687,14 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46245</v>
+        <v>46258</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>7894</v>
+        <v>3456</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -3716,7 +3708,7 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>185967.99</v>
+        <v>335974.68</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -3739,31 +3731,31 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>46247</v>
+        <v>46258</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>6406</v>
+        <v>5910</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>218602</v>
+        <v>17223688.74</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>0</v>
+        <v>2959426.8</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3779,18 +3771,22 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K71" s="12" t="inlineStr"/>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46248</v>
+        <v>46258</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>8898</v>
+        <v>6352</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -3800,11 +3796,11 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>188043.75</v>
+        <v>1119237.26</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>0</v>
@@ -3827,19 +3823,19 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>3456</v>
+        <v>6704</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
@@ -3848,7 +3844,7 @@
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>335974.68</v>
+        <v>4609479.9</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -3867,35 +3863,39 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K73" s="12" t="inlineStr"/>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>€89 435</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>5910</v>
+        <v>5870</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>17257106.84</v>
+        <v>7819700.34</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>2965168.8</v>
+        <v>0</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3913,37 +3913,37 @@
       </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
-          <t>€334 181</t>
+          <t>€151 721</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>6352</v>
+        <v>6130</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1119237.26</v>
+        <v>73335</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="H75" s="11">
         <f>F75-G75</f>
@@ -3963,19 +3963,19 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>7002</v>
+        <v>7244</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>573945</v>
+        <v>132708.6</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4007,14 +4007,14 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>6130</v>
+        <v>4766</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>73335</v>
+        <v>1263447.42</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>36665</v>
+        <v>0</v>
       </c>
       <c r="H77" s="11">
         <f>F77-G77</f>
@@ -4044,35 +4044,35 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K77" s="12" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>7244</v>
+        <v>5910</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>132708.6</v>
+        <v>2870468.76</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4088,26 +4088,30 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="K78" s="12" t="inlineStr"/>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K78" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -4116,7 +4120,7 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>1263447.42</v>
+        <v>573945</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4139,14 +4143,14 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46267</v>
+        <v>46280</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>5910</v>
+        <v>8898</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -4160,7 +4164,7 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>2876038.16</v>
+        <v>188043.75</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4179,27 +4183,23 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K80" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K80" s="12" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>8898</v>
+        <v>7508</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>188043.75</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46282</v>
+        <v>46291</v>
       </c>
       <c r="B82" s="9" t="n">
         <v>7894</v>
@@ -4275,28 +4275,28 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46283</v>
+        <v>46308</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>7508</v>
+        <v>6352</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>371982.96</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4312,14 +4312,14 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K83" s="12" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46308</v>
+        <v>46321</v>
       </c>
       <c r="B84" s="9" t="n">
         <v>6352</v>
@@ -4336,11 +4336,11 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>371982.96</v>
+        <v>651792.28</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4362,70 +4362,26 @@
       <c r="K84" s="12" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B85" s="9" t="n">
-        <v>6352</v>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>АБМК SCP Blade 8PS</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>Донська</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>П'ятий платіж</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="n">
-        <v>651792.28</v>
-      </c>
-      <c r="G85" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="11">
-        <f>F85-G85</f>
-        <v/>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>очікується</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K85" s="12" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F86" s="13">
-        <f>SUM(F2:F85)</f>
-        <v/>
-      </c>
-      <c r="G86" s="13">
-        <f>SUM(G2:G85)</f>
-        <v/>
-      </c>
-      <c r="H86" s="13">
-        <f>SUM(H2:H85)</f>
+      <c r="F85" s="13">
+        <f>SUM(F2:F84)</f>
+        <v/>
+      </c>
+      <c r="G85" s="13">
+        <f>SUM(G2:G84)</f>
+        <v/>
+      </c>
+      <c r="H85" s="13">
+        <f>SUM(H2:H84)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I85"/>
+  <autoFilter ref="A1:I84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4668,7 +4624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4719,26 +4675,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46203</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5870</v>
+        <v>7068</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>7834872.44</v>
+        <v>5640128</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>0</v>
+        <v>1692038</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -4747,23 +4703,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46165</v>
+        <v>46238</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6704</v>
+        <v>8188</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4618423.4</v>
+        <v>73926</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -4774,82 +4730,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>7068</v>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>А Remtec energy  AGM  160 TP</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>Авансовий платіж</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>5640128</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>1692038</v>
-      </c>
-      <c r="G4" s="11">
-        <f>E4-F4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>46238</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>8188</v>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Фундамент Ужгород Стефанія</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>73926</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="11">
-        <f>E5-F5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E6" s="13">
-        <f>SUM(E2:E5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="13">
-        <f>SUM(F2:F5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>SUM(G2:G5)</f>
+      <c r="E4" s="13">
+        <f>SUM(E2:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="13">
+        <f>SUM(F2:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="13">
+        <f>SUM(G2:G3)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 05.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 06.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>2606583.96</v>
+        <v>2611135.62</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>2606583.96</v>
+        <v>2611135.62</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>5298312</v>
+        <v>5307564</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>5298312</v>
+        <v>5307564</v>
       </c>
       <c r="H12" s="11">
         <f>F12-G12</f>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>1907134.62</v>
+        <v>1910464.89</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>1907134.62</v>
+        <v>1910464.89</v>
       </c>
       <c r="H40" s="11">
         <f>F40-G40</f>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>453552</v>
+        <v>454344</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>453552</v>
+        <v>454344</v>
       </c>
       <c r="H45" s="11">
         <f>F45-G45</f>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>8611818.6</v>
+        <v>8626856.700000001</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>8611818.6</v>
+        <v>8626856.700000001</v>
       </c>
       <c r="H55" s="11">
         <f>F55-G55</f>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>17223688.74</v>
+        <v>17253765.03</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>2959426.8</v>
+        <v>2964594.6</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3844,7 +3844,7 @@
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>4609479.9</v>
+        <v>4617529.05</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>7819700.34</v>
+        <v>7833355.23</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2870468.76</v>
+        <v>2875481.22</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 06.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 07.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -573,9 +572,10 @@
           <t>Прострочені надходження, ₴</t>
         </is>
       </c>
-      <c r="B8" s="4">
-        <f>SUMIF('Прострочені'!A:A,"&lt;&gt;",'Прострочені'!G:G)</f>
-        <v/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -675,19 +675,19 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46113</v>
+        <v>46128</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>7068</v>
+        <v>8070</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>А Карпорты B2C  SCP</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="F2" s="10" t="n">
-        <v>5640128</v>
+        <v>126641</v>
       </c>
       <c r="G2" s="10" t="n">
-        <v>1692038</v>
+        <v>126641</v>
       </c>
       <c r="H2" s="11">
         <f>F2-G2</f>
@@ -707,7 +707,7 @@
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,19 +719,19 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46128</v>
+        <v>46133</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>8070</v>
+        <v>7244</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>А Карпорты B2C  SCP</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>126641</v>
+        <v>77600</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>126641</v>
+        <v>77600</v>
       </c>
       <c r="H3" s="11">
         <f>F3-G3</f>
@@ -763,19 +763,19 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7244</v>
+        <v>7536</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="F4" s="10" t="n">
-        <v>77600</v>
+        <v>244374</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>77600</v>
+        <v>244374</v>
       </c>
       <c r="H4" s="11">
         <f>F4-G4</f>
@@ -807,19 +807,19 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46139</v>
+        <v>46147</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>7536</v>
+        <v>3456</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="F5" s="10" t="n">
-        <v>244374</v>
+        <v>421968</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>244374</v>
+        <v>421968</v>
       </c>
       <c r="H5" s="11">
         <f>F5-G5</f>
@@ -844,38 +844,38 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>3456</v>
+        <v>7536</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>421968</v>
+        <v>200000</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>421968</v>
+        <v>200000</v>
       </c>
       <c r="H6" s="11">
         <f>F6-G6</f>
@@ -895,31 +895,31 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>7536</v>
+        <v>8360</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
+          <t>Хаджет Лебедівка</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>200000</v>
+        <v>231000</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>200000</v>
+        <v>231000</v>
       </c>
       <c r="H7" s="11">
         <f>F7-G7</f>
@@ -939,31 +939,31 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>8360</v>
+        <v>7536</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Хаджет Лебедівка</t>
+          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>231000</v>
+        <v>200000</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>231000</v>
+        <v>200000</v>
       </c>
       <c r="H8" s="11">
         <f>F8-G8</f>
@@ -983,31 +983,31 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>7536</v>
+        <v>8008</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>А Ранчо “Едельвейс”  AGM  171PV</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
-        <v>200000</v>
+        <v>430850.64</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>200000</v>
+        <v>430850.64</v>
       </c>
       <c r="H9" s="11">
         <f>F9-G9</f>
@@ -1027,19 +1027,19 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>8008</v>
+        <v>5870</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>430850.64</v>
+        <v>2583500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>430850.64</v>
+        <v>2583500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1067,18 +1067,22 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>€50 000</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
         <v>46161</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>5870</v>
+        <v>6704</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -1092,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>2611135.62</v>
+        <v>5167000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>2611135.62</v>
+        <v>5167000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -1113,7 +1117,7 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>€50 574</t>
+          <t>€100 000</t>
         </is>
       </c>
     </row>
@@ -1122,16 +1126,16 @@
         <v>46161</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>6704</v>
+        <v>7068</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>А Remtec energy  AGM  160 TP</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1140,10 +1144,10 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>5307564</v>
+        <v>2416856</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>5307564</v>
+        <v>2416856</v>
       </c>
       <c r="H12" s="11">
         <f>F12-G12</f>
@@ -1159,11 +1163,7 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t>€102 800</t>
-        </is>
-      </c>
+      <c r="K12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -2270,28 +2270,28 @@
         <v>46197</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>7068</v>
+        <v>8360</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>Хаджет Лебедівка</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>0</v>
+        <v>95968.3</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>1153420</v>
+        <v>95968.3</v>
       </c>
       <c r="H38" s="11">
         <f>F38-G38</f>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2311,31 +2311,31 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>8360</v>
+        <v>6704</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Хаджет Лебедівка</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>95968.3</v>
+        <v>1860120</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>95968.3</v>
+        <v>1860120</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2351,35 +2351,39 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="K39" s="12" t="inlineStr"/>
+      <c r="K39" s="12" t="inlineStr">
+        <is>
+          <t>€36 000</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>6704</v>
+        <v>4766</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>1910464.89</v>
+        <v>20000</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>1910464.89</v>
+        <v>20000</v>
       </c>
       <c r="H40" s="11">
         <f>F40-G40</f>
@@ -2392,25 +2396,21 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="K40" s="12" t="inlineStr">
-        <is>
-          <t>€37 003</t>
-        </is>
-      </c>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B41" s="9" t="n">
-        <v>4766</v>
+        <v>8878</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>20000</v>
+        <v>410320</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>20000</v>
+        <v>410320</v>
       </c>
       <c r="H41" s="11">
         <f>F41-G41</f>
@@ -2447,31 +2447,31 @@
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>8878</v>
+        <v>8008</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>Модулі Григорівка</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>410320</v>
+        <v>178088.4</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>410320</v>
+        <v>178088.4</v>
       </c>
       <c r="H42" s="11">
         <f>F42-G42</f>
@@ -2491,14 +2491,14 @@
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="B43" s="9" t="n">
-        <v>8008</v>
+        <v>8454</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Модулі Григорівка</t>
+          <t>Олександр каркасний Верховина</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>178088.4</v>
+        <v>69666</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>178088.4</v>
+        <v>69666</v>
       </c>
       <c r="H43" s="11">
         <f>F43-G43</f>
@@ -2535,31 +2535,31 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>8454</v>
+        <v>8496</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Олександр каркасний Верховина</t>
+          <t>А Greensource  SGM  110MWp</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>69666</v>
+        <v>454696</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>69666</v>
+        <v>454696</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -2575,23 +2575,27 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K44" s="12" t="inlineStr"/>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>€8 800</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
         <v>46216</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>8496</v>
+        <v>8898</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>А Greensource  SGM  110MWp</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2600,10 +2604,10 @@
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>454344</v>
+        <v>290403.65</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>454344</v>
+        <v>290403.65</v>
       </c>
       <c r="H45" s="11">
         <f>F45-G45</f>
@@ -2619,39 +2623,35 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>€8 800</t>
-        </is>
-      </c>
+      <c r="K45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>8898</v>
+        <v>4766</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F46" s="10" t="n">
-        <v>290403.65</v>
+        <v>100000</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>290403.65</v>
+        <v>100000</v>
       </c>
       <c r="H46" s="11">
         <f>F46-G46</f>
@@ -2674,16 +2674,16 @@
         <v>46217</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>4766</v>
+        <v>8185</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фундамент Hytte House Development Славське</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>100000</v>
+        <v>63313.4</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>100000</v>
+        <v>63313.4</v>
       </c>
       <c r="H47" s="11">
         <f>F47-G47</f>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
@@ -2759,14 +2759,14 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>8185</v>
+        <v>6352</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Hytte House Development Славське</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2776,14 +2776,14 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>63313.4</v>
+        <v>80000.03999999999</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>63313.4</v>
+        <v>80000.03999999999</v>
       </c>
       <c r="H49" s="11">
         <f>F49-G49</f>
@@ -2806,11 +2806,11 @@
         <v>46219</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>6352</v>
+        <v>7002</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>80000.03999999999</v>
+        <v>126896.64</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>80000.03999999999</v>
+        <v>126896.64</v>
       </c>
       <c r="H50" s="11">
         <f>F50-G50</f>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F51" s="10" t="n">
@@ -2908,14 +2908,14 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>126896.64</v>
+        <v>573945</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>126896.64</v>
+        <v>573945</v>
       </c>
       <c r="H52" s="11">
         <f>F52-G52</f>
@@ -2935,31 +2935,31 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>7002</v>
+        <v>4766</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>573945</v>
+        <v>4368478.98</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>573945</v>
+        <v>4368478.98</v>
       </c>
       <c r="H53" s="11">
         <f>F53-G53</f>
@@ -2979,31 +2979,31 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>4368478.98</v>
+        <v>8633540.300000001</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>4368478.98</v>
+        <v>8633540.300000001</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3019,23 +3019,27 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K54" s="12" t="inlineStr"/>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>€167 090</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>5910</v>
+        <v>6312</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>-26 ГШ Фундамент домобудування Георгій</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -3044,10 +3048,10 @@
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>8626856.700000001</v>
+        <v>543429</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>8626856.700000001</v>
+        <v>543429</v>
       </c>
       <c r="H55" s="11">
         <f>F55-G55</f>
@@ -3063,22 +3067,18 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K55" s="12" t="inlineStr">
-        <is>
-          <t>€167 090</t>
-        </is>
-      </c>
+      <c r="K55" s="12" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>6312</v>
+        <v>6130</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Георгій</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>543429</v>
+        <v>56056</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>543429</v>
+        <v>56056</v>
       </c>
       <c r="H56" s="11">
         <f>F56-G56</f>
@@ -3118,28 +3118,28 @@
         <v>46231</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>6130</v>
+        <v>6704</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>SCP Taurus 236PS</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>56056</v>
+        <v>4066429</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>56056</v>
+        <v>4066429</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3155,7 +3155,11 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="K57" s="12" t="inlineStr"/>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>€78 700</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
@@ -3247,31 +3251,31 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>7068</v>
+        <v>6130</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>А Remtec energy  AGM  160 TP</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Александров</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>2794670</v>
+        <v>36665</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3279,12 +3283,12 @@
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K60" s="12" t="inlineStr"/>
@@ -3294,28 +3298,28 @@
         <v>46237</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>6130</v>
+        <v>6352</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>36665</v>
+        <v>1399046.58</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>36665</v>
+        <v>1399046.58</v>
       </c>
       <c r="H61" s="11">
         <f>F61-G61</f>
@@ -3335,31 +3339,31 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>6352</v>
+        <v>4766</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>1399046.58</v>
+        <v>64050</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>1399046.58</v>
+        <v>64050</v>
       </c>
       <c r="H62" s="11">
         <f>F62-G62</f>
@@ -3382,28 +3386,28 @@
         <v>46238</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>4766</v>
+        <v>8188</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>64050</v>
+        <v>73926</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>64050</v>
+        <v>75926</v>
       </c>
       <c r="H63" s="11">
         <f>F63-G63</f>
@@ -3423,19 +3427,19 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>8188</v>
+        <v>5870</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3444,10 +3448,10 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>73926</v>
+        <v>4946110.75</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>0</v>
+        <v>4946110.75</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3455,7 +3459,7 @@
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3463,7 +3467,11 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K64" s="12" t="inlineStr"/>
+      <c r="K64" s="12" t="inlineStr">
+        <is>
+          <t>€95 725</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
@@ -3602,16 +3610,16 @@
         <v>46248</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>7894</v>
+        <v>5870</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3620,7 +3628,7 @@
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>185967.99</v>
+        <v>1657315.25</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3639,18 +3647,22 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K68" s="12" t="inlineStr"/>
+      <c r="K68" s="12" t="inlineStr">
+        <is>
+          <t>€32 075</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>8898</v>
+        <v>7894</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -3660,11 +3672,11 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>188043.75</v>
+        <v>185967.99</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0</v>
@@ -3687,14 +3699,14 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>3456</v>
+        <v>8898</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -3704,11 +3716,11 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>335974.68</v>
+        <v>188043.75</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -3734,11 +3746,11 @@
         <v>46258</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>5910</v>
+        <v>3456</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -3748,14 +3760,14 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>17253765.03</v>
+        <v>335974.68</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>2964594.6</v>
+        <v>0</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3771,22 +3783,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K71" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K71" s="12" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
         <v>46258</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>6352</v>
+        <v>5910</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -3796,14 +3804,14 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>1119237.26</v>
+        <v>17267132.27</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>0</v>
+        <v>2966891.4</v>
       </c>
       <c r="H72" s="11">
         <f>F72-G72</f>
@@ -3819,23 +3827,27 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K72" s="12" t="inlineStr"/>
+      <c r="K72" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46263</v>
+        <v>46258</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>6704</v>
+        <v>6352</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>SCP Taurus 236PS</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
@@ -3844,7 +3856,7 @@
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>4617529.05</v>
+        <v>1119237.26</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -3863,39 +3875,35 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K73" s="12" t="inlineStr">
-        <is>
-          <t>€89 435</t>
-        </is>
-      </c>
+      <c r="K73" s="12" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>5870</v>
+        <v>6130</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>7833355.23</v>
+        <v>73335</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3911,22 +3919,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K74" s="12" t="inlineStr">
-        <is>
-          <t>€151 721</t>
-        </is>
-      </c>
+      <c r="K74" s="12" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
         <v>46265</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>6130</v>
+        <v>7244</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -3940,10 +3944,10 @@
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>73335</v>
+        <v>132708.6</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>36665</v>
+        <v>0</v>
       </c>
       <c r="H75" s="11">
         <f>F75-G75</f>
@@ -3963,14 +3967,14 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>7244</v>
+        <v>4766</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -3984,7 +3988,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>132708.6</v>
+        <v>1263447.42</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4000,7 +4004,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr"/>
@@ -4010,25 +4014,25 @@
         <v>46267</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>1263447.42</v>
+        <v>2877708.98</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4047,18 +4051,22 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K77" s="12" t="inlineStr"/>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -4068,11 +4076,11 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2875481.22</v>
+        <v>573945</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4091,22 +4099,18 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K78" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K78" s="12" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>7002</v>
+        <v>8898</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4116,11 +4120,11 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>573945</v>
+        <v>188043.75</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4143,19 +4147,19 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>8898</v>
+        <v>7508</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -4164,7 +4168,7 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>188043.75</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4187,28 +4191,28 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46283</v>
+        <v>46291</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>7508</v>
+        <v>7894</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>737597.4</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4231,14 +4235,14 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46291</v>
+        <v>46308</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>7894</v>
+        <v>6352</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -4248,11 +4252,11 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>737597.4</v>
+        <v>371982.96</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4268,14 +4272,14 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K82" s="12" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46308</v>
+        <v>46321</v>
       </c>
       <c r="B83" s="9" t="n">
         <v>6352</v>
@@ -4292,11 +4296,11 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>371982.96</v>
+        <v>651792.28</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4318,70 +4322,26 @@
       <c r="K83" s="12" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B84" s="9" t="n">
-        <v>6352</v>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>АБМК SCP Blade 8PS</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>Донська</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>П'ятий платіж</t>
-        </is>
-      </c>
-      <c r="F84" s="10" t="n">
-        <v>651792.28</v>
-      </c>
-      <c r="G84" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="11">
-        <f>F84-G84</f>
-        <v/>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>очікується</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K84" s="12" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F85" s="13">
-        <f>SUM(F2:F84)</f>
-        <v/>
-      </c>
-      <c r="G85" s="13">
-        <f>SUM(G2:G84)</f>
-        <v/>
-      </c>
-      <c r="H85" s="13">
-        <f>SUM(H2:H84)</f>
+      <c r="F84" s="13">
+        <f>SUM(F2:F83)</f>
+        <v/>
+      </c>
+      <c r="G84" s="13">
+        <f>SUM(G2:G83)</f>
+        <v/>
+      </c>
+      <c r="H84" s="13">
+        <f>SUM(H2:H83)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I84"/>
+  <autoFilter ref="A1:I83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4624,7 +4584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4673,83 +4633,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B2" s="9" t="n">
-        <v>7068</v>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>А Remtec energy  AGM  160 TP</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>Авансовий платіж</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="n">
-        <v>5640128</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>1692038</v>
-      </c>
-      <c r="G2" s="11">
-        <f>E2-F2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="n">
-        <v>46238</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>8188</v>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Фундамент Ужгород Стефанія</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>73926</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="11">
-        <f>E3-F3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Разом</t>
-        </is>
-      </c>
-      <c r="E4" s="13">
-        <f>SUM(E2:E3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>SUM(F2:F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>SUM(G2:G3)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,6 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 07.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 11.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -572,10 +573,9 @@
           <t>Прострочені надходження, ₴</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="B8" s="4">
+        <f>SUMIF('Прострочені'!A:A,"&lt;&gt;",'Прострочені'!G:G)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2583500</v>
+        <v>2589000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2583500</v>
+        <v>2589000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5167000</v>
+        <v>5178000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5167000</v>
+        <v>5178000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1860120</v>
+        <v>1864080</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1860120</v>
+        <v>1864080</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>454696</v>
+        <v>455664</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>454696</v>
+        <v>455664</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8633540.300000001</v>
+        <v>8651920.200000001</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8633540.300000001</v>
+        <v>8651920.200000001</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4066429</v>
+        <v>4075086</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4066429</v>
+        <v>4075086</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4946110.75</v>
+        <v>4956640.5</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>4946110.75</v>
+        <v>4956640.5</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3563,28 +3563,28 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>7894</v>
+        <v>5870</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>185968</v>
+        <v>1660843.5</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -3603,32 +3603,36 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K67" s="12" t="inlineStr"/>
+      <c r="K67" s="12" t="inlineStr">
+        <is>
+          <t>€32 075</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>5870</v>
+        <v>8898</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1657315.25</v>
+        <v>188043.75</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3647,22 +3651,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K68" s="12" t="inlineStr">
-        <is>
-          <t>€32 075</t>
-        </is>
-      </c>
+      <c r="K68" s="12" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46248</v>
+        <v>46258</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>7894</v>
+        <v>3456</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>185967.99</v>
+        <v>335974.68</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0</v>
@@ -3699,14 +3699,14 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>8898</v>
+        <v>5910</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>188043.75</v>
+        <v>17303892.18</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>0</v>
+        <v>2973207.6</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3739,18 +3739,22 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K70" s="12" t="inlineStr"/>
+      <c r="K70" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
         <v>46258</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>3456</v>
+        <v>6352</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -3764,7 +3768,7 @@
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>335974.68</v>
+        <v>1119237.26</v>
       </c>
       <c r="G71" s="10" t="n">
         <v>0</v>
@@ -3787,14 +3791,14 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -3804,14 +3808,14 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>17267132.27</v>
+        <v>185968</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>2966891.4</v>
+        <v>0</v>
       </c>
       <c r="H72" s="11">
         <f>F72-G72</f>
@@ -3827,22 +3831,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K72" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K72" s="12" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>6352</v>
+        <v>7894</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>1119237.26</v>
+        <v>185967.99</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>2877708.98</v>
+        <v>2883835.32</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="B81" s="9" t="n">
         <v>7894</v>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr"/>
@@ -4584,7 +4584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4633,7 +4633,55 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="8" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>8878</v>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>12823</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11">
+        <f>E2-F2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="E3" s="13">
+        <f>SUM(E2:E2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="13">
+        <f>SUM(F2:F2)</f>
+        <v/>
+      </c>
+      <c r="G3" s="13">
+        <f>SUM(G2:G2)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Александров</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 11.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 13.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2589000</v>
+        <v>2580500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2589000</v>
+        <v>2580500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5178000</v>
+        <v>5161000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5178000</v>
+        <v>5161000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1864080</v>
+        <v>1857960</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1864080</v>
+        <v>1857960</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>455664</v>
+        <v>454168</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>455664</v>
+        <v>454168</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8651920.200000001</v>
+        <v>8623514.9</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8651920.200000001</v>
+        <v>8623514.9</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4075086</v>
+        <v>4061707</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4075086</v>
+        <v>4061707</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4956640.5</v>
+        <v>4940367.25</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>4956640.5</v>
+        <v>4940367.25</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3475,28 +3475,28 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>8878</v>
+        <v>6406</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>12823</v>
+        <v>218602</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3519,28 +3519,28 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>6406</v>
+        <v>5870</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>218602</v>
+        <v>1655390.75</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3559,32 +3559,36 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K66" s="12" t="inlineStr"/>
+      <c r="K66" s="12" t="inlineStr">
+        <is>
+          <t>€32 075</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>5870</v>
+        <v>8878</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>1660843.5</v>
+        <v>12823</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -3603,11 +3607,7 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K67" s="12" t="inlineStr">
-        <is>
-          <t>€32 075</t>
-        </is>
-      </c>
+      <c r="K67" s="12" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>17303892.18</v>
+        <v>17247081.41</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>2973207.6</v>
+        <v>2963446.2</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>2883835.32</v>
+        <v>2874367.34</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4635,23 +4635,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>8878</v>
+        <v>6406</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>12823</v>
+        <v>218602</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 13.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 14.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2580500</v>
+        <v>2577500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2580500</v>
+        <v>2577500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5161000</v>
+        <v>5155000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5161000</v>
+        <v>5155000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1857960</v>
+        <v>1855800</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1857960</v>
+        <v>1855800</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>454168</v>
+        <v>453640</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>454168</v>
+        <v>453640</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8623514.9</v>
+        <v>8613489.5</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8623514.9</v>
+        <v>8613489.5</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4061707</v>
+        <v>4056985</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4061707</v>
+        <v>4056985</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4940367.25</v>
+        <v>4934623.75</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>4940367.25</v>
+        <v>4934623.75</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>1655390.75</v>
+        <v>1653466.25</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>17247081.41</v>
+        <v>17227030.55</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>2963446.2</v>
+        <v>2960001</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>2874367.34</v>
+        <v>2871025.7</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4584,7 +4584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4635,23 +4635,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>6406</v>
+        <v>5870</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>218602</v>
+        <v>1653466.25</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -4662,26 +4662,54 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11">
+        <f>E3-F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E3" s="13">
-        <f>SUM(E2:E2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="13">
-        <f>SUM(F2:F2)</f>
-        <v/>
-      </c>
-      <c r="G3" s="13">
-        <f>SUM(G2:G2)</f>
+      <c r="E4" s="13">
+        <f>SUM(E2:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="13">
+        <f>SUM(F2:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="13">
+        <f>SUM(G2:G3)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 14.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 17.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -573,9 +572,10 @@
           <t>Прострочені надходження, ₴</t>
         </is>
       </c>
-      <c r="B8" s="4">
-        <f>SUMIF('Прострочені'!A:A,"&lt;&gt;",'Прострочені'!G:G)</f>
-        <v/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2577500</v>
+        <v>2585500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2577500</v>
+        <v>2585500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5155000</v>
+        <v>5171000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5155000</v>
+        <v>5171000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1855800</v>
+        <v>1861560</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1855800</v>
+        <v>1861560</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>453640</v>
+        <v>455048</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>453640</v>
+        <v>455048</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8613489.5</v>
+        <v>8640223.9</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8613489.5</v>
+        <v>8640223.9</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4056985</v>
+        <v>4069577</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4056985</v>
+        <v>4069577</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4934623.75</v>
+        <v>4949939.75</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>4934623.75</v>
+        <v>4949939.75</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3475,19 +3475,19 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>6406</v>
+        <v>8898</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>218602</v>
+        <v>188043.75</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3519,28 +3519,28 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>5870</v>
+        <v>8878</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>1653466.25</v>
+        <v>12823</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3559,36 +3559,32 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K66" s="12" t="inlineStr">
-        <is>
-          <t>€32 075</t>
-        </is>
-      </c>
+      <c r="K66" s="12" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>8878</v>
+        <v>3456</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>12823</v>
+        <v>335974.68</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -3611,14 +3607,14 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>8898</v>
+        <v>6352</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -3628,11 +3624,11 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>188043.75</v>
+        <v>1119237.26</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3655,28 +3651,28 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>3456</v>
+        <v>6406</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>335974.68</v>
+        <v>218602</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0</v>
@@ -3699,7 +3695,7 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B70" s="9" t="n">
         <v>5910</v>
@@ -3720,10 +3716,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>17227030.55</v>
+        <v>17280499.51</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>2960001</v>
+        <v>2969188.2</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3747,14 +3743,14 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>6352</v>
+        <v>7894</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -3764,11 +3760,11 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>1119237.26</v>
+        <v>185968</v>
       </c>
       <c r="G71" s="10" t="n">
         <v>0</v>
@@ -3791,28 +3787,28 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>7894</v>
+        <v>5870</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>185968</v>
+        <v>1658598.25</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>0</v>
@@ -3831,7 +3827,11 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K72" s="12" t="inlineStr"/>
+      <c r="K72" s="12" t="inlineStr">
+        <is>
+          <t>€32 075</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>2871025.7</v>
+        <v>2879936.74</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4584,7 +4584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4633,83 +4633,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="n">
-        <v>46248</v>
-      </c>
-      <c r="B2" s="9" t="n">
-        <v>5870</v>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>Carport Airport Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="n">
-        <v>1653466.25</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="11">
-        <f>E2-F2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="n">
-        <v>46247</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>6406</v>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Максим Яловий Чинадієво</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>218602</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="11">
-        <f>E3-F3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Разом</t>
-        </is>
-      </c>
-      <c r="E4" s="13">
-        <f>SUM(E2:E3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>SUM(F2:F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>SUM(G2:G3)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 17.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 18.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3475,31 +3475,31 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46253</v>
+        <v>46241</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>8898</v>
+        <v>5870</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>188043.75</v>
+        <v>753673.25</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>0</v>
+        <v>753673.25</v>
       </c>
       <c r="H65" s="11">
         <f>F65-G65</f>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3515,32 +3515,36 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K65" s="12" t="inlineStr"/>
+      <c r="K65" s="12" t="inlineStr">
+        <is>
+          <t>€14 575</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>8878</v>
+        <v>8898</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>12823</v>
+        <v>188043.75</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3563,28 +3567,28 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>3456</v>
+        <v>8878</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>335974.68</v>
+        <v>12823</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -3610,11 +3614,11 @@
         <v>46258</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>6352</v>
+        <v>3456</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -3628,7 +3632,7 @@
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1119237.26</v>
+        <v>335974.68</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3651,28 +3655,28 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>6406</v>
+        <v>6352</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>218602</v>
+        <v>1119237.26</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0</v>
@@ -3695,31 +3699,31 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>5910</v>
+        <v>6406</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>17280499.51</v>
+        <v>218602</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>2969188.2</v>
+        <v>0</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3735,22 +3739,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K70" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K70" s="12" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -3760,14 +3760,14 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>185968</v>
+        <v>17280499.51</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>0</v>
+        <v>2969188.2</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3783,32 +3783,36 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K71" s="12" t="inlineStr"/>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>5870</v>
+        <v>7894</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>1658598.25</v>
+        <v>185968</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>0</v>
@@ -3827,11 +3831,7 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K72" s="12" t="inlineStr">
-        <is>
-          <t>€32 075</t>
-        </is>
-      </c>
+      <c r="K72" s="12" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
@@ -3879,31 +3879,31 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>6130</v>
+        <v>5870</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>73335</v>
+        <v>904925</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>36665</v>
+        <v>0</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3919,18 +3919,22 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K74" s="12" t="inlineStr"/>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <t>€17 500</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
         <v>46265</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>7244</v>
+        <v>6130</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -3944,10 +3948,10 @@
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>132708.6</v>
+        <v>73335</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="H75" s="11">
         <f>F75-G75</f>
@@ -3967,14 +3971,14 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>4766</v>
+        <v>7244</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -3988,7 +3992,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>1263447.42</v>
+        <v>132708.6</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4004,7 +4008,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr"/>
@@ -4014,25 +4018,25 @@
         <v>46267</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>2879936.74</v>
+        <v>1263447.42</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4051,22 +4055,18 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K77" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K77" s="12" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>7002</v>
+        <v>5910</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -4076,11 +4076,11 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>573945</v>
+        <v>2879936.74</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4099,18 +4099,22 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K78" s="12" t="inlineStr"/>
+      <c r="K78" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>8898</v>
+        <v>7002</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4120,11 +4124,11 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>188043.75</v>
+        <v>573945</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4147,19 +4151,19 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>7508</v>
+        <v>8898</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -4168,7 +4172,7 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>188043.75</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4191,28 +4195,28 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46297</v>
+        <v>46283</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>7894</v>
+        <v>7508</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>737597.4</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4228,21 +4232,21 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46308</v>
+        <v>46297</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>6352</v>
+        <v>7894</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -4252,11 +4256,11 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>371982.96</v>
+        <v>737597.4</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4279,7 +4283,7 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46321</v>
+        <v>46308</v>
       </c>
       <c r="B83" s="9" t="n">
         <v>6352</v>
@@ -4296,11 +4300,11 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>651792.28</v>
+        <v>371982.96</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4322,26 +4326,70 @@
       <c r="K83" s="12" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="E84" s="3" t="inlineStr">
+      <c r="A84" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B84" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>АБМК SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G84" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="11">
+        <f>F84-G84</f>
+        <v/>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K84" s="12" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F84" s="13">
-        <f>SUM(F2:F83)</f>
-        <v/>
-      </c>
-      <c r="G84" s="13">
-        <f>SUM(G2:G83)</f>
-        <v/>
-      </c>
-      <c r="H84" s="13">
-        <f>SUM(H2:H83)</f>
+      <c r="F85" s="13">
+        <f>SUM(F2:F84)</f>
+        <v/>
+      </c>
+      <c r="G85" s="13">
+        <f>SUM(G2:G84)</f>
+        <v/>
+      </c>
+      <c r="H85" s="13">
+        <f>SUM(H2:H84)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I83"/>
+  <autoFilter ref="A1:I84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,6 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 18.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 19.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -572,10 +573,9 @@
           <t>Прострочені надходження, ₴</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="B8" s="4">
+        <f>SUMIF('Прострочені'!A:A,"&lt;&gt;",'Прострочені'!G:G)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2585500</v>
+        <v>2591500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2585500</v>
+        <v>2591500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5171000</v>
+        <v>5183000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5171000</v>
+        <v>5183000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1861560</v>
+        <v>1865880</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1861560</v>
+        <v>1865880</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>455048</v>
+        <v>456104</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>455048</v>
+        <v>456104</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8640223.9</v>
+        <v>8660274.699999999</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8640223.9</v>
+        <v>8660274.699999999</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4069577</v>
+        <v>4079021</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4069577</v>
+        <v>4079021</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4949939.75</v>
+        <v>4961426.75</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>4949939.75</v>
+        <v>4961426.75</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>753673.25</v>
+        <v>755422.25</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>753673.25</v>
+        <v>755422.25</v>
       </c>
       <c r="H65" s="11">
         <f>F65-G65</f>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>17280499.51</v>
+        <v>17320601.23</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>2969188.2</v>
+        <v>2976078.6</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>904925</v>
+        <v>907025</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>0</v>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2879936.74</v>
+        <v>2886620.02</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>0</v>
+        <v>248006.55</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4632,7 +4632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4681,7 +4681,55 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="8" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>8898</v>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Григорівка №3</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>188043.75</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11">
+        <f>E2-F2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="E3" s="13">
+        <f>SUM(E2:E2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="13">
+        <f>SUM(F2:F2)</f>
+        <v/>
+      </c>
+      <c r="G3" s="13">
+        <f>SUM(G2:G2)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 19.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 20.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -573,9 +572,10 @@
           <t>Прострочені надходження, ₴</t>
         </is>
       </c>
-      <c r="B8" s="4">
-        <f>SUMIF('Прострочені'!A:A,"&lt;&gt;",'Прострочені'!G:G)</f>
-        <v/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2591500</v>
+        <v>2593000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2591500</v>
+        <v>2593000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5183000</v>
+        <v>5186000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5183000</v>
+        <v>5186000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1865880</v>
+        <v>1866960</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1865880</v>
+        <v>1866960</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>456104</v>
+        <v>456368</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>456104</v>
+        <v>456368</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8660274.699999999</v>
+        <v>8665287.4</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8660274.699999999</v>
+        <v>8665287.4</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4079021</v>
+        <v>4081382</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4079021</v>
+        <v>4081382</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4961426.75</v>
+        <v>4964298.5</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>4961426.75</v>
+        <v>4964298.5</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>755422.25</v>
+        <v>755859.5</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>755422.25</v>
+        <v>755859.5</v>
       </c>
       <c r="H65" s="11">
         <f>F65-G65</f>
@@ -3523,28 +3523,28 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>8898</v>
+        <v>8878</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>188043.75</v>
+        <v>12823</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3570,25 +3570,25 @@
         <v>46255</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>8878</v>
+        <v>8898</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>12823</v>
+        <v>188043.75</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>17320601.23</v>
+        <v>17330626.66</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>2976078.6</v>
+        <v>2977801.2</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>907025</v>
+        <v>907550</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>0</v>
@@ -4059,14 +4059,14 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -4076,14 +4076,14 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2886620.02</v>
+        <v>573945</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>248006.55</v>
+        <v>0</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4099,22 +4099,18 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K78" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K78" s="12" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>7002</v>
+        <v>8898</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4124,11 +4120,11 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>573945</v>
+        <v>188043.75</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4151,19 +4147,19 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>8898</v>
+        <v>7508</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -4172,7 +4168,7 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>188043.75</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4195,28 +4191,28 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46283</v>
+        <v>46297</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>7508</v>
+        <v>7894</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>737597.4</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4232,21 +4228,21 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -4256,14 +4252,14 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>737597.4</v>
+        <v>2888290.84</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>0</v>
+        <v>248150.1</v>
       </c>
       <c r="H82" s="11">
         <f>F82-G82</f>
@@ -4279,7 +4275,11 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K82" s="12" t="inlineStr"/>
+      <c r="K82" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
@@ -4632,7 +4632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4681,55 +4681,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="n">
-        <v>46253</v>
-      </c>
-      <c r="B2" s="9" t="n">
-        <v>8898</v>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>Григорівка №3</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="n">
-        <v>188043.75</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="11">
-        <f>E2-F2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Разом</t>
-        </is>
-      </c>
-      <c r="E3" s="13">
-        <f>SUM(E2:E2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="13">
-        <f>SUM(F2:F2)</f>
-        <v/>
-      </c>
-      <c r="G3" s="13">
-        <f>SUM(G2:G2)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,6 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 20.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 21.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -572,10 +573,9 @@
           <t>Прострочені надходження, ₴</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="B8" s="4">
+        <f>SUMIF('Прострочені'!A:A,"&lt;&gt;",'Прострочені'!G:G)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2593000</v>
+        <v>2606500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2593000</v>
+        <v>2606500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5186000</v>
+        <v>5213000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5186000</v>
+        <v>5213000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1866960</v>
+        <v>1876680</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1866960</v>
+        <v>1876680</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>456368</v>
+        <v>458744</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>456368</v>
+        <v>458744</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8665287.4</v>
+        <v>8710401.700000001</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8665287.4</v>
+        <v>8710401.700000001</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4081382</v>
+        <v>4102631</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4081382</v>
+        <v>4102631</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4964298.5</v>
+        <v>4990144.25</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>4964298.5</v>
+        <v>4990144.25</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>755859.5</v>
+        <v>759794.75</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>755859.5</v>
+        <v>759794.75</v>
       </c>
       <c r="H65" s="11">
         <f>F65-G65</f>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>17330626.66</v>
+        <v>17420855.53</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>2977801.2</v>
+        <v>2993304.6</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>907550</v>
+        <v>912275</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>0</v>
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>2888290.84</v>
+        <v>2903328.22</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>248150.1</v>
+        <v>249442.05</v>
       </c>
       <c r="H82" s="11">
         <f>F82-G82</f>
@@ -4632,7 +4632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4681,7 +4681,83 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="8" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>8898</v>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Григорівка №3</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>188043.75</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11">
+        <f>E2-F2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>8878</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>12823</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11">
+        <f>E3-F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="E4" s="13">
+        <f>SUM(E2:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="13">
+        <f>SUM(F2:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="13">
+        <f>SUM(G2:G3)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 21.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 24.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2606500</v>
+        <v>2612000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2606500</v>
+        <v>2612000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5213000</v>
+        <v>5224000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5213000</v>
+        <v>5224000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1876680</v>
+        <v>1880640</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1876680</v>
+        <v>1880640</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>458744</v>
+        <v>459712</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>458744</v>
+        <v>459712</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8710401.700000001</v>
+        <v>8728781.6</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8710401.700000001</v>
+        <v>8728781.6</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4102631</v>
+        <v>4111288</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4102631</v>
+        <v>4111288</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4990144.25</v>
+        <v>5000674</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>4990144.25</v>
+        <v>5000674</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>759794.75</v>
+        <v>761398</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>759794.75</v>
+        <v>761398</v>
       </c>
       <c r="H65" s="11">
         <f>F65-G65</f>
@@ -3526,28 +3526,28 @@
         <v>46255</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>8878</v>
+        <v>7894</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>12823</v>
+        <v>185968</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>0</v>
+        <v>185968</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3570,11 +3570,11 @@
         <v>46255</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>8898</v>
+        <v>7894</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>188043.75</v>
+        <v>185967.99</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>0</v>
+        <v>185967.99</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3611,14 +3611,14 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>3456</v>
+        <v>7894</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -3628,14 +3628,14 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>335974.68</v>
+        <v>737597.4</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>0</v>
+        <v>737597.4</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3655,14 +3655,14 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>6352</v>
+        <v>8898</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -3672,14 +3672,14 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>1119237.26</v>
+        <v>188043.75</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>0</v>
+        <v>188043.75</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3699,28 +3699,28 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>6406</v>
+        <v>3456</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>218602</v>
+        <v>335974.68</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3743,31 +3743,31 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>5910</v>
+        <v>6406</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>17420855.53</v>
+        <v>218602</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>2993304.6</v>
+        <v>0</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3783,22 +3783,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K71" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K71" s="12" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -3808,14 +3804,14 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>185968</v>
+        <v>17457615.44</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>0</v>
+        <v>2999620.8</v>
       </c>
       <c r="H72" s="11">
         <f>F72-G72</f>
@@ -3831,32 +3827,36 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K72" s="12" t="inlineStr"/>
+      <c r="K72" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>7894</v>
+        <v>5870</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>185967.99</v>
+        <v>914200</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -3875,35 +3875,39 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K73" s="12" t="inlineStr"/>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>€17 500</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>5870</v>
+        <v>6130</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>912275</v>
+        <v>73335</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3919,22 +3923,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K74" s="12" t="inlineStr">
-        <is>
-          <t>€17 500</t>
-        </is>
-      </c>
+      <c r="K74" s="12" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
         <v>46265</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>6130</v>
+        <v>7244</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>73335</v>
+        <v>132708.6</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>36665</v>
+        <v>0</v>
       </c>
       <c r="H75" s="11">
         <f>F75-G75</f>
@@ -3974,11 +3974,11 @@
         <v>46265</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>7244</v>
+        <v>8878</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>132708.6</v>
+        <v>12823</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4059,14 +4059,14 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>7002</v>
+        <v>6352</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -4076,11 +4076,11 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>573945</v>
+        <v>1119237.26</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4103,14 +4103,14 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>8898</v>
+        <v>7002</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4120,11 +4120,11 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>188043.75</v>
+        <v>573945</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4147,19 +4147,19 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>7508</v>
+        <v>8898</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>188043.75</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4191,28 +4191,28 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46297</v>
+        <v>46283</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>7894</v>
+        <v>7508</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>737597.4</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4228,21 +4228,21 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -4252,14 +4252,14 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>2903328.22</v>
+        <v>737597.4</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>249442.05</v>
+        <v>0</v>
       </c>
       <c r="H82" s="11">
         <f>F82-G82</f>
@@ -4275,22 +4275,18 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K82" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K82" s="12" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46308</v>
+        <v>46300</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>6352</v>
+        <v>5910</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -4300,14 +4296,14 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>371982.96</v>
+        <v>2909454.56</v>
       </c>
       <c r="G83" s="10" t="n">
-        <v>0</v>
+        <v>249968.4</v>
       </c>
       <c r="H83" s="11">
         <f>F83-G83</f>
@@ -4323,11 +4319,15 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K83" s="12" t="inlineStr"/>
+      <c r="K83" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46321</v>
+        <v>46308</v>
       </c>
       <c r="B84" s="9" t="n">
         <v>6352</v>
@@ -4344,11 +4344,11 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>651792.28</v>
+        <v>371982.96</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4370,26 +4370,70 @@
       <c r="K84" s="12" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="E85" s="3" t="inlineStr">
+      <c r="A85" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>АБМК SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="11">
+        <f>F85-G85</f>
+        <v/>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K85" s="12" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F85" s="13">
-        <f>SUM(F2:F84)</f>
-        <v/>
-      </c>
-      <c r="G85" s="13">
-        <f>SUM(G2:G84)</f>
-        <v/>
-      </c>
-      <c r="H85" s="13">
-        <f>SUM(H2:H84)</f>
+      <c r="F86" s="13">
+        <f>SUM(F2:F85)</f>
+        <v/>
+      </c>
+      <c r="G86" s="13">
+        <f>SUM(G2:G85)</f>
+        <v/>
+      </c>
+      <c r="H86" s="13">
+        <f>SUM(H2:H85)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I84"/>
+  <autoFilter ref="A1:I85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4632,7 +4676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4683,23 +4727,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>8898</v>
+        <v>3456</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>188043.75</v>
+        <v>335974.68</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -4710,54 +4754,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>8878</v>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>П'ятий платіж</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>12823</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="11">
-        <f>E3-F3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E4" s="13">
-        <f>SUM(E2:E3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>SUM(F2:F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>SUM(G2:G3)</f>
+      <c r="E3" s="13">
+        <f>SUM(E2:E2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="13">
+        <f>SUM(F2:F2)</f>
+        <v/>
+      </c>
+      <c r="G3" s="13">
+        <f>SUM(G2:G2)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 24.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 26.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2612000</v>
+        <v>2604500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2612000</v>
+        <v>2604500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5224000</v>
+        <v>5209000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5224000</v>
+        <v>5209000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1880640</v>
+        <v>1875240</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1880640</v>
+        <v>1875240</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>459712</v>
+        <v>458392.0000000001</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>459712</v>
+        <v>458392.0000000001</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8728781.6</v>
+        <v>8703718.100000001</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8728781.6</v>
+        <v>8703718.100000001</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4111288</v>
+        <v>4099483</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4111288</v>
+        <v>4099483</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3254,11 +3254,11 @@
         <v>46237</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>6130</v>
+        <v>6024</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -3268,14 +3268,14 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>36665</v>
+        <v>201600</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>36665</v>
+        <v>201600</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3298,28 +3298,28 @@
         <v>46237</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>6352</v>
+        <v>6130</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>1399046.58</v>
+        <v>36665</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>1399046.58</v>
+        <v>36665</v>
       </c>
       <c r="H61" s="11">
         <f>F61-G61</f>
@@ -3339,31 +3339,31 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>4766</v>
+        <v>6352</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>64050</v>
+        <v>1399046.58</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>64050</v>
+        <v>1399046.58</v>
       </c>
       <c r="H62" s="11">
         <f>F62-G62</f>
@@ -3386,28 +3386,28 @@
         <v>46238</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>8188</v>
+        <v>4766</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Фундамент Ужгород Стефанія</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>73926</v>
+        <v>64050</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>75926</v>
+        <v>64050</v>
       </c>
       <c r="H63" s="11">
         <f>F63-G63</f>
@@ -3427,19 +3427,19 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>5870</v>
+        <v>8188</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>Фундамент Ужгород Стефанія</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>5000674</v>
+        <v>73926</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>5000674</v>
+        <v>75926</v>
       </c>
       <c r="H64" s="11">
         <f>F64-G64</f>
@@ -3467,15 +3467,11 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K64" s="12" t="inlineStr">
-        <is>
-          <t>€95 725</t>
-        </is>
-      </c>
+      <c r="K64" s="12" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B65" s="9" t="n">
         <v>5870</v>
@@ -3492,14 +3488,14 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>761398</v>
+        <v>4986315.25</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>761398</v>
+        <v>4986315.25</v>
       </c>
       <c r="H65" s="11">
         <f>F65-G65</f>
@@ -3517,37 +3513,37 @@
       </c>
       <c r="K65" s="12" t="inlineStr">
         <is>
-          <t>€14 575</t>
+          <t>€95 725</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46255</v>
+        <v>46241</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>7894</v>
+        <v>5870</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>185968</v>
+        <v>759211.75</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>185968</v>
+        <v>759211.75</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3563,35 +3559,39 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K66" s="12" t="inlineStr"/>
+      <c r="K66" s="12" t="inlineStr">
+        <is>
+          <t>€14 575</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
         <v>46255</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>7894</v>
+        <v>7414</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>185967.99</v>
+        <v>94000</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>185967.99</v>
+        <v>94000</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3628,14 +3628,14 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>737597.4</v>
+        <v>185968</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>737597.4</v>
+        <v>185968</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3658,11 +3658,11 @@
         <v>46255</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>8898</v>
+        <v>7894</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -3672,14 +3672,14 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>188043.75</v>
+        <v>185967.99</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>188043.75</v>
+        <v>185967.99</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3699,14 +3699,14 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>3456</v>
+        <v>7894</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>335974.68</v>
+        <v>737597.4</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>0</v>
+        <v>737597.4</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3743,19 +3743,19 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>6406</v>
+        <v>8898</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>218602</v>
+        <v>188043.75</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>0</v>
+        <v>188043.75</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3787,14 +3787,14 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46263</v>
+        <v>46258</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>5910</v>
+        <v>3456</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -3804,14 +3804,14 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>17457615.44</v>
+        <v>335974.68</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>2999620.8</v>
+        <v>0</v>
       </c>
       <c r="H72" s="11">
         <f>F72-G72</f>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3827,36 +3827,32 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K72" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K72" s="12" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46264</v>
+        <v>46259</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>5870</v>
+        <v>6406</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>914200</v>
+        <v>218602</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -3867,7 +3863,7 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3875,39 +3871,35 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K73" s="12" t="inlineStr">
-        <is>
-          <t>€17 500</t>
-        </is>
-      </c>
+      <c r="K73" s="12" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>6130</v>
+        <v>5910</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>73335</v>
+        <v>17407488.29</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>36665</v>
+        <v>2991007.8</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3923,32 +3915,36 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K74" s="12" t="inlineStr"/>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>7244</v>
+        <v>5870</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>132708.6</v>
+        <v>911575.0000000001</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>0</v>
@@ -3967,18 +3963,22 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K75" s="12" t="inlineStr"/>
+      <c r="K75" s="12" t="inlineStr">
+        <is>
+          <t>€17 500</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
         <v>46265</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>8878</v>
+        <v>6130</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>12823</v>
+        <v>73335</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="H76" s="11">
         <f>F76-G76</f>
@@ -4015,14 +4015,14 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>4766</v>
+        <v>7244</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>1263447.42</v>
+        <v>132708.6</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4052,35 +4052,35 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K77" s="12" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>6352</v>
+        <v>8878</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>1119237.26</v>
+        <v>12823</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4096,26 +4096,26 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>7002</v>
+        <v>4766</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>573945</v>
+        <v>1263447.42</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4147,14 +4147,14 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>8898</v>
+        <v>6352</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>188043.75</v>
+        <v>1119237.26</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4191,28 +4191,28 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>7508</v>
+        <v>7002</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>573945</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4235,14 +4235,14 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46298</v>
+        <v>46280</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>7894</v>
+        <v>8898</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -4252,11 +4252,11 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>737597.4</v>
+        <v>188043.75</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4272,26 +4272,26 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K82" s="12" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46300</v>
+        <v>46283</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>5910</v>
+        <v>7508</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>2909454.56</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G83" s="10" t="n">
-        <v>249968.4</v>
+        <v>0</v>
       </c>
       <c r="H83" s="11">
         <f>F83-G83</f>
@@ -4316,39 +4316,35 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K83" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K83" s="12" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46308</v>
+        <v>46288</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Етап 2</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>371982.96</v>
+        <v>57497.5</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4364,35 +4360,35 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46321</v>
+        <v>46295</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Етап 3</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>651792.28</v>
+        <v>57497.5</v>
       </c>
       <c r="G85" s="10" t="n">
         <v>0</v>
@@ -4408,32 +4404,256 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K85" s="12" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B86" s="9" t="n">
+        <v>7894</v>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>SCP Фора  Хотів</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>737597.4</v>
+      </c>
+      <c r="G86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="11">
+        <f>F86-G86</f>
+        <v/>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K85" s="12" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="E86" s="3" t="inlineStr">
+      <c r="K86" s="12" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B87" s="9" t="n">
+        <v>5910</v>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>SGM Brdovec, Хорватия</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="n">
+        <v>2901100.46</v>
+      </c>
+      <c r="G87" s="10" t="n">
+        <v>249250.65</v>
+      </c>
+      <c r="H87" s="11">
+        <f>F87-G87</f>
+        <v/>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K87" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B88" s="9" t="n">
+        <v>6024</v>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>Етап 2</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>246402</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="11">
+        <f>F88-G88</f>
+        <v/>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K88" s="12" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B89" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>АБМК SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>Четвертий платіж</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="n">
+        <v>371982.96</v>
+      </c>
+      <c r="G89" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="11">
+        <f>F89-G89</f>
+        <v/>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K89" s="12" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B90" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>АБМК SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="11">
+        <f>F90-G90</f>
+        <v/>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K90" s="12" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F86" s="13">
-        <f>SUM(F2:F85)</f>
-        <v/>
-      </c>
-      <c r="G86" s="13">
-        <f>SUM(G2:G85)</f>
-        <v/>
-      </c>
-      <c r="H86" s="13">
-        <f>SUM(H2:H85)</f>
+      <c r="F91" s="13">
+        <f>SUM(F2:F90)</f>
+        <v/>
+      </c>
+      <c r="G91" s="13">
+        <f>SUM(G2:G90)</f>
+        <v/>
+      </c>
+      <c r="H91" s="13">
+        <f>SUM(H2:H90)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I85"/>
+  <autoFilter ref="A1:I90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4676,7 +4896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4754,26 +4974,54 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11">
+        <f>E3-F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E3" s="13">
-        <f>SUM(E2:E2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="13">
-        <f>SUM(F2:F2)</f>
-        <v/>
-      </c>
-      <c r="G3" s="13">
-        <f>SUM(G2:G2)</f>
+      <c r="E4" s="13">
+        <f>SUM(E2:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="13">
+        <f>SUM(F2:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="13">
+        <f>SUM(G2:G3)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3787,28 +3787,28 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>3456</v>
+        <v>6406</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>335974.68</v>
+        <v>218602</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>0</v>
@@ -3831,28 +3831,28 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>6406</v>
+        <v>5870</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>218602</v>
+        <v>911575.0000000001</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3871,11 +3871,15 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K73" s="12" t="inlineStr"/>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>€17 500</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B74" s="9" t="n">
         <v>5910</v>
@@ -3923,31 +3927,31 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>5870</v>
+        <v>6130</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>911575.0000000001</v>
+        <v>73335</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>0</v>
+        <v>36665</v>
       </c>
       <c r="H75" s="11">
         <f>F75-G75</f>
@@ -3963,22 +3967,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K75" s="12" t="inlineStr">
-        <is>
-          <t>€17 500</t>
-        </is>
-      </c>
+      <c r="K75" s="12" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
         <v>46265</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>6130</v>
+        <v>7244</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>73335</v>
+        <v>132708.6</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>36665</v>
+        <v>0</v>
       </c>
       <c r="H76" s="11">
         <f>F76-G76</f>
@@ -4018,11 +4018,11 @@
         <v>46265</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>7244</v>
+        <v>8878</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>132708.6</v>
+        <v>12823</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4059,28 +4059,28 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>8878</v>
+        <v>3456</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>12823</v>
+        <v>335974.68</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr"/>
@@ -4896,7 +4896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4947,23 +4947,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>3456</v>
+        <v>6406</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>335974.68</v>
+        <v>218602</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -4974,54 +4974,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>6406</v>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Максим Яловий Чинадієво</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>218602</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="11">
-        <f>E3-F3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E4" s="13">
-        <f>SUM(E2:E3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>SUM(F2:F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>SUM(G2:G3)</f>
+      <c r="E3" s="13">
+        <f>SUM(E2:E2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="13">
+        <f>SUM(F2:F2)</f>
+        <v/>
+      </c>
+      <c r="G3" s="13">
+        <f>SUM(G2:G2)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -3787,7 +3787,7 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B72" s="9" t="n">
         <v>6406</v>
@@ -4947,7 +4947,7 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B2" s="9" t="n">
         <v>6406</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3275,7 +3275,7 @@
         <v>201600</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>201600</v>
+        <v>0</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4503,7 +4503,7 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="B88" s="9" t="n">
         <v>6024</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Етап 2</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
@@ -4896,7 +4896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4974,26 +4974,54 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>6024</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Авансовий платіж</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>201600</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11">
+        <f>E3-F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E3" s="13">
-        <f>SUM(E2:E2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="13">
-        <f>SUM(F2:F2)</f>
-        <v/>
-      </c>
-      <c r="G3" s="13">
-        <f>SUM(G2:G2)</f>
+      <c r="E4" s="13">
+        <f>SUM(E2:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="13">
+        <f>SUM(F2:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="13">
+        <f>SUM(G2:G3)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3275,7 +3275,7 @@
         <v>201600</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>0</v>
+        <v>201600</v>
       </c>
       <c r="H60" s="11">
         <f>F60-G60</f>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4974,54 +4974,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>6024</v>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Авансовий платіж</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>201600</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="11">
-        <f>E3-F3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E4" s="13">
-        <f>SUM(E2:E3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>SUM(F2:F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>SUM(G2:G3)</f>
+      <c r="E3" s="13">
+        <f>SUM(E2:E2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="13">
+        <f>SUM(F2:F2)</f>
+        <v/>
+      </c>
+      <c r="G3" s="13">
+        <f>SUM(G2:G2)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 26.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 27.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2604500</v>
+        <v>2600500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2604500</v>
+        <v>2600500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5209000</v>
+        <v>5201000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5209000</v>
+        <v>5201000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1875240</v>
+        <v>1872360</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1875240</v>
+        <v>1872360</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>458392.0000000001</v>
+        <v>457688</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>458392.0000000001</v>
+        <v>457688</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8703718.100000001</v>
+        <v>8690350.9</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8703718.100000001</v>
+        <v>8690350.9</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4099483</v>
+        <v>4093187</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4099483</v>
+        <v>4093187</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3471,31 +3471,31 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B65" s="9" t="n">
-        <v>5870</v>
+        <v>6130</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>4986315.25</v>
+        <v>73335</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>4986315.25</v>
+        <v>73335</v>
       </c>
       <c r="H65" s="11">
         <f>F65-G65</f>
@@ -3511,15 +3511,11 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K65" s="12" t="inlineStr">
-        <is>
-          <t>€95 725</t>
-        </is>
-      </c>
+      <c r="K65" s="12" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B66" s="9" t="n">
         <v>5870</v>
@@ -3536,14 +3532,14 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>759211.75</v>
+        <v>4978657.25</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>759211.75</v>
+        <v>4978657.25</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3561,37 +3557,37 @@
       </c>
       <c r="K66" s="12" t="inlineStr">
         <is>
-          <t>€14 575</t>
+          <t>€95 725</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>46255</v>
+        <v>46241</v>
       </c>
       <c r="B67" s="9" t="n">
-        <v>7414</v>
+        <v>5870</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>94000</v>
+        <v>758045.75</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>94000</v>
+        <v>758045.75</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3607,35 +3603,39 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K67" s="12" t="inlineStr"/>
+      <c r="K67" s="12" t="inlineStr">
+        <is>
+          <t>€14 575</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
         <v>46255</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>7894</v>
+        <v>7414</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>185968</v>
+        <v>94000</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>185968</v>
+        <v>94000</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3672,14 +3672,14 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>185967.99</v>
+        <v>185968</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>185967.99</v>
+        <v>185968</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3716,14 +3716,14 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>737597.4</v>
+        <v>185967.99</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>737597.4</v>
+        <v>185967.99</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3746,11 +3746,11 @@
         <v>46255</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>8898</v>
+        <v>7894</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -3760,14 +3760,14 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>188043.75</v>
+        <v>737597.4</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>188043.75</v>
+        <v>737597.4</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3787,19 +3787,19 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46260</v>
+        <v>46255</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>6406</v>
+        <v>8898</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>218602</v>
+        <v>188043.75</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>0</v>
+        <v>188043.75</v>
       </c>
       <c r="H72" s="11">
         <f>F72-G72</f>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3831,28 +3831,28 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46264</v>
+        <v>46260</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>5870</v>
+        <v>6406</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>911575.0000000001</v>
+        <v>218602</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3871,39 +3871,35 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K73" s="12" t="inlineStr">
-        <is>
-          <t>€17 500</t>
-        </is>
-      </c>
+      <c r="K73" s="12" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>5910</v>
+        <v>5870</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>17407488.29</v>
+        <v>910175</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>2991007.8</v>
+        <v>0</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3921,7 +3917,7 @@
       </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
-          <t>€334 181</t>
+          <t>€17 500</t>
         </is>
       </c>
     </row>
@@ -3930,11 +3926,11 @@
         <v>46265</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>6130</v>
+        <v>7244</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Євро Простір Марія</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -3948,10 +3944,10 @@
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>73335</v>
+        <v>132708.6</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>36665</v>
+        <v>0</v>
       </c>
       <c r="H75" s="11">
         <f>F75-G75</f>
@@ -3974,11 +3970,11 @@
         <v>46265</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>7244</v>
+        <v>8878</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -3992,7 +3988,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>132708.6</v>
+        <v>12823</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4015,28 +4011,28 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>8878</v>
+        <v>3456</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>12823</v>
+        <v>335974.68</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4052,35 +4048,35 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K77" s="12" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>3456</v>
+        <v>4766</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>335974.68</v>
+        <v>1263447.42</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4103,31 +4099,31 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>1263447.42</v>
+        <v>17380753.81</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>0</v>
+        <v>2986414.2</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4143,7 +4139,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K79" s="12" t="inlineStr"/>
+      <c r="K79" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Етап 2</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Етап 3</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
@@ -4476,10 +4476,10 @@
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>2901100.46</v>
+        <v>2896644.94</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>249250.65</v>
+        <v>248867.85</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 27.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 28.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2600500</v>
+        <v>2592500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2600500</v>
+        <v>2592500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5201000</v>
+        <v>5185000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5201000</v>
+        <v>5185000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1872360</v>
+        <v>1866600</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1872360</v>
+        <v>1866600</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>457688</v>
+        <v>456280</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>457688</v>
+        <v>456280</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8690350.9</v>
+        <v>8663616.5</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8690350.9</v>
+        <v>8663616.5</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4093187</v>
+        <v>4080595</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4093187</v>
+        <v>4080595</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4978657.25</v>
+        <v>4963341.25</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4978657.25</v>
+        <v>4963341.25</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>758045.75</v>
+        <v>755713.75</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>758045.75</v>
+        <v>755713.75</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3855,7 +3855,7 @@
         <v>218602</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="H73" s="11">
         <f>F73-G73</f>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>910175</v>
+        <v>907375</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>0</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>17380753.81</v>
+        <v>17327284.85</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>2986414.2</v>
+        <v>2977227</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4476,10 +4476,10 @@
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>2896644.94</v>
+        <v>2887733.9</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>248867.85</v>
+        <v>248102.25</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4966,7 +4966,7 @@
         <v>218602</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 28.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 30.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -3875,31 +3875,31 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>5870</v>
+        <v>8878</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>907375</v>
+        <v>12823</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>0</v>
+        <v>12823</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3915,22 +3915,18 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K74" s="12" t="inlineStr">
-        <is>
-          <t>€17 500</t>
-        </is>
-      </c>
+      <c r="K74" s="12" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>7244</v>
+        <v>4766</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -3944,7 +3940,7 @@
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>132708.6</v>
+        <v>1263447.42</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>0</v>
@@ -3960,35 +3956,35 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K75" s="12" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>8878</v>
+        <v>5870</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>12823</v>
+        <v>907375</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4004,21 +4000,25 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="K76" s="12" t="inlineStr"/>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="inlineStr">
+        <is>
+          <t>€17 500</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46266</v>
+        <v>46270</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>3456</v>
+        <v>5910</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -4028,14 +4028,14 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>335974.68</v>
+        <v>17327284.85</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>0</v>
+        <v>2977227</v>
       </c>
       <c r="H77" s="11">
         <f>F77-G77</f>
@@ -4051,23 +4051,27 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K77" s="12" t="inlineStr"/>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -4076,7 +4080,7 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>1263447.42</v>
+        <v>573945</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4099,14 +4103,14 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>5910</v>
+        <v>3456</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4116,14 +4120,14 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>17327284.85</v>
+        <v>335974.68</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>2977227</v>
+        <v>0</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4139,22 +4143,18 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K79" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K79" s="12" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>6352</v>
+        <v>8898</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1119237.26</v>
+        <v>188043.75</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4191,28 +4191,28 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46273</v>
+        <v>46283</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>7002</v>
+        <v>7508</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>573945</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4235,28 +4235,28 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>8898</v>
+        <v>7414</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>188043.75</v>
+        <v>57497.5</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4279,19 +4279,19 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>7508</v>
+        <v>6352</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>1119237.26</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4323,28 +4323,28 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>7414</v>
+        <v>6352</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>57497.5</v>
+        <v>371982.96</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4370,11 +4370,11 @@
         <v>46295</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>7414</v>
+        <v>7244</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -4384,11 +4384,11 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>57497.5</v>
+        <v>132708.6</v>
       </c>
       <c r="G85" s="10" t="n">
         <v>0</v>
@@ -4411,28 +4411,28 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="B86" s="9" t="n">
-        <v>7894</v>
+        <v>7414</v>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>737597.4</v>
+        <v>57497.5</v>
       </c>
       <c r="G86" s="10" t="n">
         <v>0</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K86" s="12" t="inlineStr"/>
@@ -4547,14 +4547,14 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>6352</v>
+        <v>7894</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
@@ -4564,11 +4564,11 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>371982.96</v>
+        <v>737597.4</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 30.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 31.08.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3611,31 +3611,31 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46255</v>
+        <v>46244</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>7414</v>
+        <v>6824</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SOLAR Карпорти 2</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Авансовий</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>94000</v>
+        <v>149710</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>94000</v>
+        <v>149710</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3655,31 +3655,31 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>7894</v>
+        <v>5904</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>SOLAR Карпорти Realcom</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>185968</v>
+        <v>560757.75</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>185968</v>
+        <v>560757.75</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3695,35 +3695,39 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K69" s="12" t="inlineStr"/>
+      <c r="K69" s="12" t="inlineStr">
+        <is>
+          <t>€10 815</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
         <v>46255</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>7894</v>
+        <v>7414</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>185967.99</v>
+        <v>94000</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>185967.99</v>
+        <v>94000</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3760,14 +3764,14 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>737597.4</v>
+        <v>185968</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>737597.4</v>
+        <v>185968</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3790,11 +3794,11 @@
         <v>46255</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>8898</v>
+        <v>7894</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -3804,14 +3808,14 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>188043.75</v>
+        <v>185967.99</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>188043.75</v>
+        <v>185967.99</v>
       </c>
       <c r="H72" s="11">
         <f>F72-G72</f>
@@ -3831,31 +3835,31 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>46260</v>
+        <v>46255</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>6406</v>
+        <v>7894</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>218602</v>
+        <v>737597.4</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>170788</v>
+        <v>737597.4</v>
       </c>
       <c r="H73" s="11">
         <f>F73-G73</f>
@@ -3863,7 +3867,7 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3875,31 +3879,31 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>8878</v>
+        <v>8898</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>12823</v>
+        <v>188043.75</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>12823</v>
+        <v>188043.75</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3919,31 +3923,31 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46267</v>
+        <v>46260</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>4766</v>
+        <v>6406</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1263447.42</v>
+        <v>218602</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="H75" s="11">
         <f>F75-G75</f>
@@ -3951,43 +3955,43 @@
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K75" s="12" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>5870</v>
+        <v>8878</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>907375</v>
+        <v>12823</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>0</v>
+        <v>12823</v>
       </c>
       <c r="H76" s="11">
         <f>F76-G76</f>
@@ -3995,47 +3999,43 @@
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="K76" s="12" t="inlineStr">
-        <is>
-          <t>€17 500</t>
-        </is>
-      </c>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46270</v>
+        <v>46267</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>17327284.85</v>
+        <v>1263447.42</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>2977227</v>
+        <v>0</v>
       </c>
       <c r="H77" s="11">
         <f>F77-G77</f>
@@ -4051,36 +4051,32 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K77" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K77" s="12" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>7002</v>
+        <v>5870</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>573945</v>
+        <v>907375</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4099,18 +4095,22 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K78" s="12" t="inlineStr"/>
+      <c r="K78" s="12" t="inlineStr">
+        <is>
+          <t>€17 500</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46274</v>
+        <v>46270</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>3456</v>
+        <v>5910</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>335974.68</v>
+        <v>17327284.85</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>0</v>
+        <v>2977227</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4143,18 +4143,22 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K79" s="12" t="inlineStr"/>
+      <c r="K79" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>8898</v>
+        <v>7002</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -4164,11 +4168,11 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>188043.75</v>
+        <v>573945</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4191,19 +4195,19 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46283</v>
+        <v>46274</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>7508</v>
+        <v>3456</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -4212,7 +4216,7 @@
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>335974.68</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4235,28 +4239,28 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46288</v>
+        <v>46280</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>7414</v>
+        <v>6356</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>-26 SOLAR Наземні СЕС Kirill Trokhin</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>57497.5</v>
+        <v>73128.39999999999</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4279,28 +4283,28 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46293</v>
+        <v>46280</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 SOLAR Наземні СЕС Kirill Trokhin</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий 2</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>1119237.26</v>
+        <v>3064</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4323,14 +4327,14 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46293</v>
+        <v>46280</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>6352</v>
+        <v>8898</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
@@ -4340,11 +4344,11 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>371982.96</v>
+        <v>188043.75</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4367,14 +4371,14 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46295</v>
+        <v>46283</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>7244</v>
+        <v>7508</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -4384,11 +4388,11 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>132708.6</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G85" s="10" t="n">
         <v>0</v>
@@ -4411,7 +4415,7 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B86" s="9" t="n">
         <v>7414</v>
@@ -4428,7 +4432,7 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
@@ -4455,14 +4459,14 @@
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="B87" s="9" t="n">
-        <v>5910</v>
+        <v>6352</v>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -4476,10 +4480,10 @@
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>2887733.9</v>
+        <v>1119237.26</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>248102.25</v>
+        <v>0</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4492,39 +4496,35 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K87" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K87" s="12" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46304</v>
+        <v>46293</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>6024</v>
+        <v>6352</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>246402</v>
+        <v>371982.96</v>
       </c>
       <c r="G88" s="10" t="n">
         <v>0</v>
@@ -4540,26 +4540,26 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K88" s="12" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46304</v>
+        <v>46295</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>7894</v>
+        <v>7244</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>737597.4</v>
+        <v>132708.6</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>
@@ -4584,35 +4584,35 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K89" s="12" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46321</v>
+        <v>46295</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>651792.28</v>
+        <v>57497.5</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4628,32 +4628,300 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K90" s="12" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B91" s="9" t="n">
+        <v>5910</v>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>SGM Brdovec, Хорватия</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F91" s="10" t="n">
+        <v>2887733.9</v>
+      </c>
+      <c r="G91" s="10" t="n">
+        <v>248102.25</v>
+      </c>
+      <c r="H91" s="11">
+        <f>F91-G91</f>
+        <v/>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K90" s="12" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="E91" s="3" t="inlineStr">
+      <c r="K91" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B92" s="9" t="n">
+        <v>6024</v>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>246402</v>
+      </c>
+      <c r="G92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="11">
+        <f>F92-G92</f>
+        <v/>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K92" s="12" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B93" s="9" t="n">
+        <v>7894</v>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>SCP Фора  Хотів</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="n">
+        <v>737597.4</v>
+      </c>
+      <c r="G93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="11">
+        <f>F93-G93</f>
+        <v/>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B94" s="9" t="n">
+        <v>6356</v>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>-26 SOLAR Наземні СЕС Kirill Trokhin</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>Хома</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>Етап 2</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>64240</v>
+      </c>
+      <c r="G94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="11">
+        <f>F94-G94</f>
+        <v/>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K94" s="12" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>АБМК SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="11">
+        <f>F95-G95</f>
+        <v/>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K95" s="12" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="n">
+        <v>46331</v>
+      </c>
+      <c r="B96" s="9" t="n">
+        <v>6356</v>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>-26 SOLAR Наземні СЕС Kirill Trokhin</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>Хома</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>Етап 3</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>12848</v>
+      </c>
+      <c r="G96" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="11">
+        <f>F96-G96</f>
+        <v/>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="K96" s="12" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F91" s="13">
-        <f>SUM(F2:F90)</f>
-        <v/>
-      </c>
-      <c r="G91" s="13">
-        <f>SUM(G2:G90)</f>
-        <v/>
-      </c>
-      <c r="H91" s="13">
-        <f>SUM(H2:H90)</f>
+      <c r="F97" s="13">
+        <f>SUM(F2:F96)</f>
+        <v/>
+      </c>
+      <c r="G97" s="13">
+        <f>SUM(G2:G96)</f>
+        <v/>
+      </c>
+      <c r="H97" s="13">
+        <f>SUM(H2:H96)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I90"/>
+  <autoFilter ref="A1:I96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4664,7 +4932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4863,25 +5131,48 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>лис 2026</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>SUMIF('Графік надходжень'!J:J,"2026-11",'Графік надходжень'!F:F)</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>SUMIF('Графік надходжень'!J:J,"2026-11",'Графік надходжень'!G:G)</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="14">
+        <f>IF(B9=0,0,C9/B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="B9" s="13">
-        <f>SUM(B2:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="13">
-        <f>SUM(C2:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="13">
-        <f>SUM(D2:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="15">
-        <f>IF(B9=0,0,C9/B9)</f>
+      <c r="B10" s="13">
+        <f>SUM(B2:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="13">
+        <f>SUM(C2:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="13">
+        <f>SUM(D2:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>IF(B10=0,0,C10/B10)</f>
         <v/>
       </c>
     </row>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2592500</v>
+        <v>2594000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2592500</v>
+        <v>2594000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5185000</v>
+        <v>5188000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5185000</v>
+        <v>5188000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1866600</v>
+        <v>1867680</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1866600</v>
+        <v>1867680</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>456280</v>
+        <v>456544</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>456280</v>
+        <v>456544</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8663616.5</v>
+        <v>8668629.200000001</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8663616.5</v>
+        <v>8668629.200000001</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4080595</v>
+        <v>4082956</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4080595</v>
+        <v>4082956</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4963341.25</v>
+        <v>4966213</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4963341.25</v>
+        <v>4966213</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>755713.75</v>
+        <v>756151</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>755713.75</v>
+        <v>756151</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3611,14 +3611,14 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>6824</v>
+        <v>5904</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>SOLAR Карпорти 2</t>
+          <t>SOLAR Карпорти шт. 10 шт. 0.03 Мвт SIA Realcom</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -3628,14 +3628,14 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Авансовий</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>149710</v>
+        <v>10815</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>149710</v>
+        <v>10815</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3655,31 +3655,31 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>5904</v>
+        <v>7414</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>SOLAR Карпорти Realcom</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Авансовий</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>560757.75</v>
+        <v>94000</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>560757.75</v>
+        <v>94000</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3695,39 +3695,35 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K69" s="12" t="inlineStr">
-        <is>
-          <t>€10 815</t>
-        </is>
-      </c>
+      <c r="K69" s="12" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
         <v>46255</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>7414</v>
+        <v>7894</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>94000</v>
+        <v>185968</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>94000</v>
+        <v>185968</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3764,14 +3760,14 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>185968</v>
+        <v>185967.99</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>185968</v>
+        <v>185967.99</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3808,14 +3804,14 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>185967.99</v>
+        <v>737597.4</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>185967.99</v>
+        <v>737597.4</v>
       </c>
       <c r="H72" s="11">
         <f>F72-G72</f>
@@ -3838,11 +3834,11 @@
         <v>46255</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>7894</v>
+        <v>8898</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -3852,14 +3848,14 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>737597.4</v>
+        <v>188043.75</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>737597.4</v>
+        <v>188043.75</v>
       </c>
       <c r="H73" s="11">
         <f>F73-G73</f>
@@ -3879,19 +3875,19 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>8898</v>
+        <v>6406</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -3900,10 +3896,10 @@
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>188043.75</v>
+        <v>218602</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>188043.75</v>
+        <v>170788</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3911,7 +3907,7 @@
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3923,31 +3919,31 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>6406</v>
+        <v>8878</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>218602</v>
+        <v>12823</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>170788</v>
+        <v>12823</v>
       </c>
       <c r="H75" s="11">
         <f>F75-G75</f>
@@ -3955,7 +3951,7 @@
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3967,31 +3963,31 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>8878</v>
+        <v>6356</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>12823</v>
+        <v>51392</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>12823</v>
+        <v>0</v>
       </c>
       <c r="H76" s="11">
         <f>F76-G76</f>
@@ -3999,12 +3995,12 @@
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr"/>
@@ -4076,7 +4072,7 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>907375</v>
+        <v>907900</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4124,10 +4120,10 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>17327284.85</v>
+        <v>17337310.28</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>2977227</v>
+        <v>2978949.6</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4242,25 +4238,25 @@
         <v>46280</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>6356</v>
+        <v>8898</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС Kirill Trokhin</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Авансовий</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>73128.39999999999</v>
+        <v>188043.75</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4283,28 +4279,28 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>6356</v>
+        <v>7508</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС Kirill Trokhin</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Авансовий 2</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>3064</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4327,28 +4323,28 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>8898</v>
+        <v>7414</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>188043.75</v>
+        <v>57497.5</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4371,19 +4367,19 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>7508</v>
+        <v>6352</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
@@ -4392,7 +4388,7 @@
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>1119237.26</v>
       </c>
       <c r="G85" s="10" t="n">
         <v>0</v>
@@ -4415,28 +4411,28 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B86" s="9" t="n">
-        <v>7414</v>
+        <v>6352</v>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>57497.5</v>
+        <v>371982.96</v>
       </c>
       <c r="G86" s="10" t="n">
         <v>0</v>
@@ -4459,28 +4455,28 @@
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B87" s="9" t="n">
-        <v>6352</v>
+        <v>7244</v>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>1119237.26</v>
+        <v>132708.6</v>
       </c>
       <c r="G87" s="10" t="n">
         <v>0</v>
@@ -4503,28 +4499,28 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>371982.96</v>
+        <v>57497.5</v>
       </c>
       <c r="G88" s="10" t="n">
         <v>0</v>
@@ -4547,31 +4543,31 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>7244</v>
+        <v>5910</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>132708.6</v>
+        <v>2889404.72</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>0</v>
+        <v>248245.8</v>
       </c>
       <c r="H89" s="11">
         <f>F89-G89</f>
@@ -4584,21 +4580,25 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="K89" s="12" t="inlineStr"/>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K89" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>7414</v>
+        <v>6024</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -4608,11 +4608,11 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>57497.5</v>
+        <v>246402</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4628,21 +4628,21 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>5910</v>
+        <v>7894</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -4652,14 +4652,14 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>2887733.9</v>
+        <v>737597.4</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>248102.25</v>
+        <v>0</v>
       </c>
       <c r="H91" s="11">
         <f>F91-G91</f>
@@ -4675,27 +4675,23 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K91" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K91" s="12" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46304</v>
+        <v>46316</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>6024</v>
+        <v>6356</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
@@ -4704,7 +4700,7 @@
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>246402</v>
+        <v>64240</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4727,14 +4723,14 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46304</v>
+        <v>46321</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>7894</v>
+        <v>6352</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4748,7 +4744,7 @@
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>737597.4</v>
+        <v>651792.28</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4771,14 +4767,14 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46310</v>
+        <v>46322</v>
       </c>
       <c r="B94" s="9" t="n">
         <v>6356</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС Kirill Trokhin</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -4788,11 +4784,11 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Етап 2</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>64240</v>
+        <v>12848</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -4814,114 +4810,26 @@
       <c r="K94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B95" s="9" t="n">
-        <v>6352</v>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>АБМК SCP Blade 8PS</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>Донська</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>П'ятий платіж</t>
-        </is>
-      </c>
-      <c r="F95" s="10" t="n">
-        <v>651792.28</v>
-      </c>
-      <c r="G95" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="11">
-        <f>F95-G95</f>
-        <v/>
-      </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>очікується</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K95" s="12" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="n">
-        <v>46331</v>
-      </c>
-      <c r="B96" s="9" t="n">
-        <v>6356</v>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>-26 SOLAR Наземні СЕС Kirill Trokhin</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>Хома</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>Етап 3</t>
-        </is>
-      </c>
-      <c r="F96" s="10" t="n">
-        <v>12848</v>
-      </c>
-      <c r="G96" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="11">
-        <f>F96-G96</f>
-        <v/>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>очікується</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="K96" s="12" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F97" s="13">
-        <f>SUM(F2:F96)</f>
-        <v/>
-      </c>
-      <c r="G97" s="13">
-        <f>SUM(G2:G96)</f>
-        <v/>
-      </c>
-      <c r="H97" s="13">
-        <f>SUM(H2:H96)</f>
+      <c r="F95" s="13">
+        <f>SUM(F2:F94)</f>
+        <v/>
+      </c>
+      <c r="G95" s="13">
+        <f>SUM(G2:G94)</f>
+        <v/>
+      </c>
+      <c r="H95" s="13">
+        <f>SUM(H2:H94)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I96"/>
+  <autoFilter ref="A1:I94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4932,7 +4840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5131,48 +5039,25 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>лис 2026</t>
-        </is>
-      </c>
-      <c r="B9" s="11">
-        <f>SUMIF('Графік надходжень'!J:J,"2026-11",'Графік надходжень'!F:F)</f>
-        <v/>
-      </c>
-      <c r="C9" s="11">
-        <f>SUMIF('Графік надходжень'!J:J,"2026-11",'Графік надходжень'!G:G)</f>
-        <v/>
-      </c>
-      <c r="D9" s="11">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="B9" s="13">
+        <f>SUM(B2:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="13">
+        <f>SUM(C2:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="13">
+        <f>SUM(D2:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
         <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Разом</t>
-        </is>
-      </c>
-      <c r="B10" s="13">
-        <f>SUM(B2:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="13">
-        <f>SUM(C2:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="13">
-        <f>SUM(D2:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="15">
-        <f>IF(B10=0,0,C10/B10)</f>
         <v/>
       </c>
     </row>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 31.08.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 01.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5072,7 +5072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5123,26 +5123,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>6406</v>
+        <v>6356</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>218602</v>
+        <v>51392</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -5150,26 +5150,54 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>170788</v>
+      </c>
+      <c r="G3" s="11">
+        <f>E3-F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E3" s="13">
-        <f>SUM(E2:E2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="13">
-        <f>SUM(F2:F2)</f>
-        <v/>
-      </c>
-      <c r="G3" s="13">
-        <f>SUM(G2:G2)</f>
+      <c r="E4" s="13">
+        <f>SUM(E2:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="13">
+        <f>SUM(F2:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="13">
+        <f>SUM(G2:G3)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 01.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 02.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2594000</v>
+        <v>2576500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2594000</v>
+        <v>2576500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5188000</v>
+        <v>5153000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5188000</v>
+        <v>5153000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1867680</v>
+        <v>1855080</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1867680</v>
+        <v>1855080</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>456544</v>
+        <v>453464</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>456544</v>
+        <v>453464</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8668629.200000001</v>
+        <v>8610147.700000001</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8668629.200000001</v>
+        <v>8610147.700000001</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4082956</v>
+        <v>4055411</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4082956</v>
+        <v>4055411</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4966213</v>
+        <v>4932709.25</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4966213</v>
+        <v>4932709.25</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>756151</v>
+        <v>751049.75</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>756151</v>
+        <v>751049.75</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>10815</v>
+        <v>557296.9500000001</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>10815</v>
+        <v>557296.9500000001</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3651,7 +3651,11 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K68" s="12" t="inlineStr"/>
+      <c r="K68" s="12" t="inlineStr">
+        <is>
+          <t>€10 815</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
@@ -3984,7 +3988,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>51392</v>
+        <v>2648229.76</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4003,7 +4007,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K76" s="12" t="inlineStr"/>
+      <c r="K76" s="12" t="inlineStr">
+        <is>
+          <t>€51 392</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
@@ -4039,7 +4047,7 @@
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4072,7 +4080,7 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>907900</v>
+        <v>901775</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4099,14 +4107,14 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4116,14 +4124,14 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>17337310.28</v>
+        <v>573945</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>2978949.6</v>
+        <v>0</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4139,22 +4147,18 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K79" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K79" s="12" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>7002</v>
+        <v>3456</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -4164,11 +4168,11 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>573945</v>
+        <v>335974.68</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4194,11 +4198,11 @@
         <v>46274</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>3456</v>
+        <v>5910</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -4208,14 +4212,14 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>335974.68</v>
+        <v>17220346.93</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>0</v>
+        <v>2958852.6</v>
       </c>
       <c r="H81" s="11">
         <f>F81-G81</f>
@@ -4231,18 +4235,22 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K81" s="12" t="inlineStr"/>
+      <c r="K81" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>8898</v>
+        <v>5910</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -4256,10 +4264,10 @@
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>188043.75</v>
+        <v>2869911.82</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>0</v>
+        <v>246571.05</v>
       </c>
       <c r="H82" s="11">
         <f>F82-G82</f>
@@ -4275,23 +4283,27 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K82" s="12" t="inlineStr"/>
+      <c r="K82" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>7508</v>
+        <v>8898</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -4300,7 +4312,7 @@
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>188043.75</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4323,14 +4335,14 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>7414</v>
+        <v>7508</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
@@ -4340,11 +4352,11 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>57497.5</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4367,28 +4379,28 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>1119237.26</v>
+        <v>57497.5</v>
       </c>
       <c r="G85" s="10" t="n">
         <v>0</v>
@@ -4428,11 +4440,11 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>371982.96</v>
+        <v>1119237.26</v>
       </c>
       <c r="G86" s="10" t="n">
         <v>0</v>
@@ -4455,28 +4467,28 @@
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B87" s="9" t="n">
-        <v>7244</v>
+        <v>6352</v>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>132708.6</v>
+        <v>371982.96</v>
       </c>
       <c r="G87" s="10" t="n">
         <v>0</v>
@@ -4502,11 +4514,11 @@
         <v>46295</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>7414</v>
+        <v>7244</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
@@ -4516,11 +4528,11 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>57497.5</v>
+        <v>132708.6</v>
       </c>
       <c r="G88" s="10" t="n">
         <v>0</v>
@@ -4543,19 +4555,19 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>5910</v>
+        <v>7414</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -4564,10 +4576,10 @@
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>2889404.72</v>
+        <v>57497.5</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>248245.8</v>
+        <v>0</v>
       </c>
       <c r="H89" s="11">
         <f>F89-G89</f>
@@ -4580,14 +4592,10 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K89" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K89" s="12" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
@@ -4700,7 +4708,7 @@
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>64240</v>
+        <v>3310287.2</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4719,7 +4727,11 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K92" s="12" t="inlineStr"/>
+      <c r="K92" s="12" t="inlineStr">
+        <is>
+          <t>€64 240</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
@@ -4788,7 +4800,7 @@
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>12848</v>
+        <v>662057.4400000001</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -4807,7 +4819,11 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K94" s="12" t="inlineStr"/>
+      <c r="K94" s="12" t="inlineStr">
+        <is>
+          <t>€12 848</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="E95" s="3" t="inlineStr">
@@ -5072,7 +5088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5139,7 +5155,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>51392</v>
+        <v>2648229.76</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5151,26 +5167,26 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6406</v>
+        <v>4766</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>218602</v>
+        <v>1263447.42</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -5178,26 +5194,54 @@
       </c>
     </row>
     <row r="4">
-      <c r="D4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>170788</v>
+      </c>
+      <c r="G4" s="11">
+        <f>E4-F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E4" s="13">
-        <f>SUM(E2:E3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>SUM(F2:F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>SUM(G2:G3)</f>
+      <c r="E5" s="13">
+        <f>SUM(E2:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="13">
+        <f>SUM(F2:F4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="13">
+        <f>SUM(G2:G4)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 02.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 03.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2576500</v>
+        <v>2582000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2576500</v>
+        <v>2582000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5153000</v>
+        <v>5164000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5153000</v>
+        <v>5164000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1855080</v>
+        <v>1859040</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1855080</v>
+        <v>1859040</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>453464</v>
+        <v>454432</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>453464</v>
+        <v>454432</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8610147.700000001</v>
+        <v>8628527.6</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8610147.700000001</v>
+        <v>8628527.6</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4055411</v>
+        <v>4064068</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4055411</v>
+        <v>4064068</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4932709.25</v>
+        <v>4943239</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4932709.25</v>
+        <v>4943239</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>751049.75</v>
+        <v>752653</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>751049.75</v>
+        <v>752653</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>557296.9500000001</v>
+        <v>558486.6</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>557296.9500000001</v>
+        <v>558486.6</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B76" s="9" t="n">
         <v>6356</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>2648229.76</v>
+        <v>2653882.88</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4015,28 +4015,28 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>1263447.42</v>
+        <v>257000</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>901775</v>
+        <v>903700</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4195,31 +4195,31 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>17220346.93</v>
+        <v>1263447.42</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>2958852.6</v>
+        <v>0</v>
       </c>
       <c r="H81" s="11">
         <f>F81-G81</f>
@@ -4235,22 +4235,18 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K81" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K81" s="12" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>5910</v>
+        <v>8898</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -4264,10 +4260,10 @@
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>2869911.82</v>
+        <v>188043.75</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>246571.05</v>
+        <v>0</v>
       </c>
       <c r="H82" s="11">
         <f>F82-G82</f>
@@ -4283,27 +4279,23 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K82" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K82" s="12" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>8898</v>
+        <v>7508</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -4312,7 +4304,7 @@
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>188043.75</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4335,31 +4327,31 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>7508</v>
+        <v>5910</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>17257106.84</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>0</v>
+        <v>2965168.8</v>
       </c>
       <c r="H84" s="11">
         <f>F84-G84</f>
@@ -4375,35 +4367,39 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K84" s="12" t="inlineStr"/>
+      <c r="K84" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>7414</v>
+        <v>5910</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>57497.5</v>
+        <v>2876038.16</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>0</v>
+        <v>247097.4</v>
       </c>
       <c r="H85" s="11">
         <f>F85-G85</f>
@@ -4419,32 +4415,36 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K85" s="12" t="inlineStr"/>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B86" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1119237.26</v>
+        <v>57497.5</v>
       </c>
       <c r="G86" s="10" t="n">
         <v>0</v>
@@ -4484,11 +4484,11 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>371982.96</v>
+        <v>1119237.26</v>
       </c>
       <c r="G87" s="10" t="n">
         <v>0</v>
@@ -4511,28 +4511,28 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>7244</v>
+        <v>6352</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>132708.6</v>
+        <v>371982.96</v>
       </c>
       <c r="G88" s="10" t="n">
         <v>0</v>
@@ -4558,11 +4558,11 @@
         <v>46295</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>7414</v>
+        <v>7244</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
@@ -4572,11 +4572,11 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>57497.5</v>
+        <v>132708.6</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>
@@ -4599,14 +4599,14 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46304</v>
+        <v>46295</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>6024</v>
+        <v>7414</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -4616,11 +4616,11 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>246402</v>
+        <v>57497.5</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr"/>
@@ -4646,25 +4646,25 @@
         <v>46304</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>7894</v>
+        <v>6024</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>737597.4</v>
+        <v>246402</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4687,28 +4687,28 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46316</v>
+        <v>46304</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>6356</v>
+        <v>7894</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>3310287.2</v>
+        <v>737597.4</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4727,36 +4727,32 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K92" s="12" t="inlineStr">
-        <is>
-          <t>€64 240</t>
-        </is>
-      </c>
+      <c r="K92" s="12" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46321</v>
+        <v>46316</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>651792.28</v>
+        <v>3317353.6</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4775,32 +4771,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K93" s="12" t="inlineStr"/>
+      <c r="K93" s="12" t="inlineStr">
+        <is>
+          <t>€64 240</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>6356</v>
+        <v>6352</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>662057.4400000001</v>
+        <v>651792.28</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -4819,33 +4819,77 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K94" s="12" t="inlineStr">
+      <c r="K94" s="12" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>6356</v>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>Хома</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="n">
+        <v>663470.72</v>
+      </c>
+      <c r="G95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="11">
+        <f>F95-G95</f>
+        <v/>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K95" s="12" t="inlineStr">
         <is>
           <t>€12 848</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="E95" s="3" t="inlineStr">
+    <row r="96">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F95" s="13">
-        <f>SUM(F2:F94)</f>
-        <v/>
-      </c>
-      <c r="G95" s="13">
-        <f>SUM(G2:G94)</f>
-        <v/>
-      </c>
-      <c r="H95" s="13">
-        <f>SUM(H2:H94)</f>
+      <c r="F96" s="13">
+        <f>SUM(F2:F95)</f>
+        <v/>
+      </c>
+      <c r="G96" s="13">
+        <f>SUM(G2:G95)</f>
+        <v/>
+      </c>
+      <c r="H96" s="13">
+        <f>SUM(H2:H95)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I94"/>
+  <autoFilter ref="A1:I95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5139,7 +5183,7 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B2" s="9" t="n">
         <v>6356</v>
@@ -5155,7 +5199,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2648229.76</v>
+        <v>2653882.88</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5167,23 +5211,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>4766</v>
+        <v>7002</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1263447.42</v>
+        <v>257000</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 03.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 04.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2582000</v>
+        <v>2596500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2582000</v>
+        <v>2596500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5164000</v>
+        <v>5193000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5164000</v>
+        <v>5193000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1859040</v>
+        <v>1869480</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1859040</v>
+        <v>1869480</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>454432</v>
+        <v>456984</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>454432</v>
+        <v>456984</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8628527.6</v>
+        <v>8676983.699999999</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8628527.6</v>
+        <v>8676983.699999999</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4064068</v>
+        <v>4086891</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4064068</v>
+        <v>4086891</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4943239</v>
+        <v>4970999.25</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4943239</v>
+        <v>4970999.25</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>752653</v>
+        <v>756879.75</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>752653</v>
+        <v>756879.75</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>558486.6</v>
+        <v>561622.95</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>558486.6</v>
+        <v>561622.95</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>2653882.88</v>
+        <v>2827900.08</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
@@ -4009,34 +4009,34 @@
       </c>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>€51 392</t>
+          <t>€54 456</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>7002</v>
+        <v>8497</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>257000</v>
+        <v>1569584.25</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>0</v>
@@ -4055,32 +4055,36 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K77" s="12" t="inlineStr"/>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>€30 225</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>5870</v>
+        <v>7002</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>903700</v>
+        <v>257000</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
@@ -4099,22 +4103,18 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K78" s="12" t="inlineStr">
-        <is>
-          <t>€17 500</t>
-        </is>
-      </c>
+      <c r="K78" s="12" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>7002</v>
+        <v>3456</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4124,11 +4124,11 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>573945</v>
+        <v>335974.68</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4154,25 +4154,25 @@
         <v>46274</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>3456</v>
+        <v>5870</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>335974.68</v>
+        <v>908775</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4191,7 +4191,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K80" s="12" t="inlineStr"/>
+      <c r="K80" s="12" t="inlineStr">
+        <is>
+          <t>€17 500</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
@@ -4239,14 +4243,14 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46280</v>
+        <v>46277</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>8898</v>
+        <v>7002</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -4256,11 +4260,11 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>188043.75</v>
+        <v>573945</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4283,19 +4287,19 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>7508</v>
+        <v>8898</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -4304,7 +4308,7 @@
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>188043.75</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4327,31 +4331,31 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>5910</v>
+        <v>7508</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>17257106.84</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>2965168.8</v>
+        <v>0</v>
       </c>
       <c r="H84" s="11">
         <f>F84-G84</f>
@@ -4367,11 +4371,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K84" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K84" s="12" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
@@ -4392,14 +4392,14 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>2876038.16</v>
+        <v>17354019.33</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>247097.4</v>
+        <v>7238055.33</v>
       </c>
       <c r="H85" s="11">
         <f>F85-G85</f>
@@ -4417,37 +4417,37 @@
       </c>
       <c r="K85" s="12" t="inlineStr">
         <is>
-          <t>€55 694</t>
+          <t>€334 181</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B86" s="9" t="n">
-        <v>7414</v>
+        <v>5910</v>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>57497.5</v>
+        <v>2892189.42</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>0</v>
+        <v>459216.99</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4463,32 +4463,36 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K86" s="12" t="inlineStr"/>
+      <c r="K86" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B87" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>1119237.26</v>
+        <v>57497.5</v>
       </c>
       <c r="G87" s="10" t="n">
         <v>0</v>
@@ -4528,11 +4532,11 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>371982.96</v>
+        <v>1119237.26</v>
       </c>
       <c r="G88" s="10" t="n">
         <v>0</v>
@@ -4555,28 +4559,28 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>7244</v>
+        <v>6352</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>132708.6</v>
+        <v>371982.96</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>
@@ -4602,11 +4606,11 @@
         <v>46295</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>7414</v>
+        <v>7244</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -4616,11 +4620,11 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>57497.5</v>
+        <v>132708.6</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4643,14 +4647,14 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46304</v>
+        <v>46295</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>6024</v>
+        <v>7414</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -4660,11 +4664,11 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>246402</v>
+        <v>57497.5</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4680,7 +4684,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K91" s="12" t="inlineStr"/>
@@ -4690,25 +4694,25 @@
         <v>46304</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>7894</v>
+        <v>6024</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>737597.4</v>
+        <v>246402</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4731,28 +4735,28 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>6356</v>
+        <v>7894</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>3317353.6</v>
+        <v>737597.4</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4771,36 +4775,32 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K93" s="12" t="inlineStr">
-        <is>
-          <t>€64 240</t>
-        </is>
-      </c>
+      <c r="K93" s="12" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46321</v>
+        <v>46311</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>6352</v>
+        <v>8497</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>651792.28</v>
+        <v>523194.75</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -4819,11 +4819,15 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K94" s="12" t="inlineStr"/>
+      <c r="K94" s="12" t="inlineStr">
+        <is>
+          <t>€10 075</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46322</v>
+        <v>46316</v>
       </c>
       <c r="B95" s="9" t="n">
         <v>6356</v>
@@ -4840,11 +4844,11 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>663470.72</v>
+        <v>3335983.2</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -4865,31 +4869,123 @@
       </c>
       <c r="K95" s="12" t="inlineStr">
         <is>
+          <t>€64 240</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B96" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>АБМК SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G96" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="11">
+        <f>F96-G96</f>
+        <v/>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K96" s="12" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B97" s="9" t="n">
+        <v>6356</v>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>Хома</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="n">
+        <v>667196.64</v>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="11">
+        <f>F97-G97</f>
+        <v/>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K97" s="12" t="inlineStr">
+        <is>
           <t>€12 848</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="E96" s="3" t="inlineStr">
+    <row r="98">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F96" s="13">
-        <f>SUM(F2:F95)</f>
-        <v/>
-      </c>
-      <c r="G96" s="13">
-        <f>SUM(G2:G95)</f>
-        <v/>
-      </c>
-      <c r="H96" s="13">
-        <f>SUM(H2:H95)</f>
+      <c r="F98" s="13">
+        <f>SUM(F2:F97)</f>
+        <v/>
+      </c>
+      <c r="G98" s="13">
+        <f>SUM(G2:G97)</f>
+        <v/>
+      </c>
+      <c r="H98" s="13">
+        <f>SUM(H2:H97)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I95"/>
+  <autoFilter ref="A1:I97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5199,7 +5295,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2653882.88</v>
+        <v>2827900.08</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5211,23 +5307,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>7002</v>
+        <v>8497</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>257000</v>
+        <v>1569584.25</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3991,7 +3991,7 @@
         <v>2827900.08</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>0</v>
+        <v>2827900.08</v>
       </c>
       <c r="H76" s="11">
         <f>F76-G76</f>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5279,14 +5279,14 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>6356</v>
+        <v>8497</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2827900.08</v>
+        <v>1569584.25</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5307,26 +5307,26 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46269</v>
+        <v>46260</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>8497</v>
+        <v>6406</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1569584.25</v>
+        <v>218602</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -5334,54 +5334,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>6406</v>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Максим Яловий Чинадієво</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>218602</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>170788</v>
-      </c>
-      <c r="G4" s="11">
-        <f>E4-F4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E5" s="13">
-        <f>SUM(E2:E4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>SUM(F2:F4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>SUM(G2:G4)</f>
+      <c r="E4" s="13">
+        <f>SUM(E2:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="13">
+        <f>SUM(F2:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="13">
+        <f>SUM(G2:G3)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 04.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 08.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2596500</v>
+        <v>2584000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2596500</v>
+        <v>2584000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5193000</v>
+        <v>5168000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5193000</v>
+        <v>5168000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1869480</v>
+        <v>1860480</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1869480</v>
+        <v>1860480</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>456984</v>
+        <v>454784</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>456984</v>
+        <v>454784</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8676983.699999999</v>
+        <v>8635211.199999999</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8676983.699999999</v>
+        <v>8635211.199999999</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4086891</v>
+        <v>4067216</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4086891</v>
+        <v>4067216</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4970999.25</v>
+        <v>4947068</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4970999.25</v>
+        <v>4947068</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>756879.75</v>
+        <v>753236</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>756879.75</v>
+        <v>753236</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3611,14 +3611,14 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>5904</v>
+        <v>6824</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>SOLAR Карпорти шт. 10 шт. 0.03 Мвт SIA Realcom</t>
+          <t>SOLAR Карпорти 2</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>561622.95</v>
+        <v>149710</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>561622.95</v>
+        <v>149710</v>
       </c>
       <c r="H68" s="11">
         <f>F68-G68</f>
@@ -3651,27 +3651,23 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K68" s="12" t="inlineStr">
-        <is>
-          <t>€10 815</t>
-        </is>
-      </c>
+      <c r="K68" s="12" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="B69" s="9" t="n">
-        <v>7414</v>
+        <v>5904</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SOLAR Карпорти шт. 10 шт. 0.03 Мвт SIA Realcom</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -3680,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>94000</v>
+        <v>558919.2</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>94000</v>
+        <v>558919.2</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3699,35 +3695,39 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K69" s="12" t="inlineStr"/>
+      <c r="K69" s="12" t="inlineStr">
+        <is>
+          <t>€10 815</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
         <v>46255</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>7894</v>
+        <v>7414</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>185968</v>
+        <v>94000</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>185968</v>
+        <v>94000</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3764,14 +3764,14 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>185967.99</v>
+        <v>185968</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>185967.99</v>
+        <v>185968</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3808,14 +3808,14 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>737597.4</v>
+        <v>185967.99</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>737597.4</v>
+        <v>185967.99</v>
       </c>
       <c r="H72" s="11">
         <f>F72-G72</f>
@@ -3838,11 +3838,11 @@
         <v>46255</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>8898</v>
+        <v>7894</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -3852,14 +3852,14 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>188043.75</v>
+        <v>737597.4</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>188043.75</v>
+        <v>737597.4</v>
       </c>
       <c r="H73" s="11">
         <f>F73-G73</f>
@@ -3879,19 +3879,19 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46260</v>
+        <v>46255</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>6406</v>
+        <v>8898</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>218602</v>
+        <v>188043.75</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>170788</v>
+        <v>188043.75</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3923,31 +3923,31 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>8878</v>
+        <v>6406</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>12823</v>
+        <v>218602</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>12823</v>
+        <v>170788</v>
       </c>
       <c r="H75" s="11">
         <f>F75-G75</f>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3967,31 +3967,31 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>6356</v>
+        <v>8878</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>2827900.08</v>
+        <v>12823</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>2827900.08</v>
+        <v>12823</v>
       </c>
       <c r="H76" s="11">
         <f>F76-G76</f>
@@ -4004,30 +4004,26 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="K76" s="12" t="inlineStr">
-        <is>
-          <t>€54 456</t>
-        </is>
-      </c>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>8497</v>
+        <v>6356</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -4036,10 +4032,10 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>1569584.25</v>
+        <v>2814286.08</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>0</v>
+        <v>2814286.08</v>
       </c>
       <c r="H77" s="11">
         <f>F77-G77</f>
@@ -4047,7 +4043,7 @@
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4057,37 +4053,37 @@
       </c>
       <c r="K77" s="12" t="inlineStr">
         <is>
-          <t>€30 225</t>
+          <t>€54 456</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>7002</v>
+        <v>7414</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>257000</v>
+        <v>13349.1</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>0</v>
+        <v>13349.1</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4095,7 +4091,7 @@
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4107,28 +4103,28 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46274</v>
+        <v>46272</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>3456</v>
+        <v>8497</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>335974.68</v>
+        <v>1562028</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>0</v>
@@ -4139,7 +4135,7 @@
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4147,32 +4143,36 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K79" s="12" t="inlineStr"/>
+      <c r="K79" s="12" t="inlineStr">
+        <is>
+          <t>€30 225</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>5870</v>
+        <v>7961</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>Сірокко Вітряк</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>908775</v>
+        <v>1159872</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4191,36 +4191,32 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K80" s="12" t="inlineStr">
-        <is>
-          <t>€17 500</t>
-        </is>
-      </c>
+      <c r="K80" s="12" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>4766</v>
+        <v>3456</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>1263447.42</v>
+        <v>335974.68</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4243,28 +4239,28 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46277</v>
+        <v>46274</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>7002</v>
+        <v>5870</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>573945</v>
+        <v>904400</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4283,18 +4279,22 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K82" s="12" t="inlineStr"/>
+      <c r="K82" s="12" t="inlineStr">
+        <is>
+          <t>€17 500</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46280</v>
+        <v>46275</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>8898</v>
+        <v>7002</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -4304,11 +4304,11 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>188043.75</v>
+        <v>573945</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4331,28 +4331,28 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>7508</v>
+        <v>7002</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>257000</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4375,31 +4375,31 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>17354019.33</v>
+        <v>1263447.42</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>7238055.33</v>
+        <v>0</v>
       </c>
       <c r="H85" s="11">
         <f>F85-G85</f>
@@ -4415,22 +4415,18 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K85" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K85" s="12" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B86" s="9" t="n">
-        <v>5910</v>
+        <v>8898</v>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
@@ -4444,10 +4440,10 @@
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>2892189.42</v>
+        <v>188043.75</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>459216.99</v>
+        <v>0</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4463,22 +4459,18 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K86" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K86" s="12" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="B87" s="9" t="n">
-        <v>7414</v>
+        <v>7508</v>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -4488,11 +4480,11 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>57497.5</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G87" s="10" t="n">
         <v>0</v>
@@ -4515,14 +4507,14 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>6352</v>
+        <v>5910</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
@@ -4532,14 +4524,14 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1119237.26</v>
+        <v>17270474.08</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>0</v>
+        <v>7203210.08</v>
       </c>
       <c r="H88" s="11">
         <f>F88-G88</f>
@@ -4555,18 +4547,22 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K88" s="12" t="inlineStr"/>
+      <c r="K88" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>6352</v>
+        <v>5910</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
@@ -4576,14 +4572,14 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>371982.96</v>
+        <v>2878265.92</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>0</v>
+        <v>457006.24</v>
       </c>
       <c r="H89" s="11">
         <f>F89-G89</f>
@@ -4599,18 +4595,22 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K89" s="12" t="inlineStr"/>
+      <c r="K89" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>7244</v>
+        <v>7414</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -4620,11 +4620,11 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>132708.6</v>
+        <v>44148.4</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4647,28 +4647,28 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>7414</v>
+        <v>7961</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>Сірокко Вітряк</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>57497.5</v>
+        <v>497088</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4691,28 +4691,28 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46304</v>
+        <v>46289</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>6024</v>
+        <v>7961</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>Сірокко Вітряк</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>246402</v>
+        <v>606396</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4728,21 +4728,21 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K92" s="12" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46308</v>
+        <v>46293</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>7894</v>
+        <v>6352</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>737597.4</v>
+        <v>1119237.26</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4772,35 +4772,35 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K93" s="12" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46311</v>
+        <v>46293</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>8497</v>
+        <v>6352</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>523194.75</v>
+        <v>371982.96</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -4816,39 +4816,35 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K94" s="12" t="inlineStr">
-        <is>
-          <t>€10 075</t>
-        </is>
-      </c>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46316</v>
+        <v>46295</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>6356</v>
+        <v>7244</v>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>3335983.2</v>
+        <v>132708.6</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -4864,39 +4860,35 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K95" s="12" t="inlineStr">
-        <is>
-          <t>€64 240</t>
-        </is>
-      </c>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K95" s="12" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46321</v>
+        <v>46295</v>
       </c>
       <c r="B96" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>651792.28</v>
+        <v>57497.5</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -4912,35 +4904,35 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K96" s="12" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>46322</v>
+        <v>46300</v>
       </c>
       <c r="B97" s="9" t="n">
-        <v>6356</v>
+        <v>6024</v>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>667196.64</v>
+        <v>246402</v>
       </c>
       <c r="G97" s="10" t="n">
         <v>0</v>
@@ -4959,33 +4951,349 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K97" s="12" t="inlineStr">
+      <c r="K97" s="12" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B98" s="9" t="n">
+        <v>6024</v>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>3999</v>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="11">
+        <f>F98-G98</f>
+        <v/>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K98" s="12" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B99" s="9" t="n">
+        <v>7961</v>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Сірокко Вітряк</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>Іщук</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>Четвертий платіж</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="n">
+        <v>259884</v>
+      </c>
+      <c r="G99" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="11">
+        <f>F99-G99</f>
+        <v/>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K99" s="12" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B100" s="9" t="n">
+        <v>7894</v>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>SCP Фора  Хотів</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>737597.4</v>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="11">
+        <f>F100-G100</f>
+        <v/>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B101" s="9" t="n">
+        <v>8497</v>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>LSG 110MWt   50 points</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>Іщук</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="n">
+        <v>520676</v>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="11">
+        <f>F101-G101</f>
+        <v/>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K101" s="12" t="inlineStr">
+        <is>
+          <t>€10 075</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B102" s="9" t="n">
+        <v>6356</v>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>Хома</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>3319923.2</v>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="11">
+        <f>F102-G102</f>
+        <v/>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K102" s="12" t="inlineStr">
+        <is>
+          <t>€64 240</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B103" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>АБМК SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="11">
+        <f>F103-G103</f>
+        <v/>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K103" s="12" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B104" s="9" t="n">
+        <v>6356</v>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>Хома</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>663984.64</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="11">
+        <f>F104-G104</f>
+        <v/>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K104" s="12" t="inlineStr">
         <is>
           <t>€12 848</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="E98" s="3" t="inlineStr">
+    <row r="105">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F98" s="13">
-        <f>SUM(F2:F97)</f>
-        <v/>
-      </c>
-      <c r="G98" s="13">
-        <f>SUM(G2:G97)</f>
-        <v/>
-      </c>
-      <c r="H98" s="13">
-        <f>SUM(H2:H97)</f>
+      <c r="F105" s="13">
+        <f>SUM(F2:F104)</f>
+        <v/>
+      </c>
+      <c r="G105" s="13">
+        <f>SUM(G2:G104)</f>
+        <v/>
+      </c>
+      <c r="H105" s="13">
+        <f>SUM(H2:H104)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I97"/>
+  <autoFilter ref="A1:I104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5228,7 +5536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5279,7 +5587,7 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B2" s="9" t="n">
         <v>8497</v>
@@ -5295,7 +5603,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1569584.25</v>
+        <v>1562028</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5307,26 +5615,26 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46260</v>
+        <v>46273</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6406</v>
+        <v>7961</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Сірокко Вітряк</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>218602</v>
+        <v>1159872</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -5334,26 +5642,54 @@
       </c>
     </row>
     <row r="4">
-      <c r="D4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>170788</v>
+      </c>
+      <c r="G4" s="11">
+        <f>E4-F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E4" s="13">
-        <f>SUM(E2:E3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>SUM(F2:F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>SUM(G2:G3)</f>
+      <c r="E5" s="13">
+        <f>SUM(E2:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="13">
+        <f>SUM(F2:F4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="13">
+        <f>SUM(G2:G4)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 08.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 09.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2584000</v>
+        <v>2581500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2584000</v>
+        <v>2581500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5168000</v>
+        <v>5163000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5168000</v>
+        <v>5163000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1860480</v>
+        <v>1858680</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1860480</v>
+        <v>1858680</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>454784</v>
+        <v>454344</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>454784</v>
+        <v>454344</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8635211.199999999</v>
+        <v>8626856.700000001</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8635211.199999999</v>
+        <v>8626856.700000001</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4067216</v>
+        <v>4063281</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4067216</v>
+        <v>4063281</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4947068</v>
+        <v>4942281.75</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4947068</v>
+        <v>4942281.75</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>753236</v>
+        <v>752507.25</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>753236</v>
+        <v>752507.25</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>558919.2</v>
+        <v>558378.4500000001</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>558919.2</v>
+        <v>558378.4500000001</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>2814286.08</v>
+        <v>2811563.28</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>2814286.08</v>
+        <v>2811563.28</v>
       </c>
       <c r="H77" s="11">
         <f>F77-G77</f>
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>1562028</v>
+        <v>1560516.75</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>0</v>
+        <v>1560516.75</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4151,28 +4151,28 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>7961</v>
+        <v>3456</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Сірокко Вітряк</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1159872</v>
+        <v>335974.68</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4198,25 +4198,25 @@
         <v>46274</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>3456</v>
+        <v>5870</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>335974.68</v>
+        <v>903525</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4235,32 +4235,36 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K81" s="12" t="inlineStr"/>
+      <c r="K81" s="12" t="inlineStr">
+        <is>
+          <t>€17 500</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>5870</v>
+        <v>7002</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>904400</v>
+        <v>573945</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4279,11 +4283,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K82" s="12" t="inlineStr">
-        <is>
-          <t>€17 500</t>
-        </is>
-      </c>
+      <c r="K82" s="12" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
@@ -4304,11 +4304,11 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>573945</v>
+        <v>257000</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4331,14 +4331,14 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>7002</v>
+        <v>8898</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
@@ -4348,11 +4348,11 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>257000</v>
+        <v>188043.75</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4375,7 +4375,7 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B85" s="9" t="n">
         <v>4766</v>
@@ -4419,19 +4419,19 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B86" s="9" t="n">
-        <v>8898</v>
+        <v>7508</v>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>188043.75</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G86" s="10" t="n">
         <v>0</v>
@@ -4463,31 +4463,31 @@
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B87" s="9" t="n">
-        <v>7508</v>
+        <v>5910</v>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>17253765.03</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>0</v>
+        <v>7196241.03</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4503,7 +4503,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K87" s="12" t="inlineStr"/>
+      <c r="K87" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
@@ -4524,14 +4528,14 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>17270474.08</v>
+        <v>2875481.22</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>7203210.08</v>
+        <v>456564.09</v>
       </c>
       <c r="H88" s="11">
         <f>F88-G88</f>
@@ -4549,7 +4553,7 @@
       </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
-          <t>€334 181</t>
+          <t>€55 694</t>
         </is>
       </c>
     </row>
@@ -4558,16 +4562,16 @@
         <v>46286</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>5910</v>
+        <v>7414</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -4576,10 +4580,10 @@
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>2878265.92</v>
+        <v>44148.4</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>457006.24</v>
+        <v>0</v>
       </c>
       <c r="H89" s="11">
         <f>F89-G89</f>
@@ -4595,27 +4599,23 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K89" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K89" s="12" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>7414</v>
+        <v>6352</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>44148.4</v>
+        <v>1119237.26</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4647,28 +4647,28 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>7961</v>
+        <v>6352</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Сірокко Вітряк</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>497088</v>
+        <v>371982.96</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4691,28 +4691,28 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>7961</v>
+        <v>7244</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Сірокко Вітряк</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>606396</v>
+        <v>132708.6</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4735,28 +4735,28 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>1119237.26</v>
+        <v>57497.5</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4779,28 +4779,28 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>6352</v>
+        <v>6024</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>371982.96</v>
+        <v>246402</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -4816,21 +4816,21 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>7244</v>
+        <v>6024</v>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -4840,11 +4840,11 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>132708.6</v>
+        <v>3999</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -4860,35 +4860,35 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K95" s="12" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46295</v>
+        <v>46311</v>
       </c>
       <c r="B96" s="9" t="n">
-        <v>7414</v>
+        <v>7894</v>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>57497.5</v>
+        <v>737597.4</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -4904,26 +4904,26 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K96" s="12" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="B97" s="9" t="n">
-        <v>6024</v>
+        <v>8497</v>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>246402</v>
+        <v>520172.25</v>
       </c>
       <c r="G97" s="10" t="n">
         <v>0</v>
@@ -4951,32 +4951,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K97" s="12" t="inlineStr"/>
+      <c r="K97" s="12" t="inlineStr">
+        <is>
+          <t>€10 075</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46300</v>
+        <v>46316</v>
       </c>
       <c r="B98" s="9" t="n">
-        <v>6024</v>
+        <v>6356</v>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3999</v>
+        <v>3316711.2</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -4995,32 +4999,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K98" s="12" t="inlineStr"/>
+      <c r="K98" s="12" t="inlineStr">
+        <is>
+          <t>€64 240</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>46303</v>
+        <v>46321</v>
       </c>
       <c r="B99" s="9" t="n">
-        <v>7961</v>
+        <v>6352</v>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Сірокко Вітряк</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>259884</v>
+        <v>651792.28</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
@@ -5043,28 +5051,28 @@
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46311</v>
+        <v>46322</v>
       </c>
       <c r="B100" s="9" t="n">
-        <v>7894</v>
+        <v>6356</v>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>737597.4</v>
+        <v>663342.24</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
@@ -5083,217 +5091,33 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K100" s="12" t="inlineStr"/>
+      <c r="K100" s="12" t="inlineStr">
+        <is>
+          <t>€12 848</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B101" s="9" t="n">
-        <v>8497</v>
-      </c>
-      <c r="C101" s="9" t="inlineStr">
-        <is>
-          <t>LSG 110MWt   50 points</t>
-        </is>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>Іщук</t>
-        </is>
-      </c>
-      <c r="E101" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="F101" s="10" t="n">
-        <v>520676</v>
-      </c>
-      <c r="G101" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="11">
-        <f>F101-G101</f>
-        <v/>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>очікується</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K101" s="12" t="inlineStr">
-        <is>
-          <t>€10 075</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="8" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B102" s="9" t="n">
-        <v>6356</v>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>Хома</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="F102" s="10" t="n">
-        <v>3319923.2</v>
-      </c>
-      <c r="G102" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="11">
-        <f>F102-G102</f>
-        <v/>
-      </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>очікується</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K102" s="12" t="inlineStr">
-        <is>
-          <t>€64 240</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="8" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B103" s="9" t="n">
-        <v>6352</v>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>АБМК SCP Blade 8PS</t>
-        </is>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>Донська</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>П'ятий платіж</t>
-        </is>
-      </c>
-      <c r="F103" s="10" t="n">
-        <v>651792.28</v>
-      </c>
-      <c r="G103" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="11">
-        <f>F103-G103</f>
-        <v/>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>очікується</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K103" s="12" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="8" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B104" s="9" t="n">
-        <v>6356</v>
-      </c>
-      <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
-        </is>
-      </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>Хома</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="F104" s="10" t="n">
-        <v>663984.64</v>
-      </c>
-      <c r="G104" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="11">
-        <f>F104-G104</f>
-        <v/>
-      </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>очікується</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K104" s="12" t="inlineStr">
-        <is>
-          <t>€12 848</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F105" s="13">
-        <f>SUM(F2:F104)</f>
-        <v/>
-      </c>
-      <c r="G105" s="13">
-        <f>SUM(G2:G104)</f>
-        <v/>
-      </c>
-      <c r="H105" s="13">
-        <f>SUM(H2:H104)</f>
+      <c r="F101" s="13">
+        <f>SUM(F2:F100)</f>
+        <v/>
+      </c>
+      <c r="G101" s="13">
+        <f>SUM(G2:G100)</f>
+        <v/>
+      </c>
+      <c r="H101" s="13">
+        <f>SUM(H2:H100)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I104"/>
+  <autoFilter ref="A1:I100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5587,23 +5411,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>8497</v>
+        <v>5870</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1562028</v>
+        <v>903525</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5615,23 +5439,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>7961</v>
+        <v>3456</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Сірокко Вітряк</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1159872</v>
+        <v>335974.68</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$100</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 09.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 10.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2581500</v>
+        <v>2599500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2581500</v>
+        <v>2599500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5163000</v>
+        <v>5199000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5163000</v>
+        <v>5199000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1858680</v>
+        <v>1871640</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1858680</v>
+        <v>1871640</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>454344</v>
+        <v>457512</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>454344</v>
+        <v>457512</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8626856.700000001</v>
+        <v>8687009.1</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8626856.700000001</v>
+        <v>8687009.1</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4063281</v>
+        <v>4091613</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4063281</v>
+        <v>4091613</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4942281.75</v>
+        <v>4976742.75</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4942281.75</v>
+        <v>4976742.75</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>752507.25</v>
+        <v>757754.25</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>752507.25</v>
+        <v>757754.25</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>558378.4500000001</v>
+        <v>562271.85</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>558378.4500000001</v>
+        <v>562271.85</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>2811563.28</v>
+        <v>2831167.44</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>2811563.28</v>
+        <v>2831167.44</v>
       </c>
       <c r="H77" s="11">
         <f>F77-G77</f>
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>1560516.75</v>
+        <v>1571397.75</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>1560516.75</v>
+        <v>1571397.75</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>903525</v>
+        <v>909825</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>17253765.03</v>
+        <v>17374070.19</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>7196241.03</v>
+        <v>7246418.19</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>2875481.22</v>
+        <v>2895531.06</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>456564.09</v>
+        <v>459747.57</v>
       </c>
       <c r="H88" s="11">
         <f>F88-G88</f>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>520172.25</v>
+        <v>523799.25</v>
       </c>
       <c r="G97" s="10" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3316711.2</v>
+        <v>3339837.6</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>663342.24</v>
+        <v>667967.52</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>903525</v>
+        <v>909825</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5439,23 +5439,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>3456</v>
+        <v>7002</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>335974.68</v>
+        <v>573945</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -5467,26 +5467,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46260</v>
+        <v>46274</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6406</v>
+        <v>3456</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>218602</v>
+        <v>335974.68</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -5494,26 +5494,82 @@
       </c>
     </row>
     <row r="5">
-      <c r="D5" s="3" t="inlineStr">
+      <c r="A5" s="8" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>7002</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Фора SCP Млиново</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Шостий платіж (Допка)</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>257000</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11">
+        <f>E5-F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>170788</v>
+      </c>
+      <c r="G6" s="11">
+        <f>E6-F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E5" s="13">
-        <f>SUM(E2:E4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>SUM(F2:F4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>SUM(G2:G4)</f>
+      <c r="E7" s="13">
+        <f>SUM(E2:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="13">
+        <f>SUM(F2:F6)</f>
+        <v/>
+      </c>
+      <c r="G7" s="13">
+        <f>SUM(G2:G6)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$100</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 10.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 11.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2599500</v>
+        <v>2588000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2599500</v>
+        <v>2588000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5199000</v>
+        <v>5176000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5199000</v>
+        <v>5176000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1871640</v>
+        <v>1863360</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1871640</v>
+        <v>1863360</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>457512</v>
+        <v>455488</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>457512</v>
+        <v>455488</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8687009.1</v>
+        <v>8648578.4</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8687009.1</v>
+        <v>8648578.4</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4091613</v>
+        <v>4073512</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4091613</v>
+        <v>4073512</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4976742.75</v>
+        <v>4954726</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4976742.75</v>
+        <v>4954726</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>757754.25</v>
+        <v>754402</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>757754.25</v>
+        <v>754402</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>562271.85</v>
+        <v>559784.4</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>562271.85</v>
+        <v>559784.4</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>2831167.44</v>
+        <v>2818642.56</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>2831167.44</v>
+        <v>2818642.56</v>
       </c>
       <c r="H77" s="11">
         <f>F77-G77</f>
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>1571397.75</v>
+        <v>1564446</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>1571397.75</v>
+        <v>1564446</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4151,28 +4151,28 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>3456</v>
+        <v>5870</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>335974.68</v>
+        <v>905800</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4191,32 +4191,36 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K80" s="12" t="inlineStr"/>
+      <c r="K80" s="12" t="inlineStr">
+        <is>
+          <t>€17 500</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>5870</v>
+        <v>7002</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>909825</v>
+        <v>573945</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4227,7 +4231,7 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4235,15 +4239,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K81" s="12" t="inlineStr">
-        <is>
-          <t>€17 500</t>
-        </is>
-      </c>
+      <c r="K81" s="12" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B82" s="9" t="n">
         <v>7002</v>
@@ -4260,11 +4260,11 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>573945</v>
+        <v>257000</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4287,14 +4287,14 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>7002</v>
+        <v>8898</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -4304,11 +4304,11 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>257000</v>
+        <v>188043.75</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4331,14 +4331,14 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>8898</v>
+        <v>3456</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>А Підселання фундаменту</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>188043.75</v>
+        <v>335974.68</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4378,11 +4378,11 @@
         <v>46283</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>4766</v>
+        <v>7508</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -4392,11 +4392,11 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>1263447.42</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G85" s="10" t="n">
         <v>0</v>
@@ -4419,31 +4419,31 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B86" s="9" t="n">
-        <v>7508</v>
+        <v>5910</v>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>17297208.56</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>0</v>
+        <v>7214360.56</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4459,7 +4459,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K86" s="12" t="inlineStr"/>
+      <c r="K86" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
@@ -4480,14 +4484,14 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>17374070.19</v>
+        <v>2882721.44</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>7246418.19</v>
+        <v>457713.68</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4505,7 +4509,7 @@
       </c>
       <c r="K87" s="12" t="inlineStr">
         <is>
-          <t>€334 181</t>
+          <t>€55 694</t>
         </is>
       </c>
     </row>
@@ -4514,16 +4518,16 @@
         <v>46286</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>5910</v>
+        <v>7414</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
@@ -4532,10 +4536,10 @@
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>2895531.06</v>
+        <v>44148.4</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>459747.57</v>
+        <v>0</v>
       </c>
       <c r="H88" s="11">
         <f>F88-G88</f>
@@ -4551,27 +4555,23 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K88" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K88" s="12" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>7414</v>
+        <v>6352</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>44148.4</v>
+        <v>1119237.26</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>
@@ -4620,11 +4620,11 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>1119237.26</v>
+        <v>371982.96</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4647,28 +4647,28 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>6352</v>
+        <v>7244</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>371982.96</v>
+        <v>132708.6</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4694,11 +4694,11 @@
         <v>46295</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>7244</v>
+        <v>7414</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
@@ -4708,11 +4708,11 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>132708.6</v>
+        <v>57497.5</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4735,14 +4735,14 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>7414</v>
+        <v>4766</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>57497.5</v>
+        <v>1263447.42</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K93" s="12" t="inlineStr"/>
@@ -4870,25 +4870,25 @@
         <v>46311</v>
       </c>
       <c r="B96" s="9" t="n">
-        <v>7894</v>
+        <v>8497</v>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>737597.4</v>
+        <v>521482</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -4907,32 +4907,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K96" s="12" t="inlineStr"/>
+      <c r="K96" s="12" t="inlineStr">
+        <is>
+          <t>€10 075</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="B97" s="9" t="n">
-        <v>8497</v>
+        <v>7894</v>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>523799.25</v>
+        <v>737597.4</v>
       </c>
       <c r="G97" s="10" t="n">
         <v>0</v>
@@ -4951,11 +4955,7 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K97" s="12" t="inlineStr">
-        <is>
-          <t>€10 075</t>
-        </is>
-      </c>
+      <c r="K97" s="12" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3339837.6</v>
+        <v>3325062.4</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>667967.52</v>
+        <v>665012.48</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5411,26 +5411,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5870</v>
+        <v>6406</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>909825</v>
+        <v>218602</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -5438,138 +5438,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>7002</v>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Фора SCP Млиново</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>П'ятий платіж</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>573945</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="11">
-        <f>E3-F3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>3456</v>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>А Підселання фундаменту</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>335974.68</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="11">
-        <f>E4-F4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>7002</v>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Фора SCP Млиново</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Шостий платіж (Допка)</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>257000</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="11">
-        <f>E5-F5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>6406</v>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Максим Яловий Чинадієво</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>218602</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>170788</v>
-      </c>
-      <c r="G6" s="11">
-        <f>E6-F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E7" s="13">
-        <f>SUM(E2:E6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>SUM(F2:F6)</f>
-        <v/>
-      </c>
-      <c r="G7" s="13">
-        <f>SUM(G2:G6)</f>
+      <c r="E3" s="13">
+        <f>SUM(E2:E2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="13">
+        <f>SUM(F2:F2)</f>
+        <v/>
+      </c>
+      <c r="G3" s="13">
+        <f>SUM(G2:G2)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>